--- a/public-assets/sample_schedule.xlsx
+++ b/public-assets/sample_schedule.xlsx
@@ -827,10 +827,10 @@
         <v>Client A</v>
       </c>
       <c r="F2" t="str">
-        <v>2025-05-05T09:00:00</v>
+        <v>2026-05-04T09:00:00</v>
       </c>
       <c r="G2" t="str">
-        <v>2025-05-05T12:00:00</v>
+        <v>2026-05-04T12:00:00</v>
       </c>
       <c r="H2" t="str">
         <v>FALSE</v>
@@ -865,10 +865,10 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>2025-05-06T14:00:00</v>
+        <v>2026-05-05T14:00:00</v>
       </c>
       <c r="G3" t="str">
-        <v>2025-05-06T15:00:00</v>
+        <v>2026-05-05T15:00:00</v>
       </c>
       <c r="H3" t="str">
         <v>FALSE</v>
@@ -903,10 +903,10 @@
         <v>Client A</v>
       </c>
       <c r="F4" t="str">
-        <v>2025-05-09T16:00:00</v>
+        <v>2026-05-08T16:00:00</v>
       </c>
       <c r="G4" t="str">
-        <v>2025-05-09T17:30:00</v>
+        <v>2026-05-08T17:30:00</v>
       </c>
       <c r="H4" t="str">
         <v>TRUE</v>

--- a/public-assets/sample_schedule.xlsx
+++ b/public-assets/sample_schedule.xlsx
@@ -713,7 +713,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:E2"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -731,12 +731,6 @@
       <c r="E1" t="str">
         <v>parentTrainingTargetMax</v>
       </c>
-      <c r="F1" t="str">
-        <v>billableHoursPerCycle</v>
-      </c>
-      <c r="G1" t="str">
-        <v>billableCycleWeeks</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2">
@@ -754,16 +748,10 @@
       <c r="E2">
         <v>4</v>
       </c>
-      <c r="F2">
-        <v>80</v>
-      </c>
-      <c r="G2">
-        <v>4</v>
-      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E2"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/public-assets/sample_schedule.xlsx
+++ b/public-assets/sample_schedule.xlsx
@@ -841,22 +841,22 @@
         <v>APT002</v>
       </c>
       <c r="B3" t="str">
-        <v>Supervision</v>
+        <v>Supervision (Sarah / Client A)</v>
       </c>
       <c r="C3" t="str">
-        <v>Weekly supervision</v>
+        <v>Weekly supervision overlapping a direct session</v>
       </c>
       <c r="D3" t="str">
         <v>Sarah Tech</v>
       </c>
       <c r="E3" t="str">
-        <v/>
+        <v>Client A</v>
       </c>
       <c r="F3" t="str">
-        <v>2026-05-05T14:00:00</v>
+        <v>2026-05-04T10:00:00</v>
       </c>
       <c r="G3" t="str">
-        <v>2026-05-05T15:00:00</v>
+        <v>2026-05-04T11:00:00</v>
       </c>
       <c r="H3" t="str">
         <v>FALSE</v>

--- a/public-assets/sample_schedule.xlsx
+++ b/public-assets/sample_schedule.xlsx
@@ -841,13 +841,13 @@
         <v>APT002</v>
       </c>
       <c r="B3" t="str">
-        <v>Supervision (Sarah / Client A)</v>
+        <v>Supervision — Client A</v>
       </c>
       <c r="C3" t="str">
-        <v>Weekly supervision overlapping a direct session</v>
+        <v>Weekly case supervision; tech being supervised is whoever is in session</v>
       </c>
       <c r="D3" t="str">
-        <v>Sarah Tech</v>
+        <v/>
       </c>
       <c r="E3" t="str">
         <v>Client A</v>

--- a/public-assets/sample_schedule.xlsx
+++ b/public-assets/sample_schedule.xlsx
@@ -400,7 +400,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:V13"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -410,131 +410,892 @@
         <v>name</v>
       </c>
       <c r="C1" t="str">
+        <v>parentTrainingMaxHours</v>
+      </c>
+      <c r="D1" t="str">
         <v>MondayStart</v>
       </c>
-      <c r="D1" t="str">
+      <c r="E1" t="str">
         <v>MondayEnd</v>
       </c>
-      <c r="E1" t="str">
+      <c r="F1" t="str">
+        <v>MondayWindows</v>
+      </c>
+      <c r="G1" t="str">
         <v>TuesdayStart</v>
       </c>
-      <c r="F1" t="str">
+      <c r="H1" t="str">
         <v>TuesdayEnd</v>
       </c>
-      <c r="G1" t="str">
+      <c r="I1" t="str">
+        <v>TuesdayWindows</v>
+      </c>
+      <c r="J1" t="str">
         <v>WednesdayStart</v>
       </c>
-      <c r="H1" t="str">
+      <c r="K1" t="str">
         <v>WednesdayEnd</v>
       </c>
-      <c r="I1" t="str">
+      <c r="L1" t="str">
+        <v>WednesdayWindows</v>
+      </c>
+      <c r="M1" t="str">
         <v>ThursdayStart</v>
       </c>
-      <c r="J1" t="str">
+      <c r="N1" t="str">
         <v>ThursdayEnd</v>
       </c>
-      <c r="K1" t="str">
+      <c r="O1" t="str">
+        <v>ThursdayWindows</v>
+      </c>
+      <c r="P1" t="str">
+        <v>notes</v>
+      </c>
+      <c r="Q1" t="str">
         <v>FridayStart</v>
       </c>
-      <c r="L1" t="str">
+      <c r="R1" t="str">
         <v>FridayEnd</v>
       </c>
-      <c r="M1" t="str">
-        <v>notes</v>
+      <c r="S1" t="str">
+        <v>FridayWindows</v>
+      </c>
+      <c r="T1" t="str">
+        <v>SaturdayStart</v>
+      </c>
+      <c r="U1" t="str">
+        <v>SaturdayEnd</v>
+      </c>
+      <c r="V1" t="str">
+        <v>SaturdayWindows</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>C001</v>
+        <v>f192eb37-ff8e-42e9-a5be-3c7a742cd358</v>
       </c>
       <c r="B2" t="str">
-        <v>Client A</v>
+        <v>AA</v>
       </c>
       <c r="C2" t="str">
-        <v>09:00</v>
+        <v/>
       </c>
       <c r="D2" t="str">
-        <v>17:00</v>
+        <v>16:00</v>
       </c>
       <c r="E2" t="str">
-        <v>09:00</v>
+        <v>19:00</v>
       </c>
       <c r="F2" t="str">
-        <v>17:00</v>
+        <v>[{"start":"16:00","end":"19:00"}]</v>
       </c>
       <c r="G2" t="str">
-        <v>09:00</v>
+        <v>16:00</v>
       </c>
       <c r="H2" t="str">
-        <v>17:00</v>
+        <v>19:00</v>
       </c>
       <c r="I2" t="str">
-        <v>09:00</v>
+        <v>[{"start":"16:00","end":"19:00"}]</v>
       </c>
       <c r="J2" t="str">
-        <v>17:00</v>
+        <v>16:00</v>
       </c>
       <c r="K2" t="str">
-        <v>09:00</v>
+        <v>19:00</v>
       </c>
       <c r="L2" t="str">
-        <v>17:00</v>
+        <v>[{"start":"16:00","end":"19:00"}]</v>
       </c>
       <c r="M2" t="str">
-        <v>Home-based services</v>
+        <v>16:00</v>
+      </c>
+      <c r="N2" t="str">
+        <v>19:00</v>
+      </c>
+      <c r="O2" t="str">
+        <v>[{"start":"16:00","end":"19:00"}]</v>
+      </c>
+      <c r="P2" t="str">
+        <v/>
+      </c>
+      <c r="Q2" t="str">
+        <v/>
+      </c>
+      <c r="R2" t="str">
+        <v/>
+      </c>
+      <c r="S2" t="str">
+        <v/>
+      </c>
+      <c r="T2" t="str">
+        <v/>
+      </c>
+      <c r="U2" t="str">
+        <v/>
+      </c>
+      <c r="V2" t="str">
+        <v/>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>C002</v>
+        <v>6069e893-806c-4f62-aaff-baf2af751813</v>
       </c>
       <c r="B3" t="str">
-        <v>Client B</v>
+        <v>AB</v>
       </c>
       <c r="C3" t="str">
+        <v/>
+      </c>
+      <c r="D3" t="str">
+        <v>10:00</v>
+      </c>
+      <c r="E3" t="str">
+        <v>15:00</v>
+      </c>
+      <c r="F3" t="str">
+        <v>[{"start":"10:00","end":"15:00"}]</v>
+      </c>
+      <c r="G3" t="str">
+        <v>10:00</v>
+      </c>
+      <c r="H3" t="str">
+        <v>15:00</v>
+      </c>
+      <c r="I3" t="str">
+        <v>[{"start":"10:00","end":"15:00"}]</v>
+      </c>
+      <c r="J3" t="str">
+        <v>10:00</v>
+      </c>
+      <c r="K3" t="str">
+        <v>15:00</v>
+      </c>
+      <c r="L3" t="str">
+        <v>[{"start":"10:00","end":"15:00"}]</v>
+      </c>
+      <c r="M3" t="str">
+        <v>10:00</v>
+      </c>
+      <c r="N3" t="str">
+        <v>15:00</v>
+      </c>
+      <c r="O3" t="str">
+        <v>[{"start":"10:00","end":"15:00"}]</v>
+      </c>
+      <c r="P3" t="str">
+        <v/>
+      </c>
+      <c r="Q3" t="str">
+        <v>10:00</v>
+      </c>
+      <c r="R3" t="str">
+        <v>15:00</v>
+      </c>
+      <c r="S3" t="str">
+        <v>[{"start":"10:00","end":"15:00"}]</v>
+      </c>
+      <c r="T3" t="str">
+        <v>10:00</v>
+      </c>
+      <c r="U3" t="str">
+        <v>15:00</v>
+      </c>
+      <c r="V3" t="str">
+        <v>[{"start":"10:00","end":"15:00"}]</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>0be8b1c8-93f8-4241-80b1-040cff827d56</v>
+      </c>
+      <c r="B4" t="str">
+        <v>BW</v>
+      </c>
+      <c r="C4" t="str">
+        <v/>
+      </c>
+      <c r="D4" t="str">
+        <v>17:30</v>
+      </c>
+      <c r="E4" t="str">
+        <v>19:30</v>
+      </c>
+      <c r="F4" t="str">
+        <v>[{"start":"17:30","end":"19:30"}]</v>
+      </c>
+      <c r="G4" t="str">
+        <v>17:30</v>
+      </c>
+      <c r="H4" t="str">
+        <v>19:30</v>
+      </c>
+      <c r="I4" t="str">
+        <v>[{"start":"17:30","end":"19:30"}]</v>
+      </c>
+      <c r="J4" t="str">
+        <v>17:30</v>
+      </c>
+      <c r="K4" t="str">
+        <v>19:30</v>
+      </c>
+      <c r="L4" t="str">
+        <v>[{"start":"17:30","end":"19:30"}]</v>
+      </c>
+      <c r="M4" t="str">
+        <v>17:30</v>
+      </c>
+      <c r="N4" t="str">
+        <v>19:30</v>
+      </c>
+      <c r="O4" t="str">
+        <v>[{"start":"17:30","end":"19:30"}]</v>
+      </c>
+      <c r="P4" t="str">
+        <v/>
+      </c>
+      <c r="Q4" t="str">
+        <v>17:30</v>
+      </c>
+      <c r="R4" t="str">
+        <v>19:30</v>
+      </c>
+      <c r="S4" t="str">
+        <v>[{"start":"17:30","end":"19:30"}]</v>
+      </c>
+      <c r="T4" t="str">
+        <v/>
+      </c>
+      <c r="U4" t="str">
+        <v/>
+      </c>
+      <c r="V4" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>eec7d8cf-af78-4b7b-8500-6f629dc522dd</v>
+      </c>
+      <c r="B5" t="str">
+        <v>CL</v>
+      </c>
+      <c r="C5" t="str">
+        <v/>
+      </c>
+      <c r="D5" t="str">
+        <v>10:45</v>
+      </c>
+      <c r="E5" t="str">
+        <v>12:45</v>
+      </c>
+      <c r="F5" t="str">
+        <v>[{"start":"10:45","end":"12:45"},{"start":"15:00","end":"17:00"}]</v>
+      </c>
+      <c r="G5" t="str">
+        <v>10:45</v>
+      </c>
+      <c r="H5" t="str">
+        <v>12:45</v>
+      </c>
+      <c r="I5" t="str">
+        <v>[{"start":"10:45","end":"12:45"},{"start":"15:00","end":"17:00"}]</v>
+      </c>
+      <c r="J5" t="str">
+        <v>10:45</v>
+      </c>
+      <c r="K5" t="str">
+        <v>12:45</v>
+      </c>
+      <c r="L5" t="str">
+        <v>[{"start":"10:45","end":"12:45"},{"start":"15:00","end":"17:00"}]</v>
+      </c>
+      <c r="M5" t="str">
+        <v>10:45</v>
+      </c>
+      <c r="N5" t="str">
+        <v>12:45</v>
+      </c>
+      <c r="O5" t="str">
+        <v>[{"start":"10:45","end":"12:45"}]</v>
+      </c>
+      <c r="P5" t="str">
+        <v/>
+      </c>
+      <c r="Q5" t="str">
+        <v>10:45</v>
+      </c>
+      <c r="R5" t="str">
+        <v>12:45</v>
+      </c>
+      <c r="S5" t="str">
+        <v>[{"start":"10:45","end":"12:45"},{"start":"15:00","end":"17:00"}]</v>
+      </c>
+      <c r="T5" t="str">
+        <v/>
+      </c>
+      <c r="U5" t="str">
+        <v/>
+      </c>
+      <c r="V5" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>b213db1a-1ffd-4a15-9ce2-e03ea5278dac</v>
+      </c>
+      <c r="B6" t="str">
+        <v>DL</v>
+      </c>
+      <c r="C6" t="str">
+        <v/>
+      </c>
+      <c r="D6" t="str">
+        <v>08:45</v>
+      </c>
+      <c r="E6" t="str">
+        <v>12:15</v>
+      </c>
+      <c r="F6" t="str">
+        <v>[{"start":"08:45","end":"12:15"}]</v>
+      </c>
+      <c r="G6" t="str">
+        <v/>
+      </c>
+      <c r="H6" t="str">
+        <v/>
+      </c>
+      <c r="I6" t="str">
+        <v/>
+      </c>
+      <c r="J6" t="str">
+        <v>08:45</v>
+      </c>
+      <c r="K6" t="str">
+        <v>12:15</v>
+      </c>
+      <c r="L6" t="str">
+        <v>[{"start":"08:45","end":"12:15"}]</v>
+      </c>
+      <c r="M6" t="str">
+        <v>08:45</v>
+      </c>
+      <c r="N6" t="str">
+        <v>12:15</v>
+      </c>
+      <c r="O6" t="str">
+        <v>[{"start":"08:45","end":"12:15"}]</v>
+      </c>
+      <c r="P6" t="str">
+        <v/>
+      </c>
+      <c r="Q6" t="str">
+        <v>08:45</v>
+      </c>
+      <c r="R6" t="str">
+        <v>12:15</v>
+      </c>
+      <c r="S6" t="str">
+        <v>[{"start":"08:45","end":"12:15"}]</v>
+      </c>
+      <c r="T6" t="str">
+        <v/>
+      </c>
+      <c r="U6" t="str">
+        <v/>
+      </c>
+      <c r="V6" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>2bc45c0c-f40e-4873-970c-2481933c6878</v>
+      </c>
+      <c r="B7" t="str">
+        <v>EC</v>
+      </c>
+      <c r="C7" t="str">
+        <v/>
+      </c>
+      <c r="D7" t="str">
+        <v>09:00</v>
+      </c>
+      <c r="E7" t="str">
+        <v>12:15</v>
+      </c>
+      <c r="F7" t="str">
+        <v>[{"start":"09:00","end":"12:15"}]</v>
+      </c>
+      <c r="G7" t="str">
+        <v>08:45</v>
+      </c>
+      <c r="H7" t="str">
+        <v>12:15</v>
+      </c>
+      <c r="I7" t="str">
+        <v>[{"start":"08:45","end":"12:15"}]</v>
+      </c>
+      <c r="J7" t="str">
+        <v>08:45</v>
+      </c>
+      <c r="K7" t="str">
+        <v>12:15</v>
+      </c>
+      <c r="L7" t="str">
+        <v>[{"start":"08:45","end":"12:15"}]</v>
+      </c>
+      <c r="M7" t="str">
+        <v>08:45</v>
+      </c>
+      <c r="N7" t="str">
+        <v>12:15</v>
+      </c>
+      <c r="O7" t="str">
+        <v>[{"start":"08:45","end":"12:15"}]</v>
+      </c>
+      <c r="P7" t="str">
+        <v/>
+      </c>
+      <c r="Q7" t="str">
+        <v>08:45</v>
+      </c>
+      <c r="R7" t="str">
+        <v>12:15</v>
+      </c>
+      <c r="S7" t="str">
+        <v>[{"start":"08:45","end":"12:15"}]</v>
+      </c>
+      <c r="T7" t="str">
+        <v/>
+      </c>
+      <c r="U7" t="str">
+        <v/>
+      </c>
+      <c r="V7" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>e5b62e37-2db5-456c-babe-038a7e56647f</v>
+      </c>
+      <c r="B8" t="str">
+        <v>EG</v>
+      </c>
+      <c r="C8" t="str">
+        <v/>
+      </c>
+      <c r="D8" t="str">
+        <v>14:15</v>
+      </c>
+      <c r="E8" t="str">
+        <v>17:00</v>
+      </c>
+      <c r="F8" t="str">
+        <v>[{"start":"14:15","end":"17:00"},{"start":"18:00","end":"20:00"}]</v>
+      </c>
+      <c r="G8" t="str">
+        <v>14:15</v>
+      </c>
+      <c r="H8" t="str">
+        <v>17:00</v>
+      </c>
+      <c r="I8" t="str">
+        <v>[{"start":"14:15","end":"17:00"},{"start":"18:00","end":"20:00"}]</v>
+      </c>
+      <c r="J8" t="str">
+        <v>14:15</v>
+      </c>
+      <c r="K8" t="str">
+        <v>17:00</v>
+      </c>
+      <c r="L8" t="str">
+        <v>[{"start":"14:15","end":"17:00"},{"start":"18:00","end":"20:00"}]</v>
+      </c>
+      <c r="M8" t="str">
+        <v>14:15</v>
+      </c>
+      <c r="N8" t="str">
+        <v>17:00</v>
+      </c>
+      <c r="O8" t="str">
+        <v>[{"start":"14:15","end":"17:00"},{"start":"18:00","end":"20:00"}]</v>
+      </c>
+      <c r="P8" t="str">
+        <v/>
+      </c>
+      <c r="Q8" t="str">
+        <v>14:15</v>
+      </c>
+      <c r="R8" t="str">
+        <v>17:00</v>
+      </c>
+      <c r="S8" t="str">
+        <v>[{"start":"14:15","end":"17:00"},{"start":"18:00","end":"20:00"}]</v>
+      </c>
+      <c r="T8" t="str">
+        <v/>
+      </c>
+      <c r="U8" t="str">
+        <v/>
+      </c>
+      <c r="V8" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>e974f1b4-1d24-4fe4-a182-1dc27a87e359</v>
+      </c>
+      <c r="B9" t="str">
+        <v>GR</v>
+      </c>
+      <c r="C9" t="str">
+        <v/>
+      </c>
+      <c r="D9" t="str">
+        <v>11:00</v>
+      </c>
+      <c r="E9" t="str">
         <v>13:00</v>
       </c>
-      <c r="D3" t="str">
-        <v>18:00</v>
-      </c>
-      <c r="E3" t="str">
-        <v>13:00</v>
-      </c>
-      <c r="F3" t="str">
-        <v>18:00</v>
-      </c>
-      <c r="G3" t="str">
-        <v>13:00</v>
-      </c>
-      <c r="H3" t="str">
-        <v>18:00</v>
-      </c>
-      <c r="I3" t="str">
-        <v>13:00</v>
-      </c>
-      <c r="J3" t="str">
-        <v>18:00</v>
-      </c>
-      <c r="K3" t="str">
-        <v>09:00</v>
-      </c>
-      <c r="L3" t="str">
+      <c r="F9" t="str">
+        <v>[{"start":"11:00","end":"13:00"}]</v>
+      </c>
+      <c r="G9" t="str">
+        <v>15:00</v>
+      </c>
+      <c r="H9" t="str">
         <v>17:00</v>
       </c>
-      <c r="M3" t="str">
-        <v>After school services</v>
+      <c r="I9" t="str">
+        <v>[{"start":"15:00","end":"17:00"}]</v>
+      </c>
+      <c r="J9" t="str">
+        <v>15:00</v>
+      </c>
+      <c r="K9" t="str">
+        <v>17:00</v>
+      </c>
+      <c r="L9" t="str">
+        <v>[{"start":"15:00","end":"17:00"}]</v>
+      </c>
+      <c r="M9" t="str">
+        <v>15:00</v>
+      </c>
+      <c r="N9" t="str">
+        <v>17:00</v>
+      </c>
+      <c r="O9" t="str">
+        <v>[{"start":"15:00","end":"17:00"}]</v>
+      </c>
+      <c r="P9" t="str">
+        <v/>
+      </c>
+      <c r="Q9" t="str">
+        <v>15:00</v>
+      </c>
+      <c r="R9" t="str">
+        <v>17:00</v>
+      </c>
+      <c r="S9" t="str">
+        <v>[{"start":"15:00","end":"17:00"}]</v>
+      </c>
+      <c r="T9" t="str">
+        <v/>
+      </c>
+      <c r="U9" t="str">
+        <v/>
+      </c>
+      <c r="V9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>fde03985-4e38-4875-b854-bce009d7f63c</v>
+      </c>
+      <c r="B10" t="str">
+        <v>JO</v>
+      </c>
+      <c r="C10" t="str">
+        <v/>
+      </c>
+      <c r="D10" t="str">
+        <v>15:30</v>
+      </c>
+      <c r="E10" t="str">
+        <v>19:00</v>
+      </c>
+      <c r="F10" t="str">
+        <v>[{"start":"15:30","end":"19:00"}]</v>
+      </c>
+      <c r="G10" t="str">
+        <v>15:30</v>
+      </c>
+      <c r="H10" t="str">
+        <v>19:00</v>
+      </c>
+      <c r="I10" t="str">
+        <v>[{"start":"15:30","end":"19:00"}]</v>
+      </c>
+      <c r="J10" t="str">
+        <v>15:30</v>
+      </c>
+      <c r="K10" t="str">
+        <v>19:00</v>
+      </c>
+      <c r="L10" t="str">
+        <v>[{"start":"15:30","end":"19:00"}]</v>
+      </c>
+      <c r="M10" t="str">
+        <v>15:30</v>
+      </c>
+      <c r="N10" t="str">
+        <v>19:00</v>
+      </c>
+      <c r="O10" t="str">
+        <v>[{"start":"15:30","end":"19:00"}]</v>
+      </c>
+      <c r="P10" t="str">
+        <v/>
+      </c>
+      <c r="Q10" t="str">
+        <v>15:30</v>
+      </c>
+      <c r="R10" t="str">
+        <v>19:00</v>
+      </c>
+      <c r="S10" t="str">
+        <v>[{"start":"15:30","end":"19:00"}]</v>
+      </c>
+      <c r="T10" t="str">
+        <v>10:00</v>
+      </c>
+      <c r="U10" t="str">
+        <v>14:00</v>
+      </c>
+      <c r="V10" t="str">
+        <v>[{"start":"10:00","end":"14:00"}]</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>8c046cf6-18e4-43a4-9804-c78f7e798661</v>
+      </c>
+      <c r="B11" t="str">
+        <v>JT</v>
+      </c>
+      <c r="C11" t="str">
+        <v/>
+      </c>
+      <c r="D11" t="str">
+        <v>08:00</v>
+      </c>
+      <c r="E11" t="str">
+        <v>12:00</v>
+      </c>
+      <c r="F11" t="str">
+        <v>[{"start":"08:00","end":"12:00"}]</v>
+      </c>
+      <c r="G11" t="str">
+        <v>08:00</v>
+      </c>
+      <c r="H11" t="str">
+        <v>12:00</v>
+      </c>
+      <c r="I11" t="str">
+        <v>[{"start":"08:00","end":"12:00"}]</v>
+      </c>
+      <c r="J11" t="str">
+        <v>08:00</v>
+      </c>
+      <c r="K11" t="str">
+        <v>12:00</v>
+      </c>
+      <c r="L11" t="str">
+        <v>[{"start":"08:00","end":"12:00"}]</v>
+      </c>
+      <c r="M11" t="str">
+        <v>08:00</v>
+      </c>
+      <c r="N11" t="str">
+        <v>12:00</v>
+      </c>
+      <c r="O11" t="str">
+        <v>[{"start":"08:00","end":"12:00"}]</v>
+      </c>
+      <c r="P11" t="str">
+        <v/>
+      </c>
+      <c r="Q11" t="str">
+        <v>08:00</v>
+      </c>
+      <c r="R11" t="str">
+        <v>12:00</v>
+      </c>
+      <c r="S11" t="str">
+        <v>[{"start":"08:00","end":"12:00"}]</v>
+      </c>
+      <c r="T11" t="str">
+        <v/>
+      </c>
+      <c r="U11" t="str">
+        <v/>
+      </c>
+      <c r="V11" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>458834bf-669f-4baa-b306-1cb87b139eb3</v>
+      </c>
+      <c r="B12" t="str">
+        <v>MR</v>
+      </c>
+      <c r="C12" t="str">
+        <v/>
+      </c>
+      <c r="D12" t="str">
+        <v>15:00</v>
+      </c>
+      <c r="E12" t="str">
+        <v>17:00</v>
+      </c>
+      <c r="F12" t="str">
+        <v>[{"start":"15:00","end":"17:00"}]</v>
+      </c>
+      <c r="G12" t="str">
+        <v>15:00</v>
+      </c>
+      <c r="H12" t="str">
+        <v>19:00</v>
+      </c>
+      <c r="I12" t="str">
+        <v>[{"start":"15:00","end":"19:00"}]</v>
+      </c>
+      <c r="J12" t="str">
+        <v>15:00</v>
+      </c>
+      <c r="K12" t="str">
+        <v>19:00</v>
+      </c>
+      <c r="L12" t="str">
+        <v>[{"start":"15:00","end":"19:00"}]</v>
+      </c>
+      <c r="M12" t="str">
+        <v>15:00</v>
+      </c>
+      <c r="N12" t="str">
+        <v>19:00</v>
+      </c>
+      <c r="O12" t="str">
+        <v>[{"start":"15:00","end":"19:00"}]</v>
+      </c>
+      <c r="P12" t="str">
+        <v/>
+      </c>
+      <c r="Q12" t="str">
+        <v>15:00</v>
+      </c>
+      <c r="R12" t="str">
+        <v>19:00</v>
+      </c>
+      <c r="S12" t="str">
+        <v>[{"start":"15:00","end":"19:00"}]</v>
+      </c>
+      <c r="T12" t="str">
+        <v/>
+      </c>
+      <c r="U12" t="str">
+        <v/>
+      </c>
+      <c r="V12" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>e3e494e9-cc01-48a1-a08a-5e3df265123e</v>
+      </c>
+      <c r="B13" t="str">
+        <v>SB</v>
+      </c>
+      <c r="C13" t="str">
+        <v/>
+      </c>
+      <c r="D13" t="str">
+        <v>17:00</v>
+      </c>
+      <c r="E13" t="str">
+        <v>19:00</v>
+      </c>
+      <c r="F13" t="str">
+        <v>[{"start":"17:00","end":"19:00"}]</v>
+      </c>
+      <c r="G13" t="str">
+        <v>17:00</v>
+      </c>
+      <c r="H13" t="str">
+        <v>19:00</v>
+      </c>
+      <c r="I13" t="str">
+        <v>[{"start":"17:00","end":"19:00"}]</v>
+      </c>
+      <c r="J13" t="str">
+        <v>17:00</v>
+      </c>
+      <c r="K13" t="str">
+        <v>19:00</v>
+      </c>
+      <c r="L13" t="str">
+        <v>[{"start":"17:00","end":"19:00"}]</v>
+      </c>
+      <c r="M13" t="str">
+        <v>17:00</v>
+      </c>
+      <c r="N13" t="str">
+        <v>19:00</v>
+      </c>
+      <c r="O13" t="str">
+        <v>[{"start":"17:00","end":"19:00"}]</v>
+      </c>
+      <c r="P13" t="str">
+        <v/>
+      </c>
+      <c r="Q13" t="str">
+        <v>17:00</v>
+      </c>
+      <c r="R13" t="str">
+        <v>19:00</v>
+      </c>
+      <c r="S13" t="str">
+        <v>[{"start":"17:00","end":"19:00"}]</v>
+      </c>
+      <c r="T13" t="str">
+        <v/>
+      </c>
+      <c r="U13" t="str">
+        <v/>
+      </c>
+      <c r="V13" t="str">
+        <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:M3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:V13"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R3"/>
+  <dimension ref="A1:Z9"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -553,167 +1314,719 @@
         <v>MondayEnd</v>
       </c>
       <c r="F1" t="str">
+        <v>MondayWindows</v>
+      </c>
+      <c r="G1" t="str">
         <v>TuesdayStart</v>
       </c>
-      <c r="G1" t="str">
+      <c r="H1" t="str">
         <v>TuesdayEnd</v>
       </c>
-      <c r="H1" t="str">
+      <c r="I1" t="str">
+        <v>TuesdayWindows</v>
+      </c>
+      <c r="J1" t="str">
         <v>WednesdayStart</v>
       </c>
-      <c r="I1" t="str">
+      <c r="K1" t="str">
         <v>WednesdayEnd</v>
       </c>
-      <c r="J1" t="str">
+      <c r="L1" t="str">
+        <v>WednesdayWindows</v>
+      </c>
+      <c r="M1" t="str">
         <v>ThursdayStart</v>
       </c>
-      <c r="K1" t="str">
+      <c r="N1" t="str">
         <v>ThursdayEnd</v>
       </c>
-      <c r="L1" t="str">
+      <c r="O1" t="str">
+        <v>ThursdayWindows</v>
+      </c>
+      <c r="P1" t="str">
         <v>FridayStart</v>
       </c>
-      <c r="M1" t="str">
+      <c r="Q1" t="str">
         <v>FridayEnd</v>
       </c>
-      <c r="N1" t="str">
+      <c r="R1" t="str">
+        <v>FridayWindows</v>
+      </c>
+      <c r="S1" t="str">
         <v>client1</v>
       </c>
-      <c r="O1" t="str">
+      <c r="T1" t="str">
         <v>hours1</v>
       </c>
-      <c r="P1" t="str">
+      <c r="U1" t="str">
+        <v>notes</v>
+      </c>
+      <c r="V1" t="str">
         <v>client2</v>
       </c>
-      <c r="Q1" t="str">
+      <c r="W1" t="str">
         <v>hours2</v>
       </c>
-      <c r="R1" t="str">
-        <v>notes</v>
+      <c r="X1" t="str">
+        <v>SaturdayStart</v>
+      </c>
+      <c r="Y1" t="str">
+        <v>SaturdayEnd</v>
+      </c>
+      <c r="Z1" t="str">
+        <v>SaturdayWindows</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>T001</v>
+        <v>605b4db3-1c7d-42c0-8074-a024ef42b9cf</v>
       </c>
       <c r="B2" t="str">
-        <v>Sarah Tech</v>
+        <v>Chen</v>
       </c>
       <c r="C2" t="str">
-        <v>TRUE</v>
+        <v>FALSE</v>
       </c>
       <c r="D2" t="str">
-        <v>08:00</v>
+        <v>08:45</v>
       </c>
       <c r="E2" t="str">
-        <v>17:00</v>
+        <v>11:00</v>
       </c>
       <c r="F2" t="str">
-        <v>08:00</v>
+        <v>[{"start":"08:45","end":"11:00"}]</v>
       </c>
       <c r="G2" t="str">
-        <v>17:00</v>
+        <v>08:45</v>
       </c>
       <c r="H2" t="str">
-        <v>08:00</v>
+        <v>11:00</v>
       </c>
       <c r="I2" t="str">
-        <v>17:00</v>
+        <v>[{"start":"08:45","end":"11:00"}]</v>
       </c>
       <c r="J2" t="str">
-        <v>08:00</v>
+        <v>08:45</v>
       </c>
       <c r="K2" t="str">
-        <v>17:00</v>
+        <v>11:00</v>
       </c>
       <c r="L2" t="str">
-        <v>08:00</v>
+        <v>[{"start":"08:45","end":"11:00"}]</v>
       </c>
       <c r="M2" t="str">
-        <v>17:00</v>
+        <v>08:45</v>
       </c>
       <c r="N2" t="str">
-        <v>C001</v>
-      </c>
-      <c r="O2">
-        <v>15</v>
+        <v>11:00</v>
+      </c>
+      <c r="O2" t="str">
+        <v>[{"start":"08:45","end":"11:00"}]</v>
       </c>
       <c r="P2" t="str">
-        <v>C002</v>
-      </c>
-      <c r="Q2">
-        <v>5</v>
+        <v>08:45</v>
+      </c>
+      <c r="Q2" t="str">
+        <v>11:00</v>
       </c>
       <c r="R2" t="str">
-        <v>Senior technician</v>
+        <v>[{"start":"08:45","end":"11:00"}]</v>
+      </c>
+      <c r="S2" t="str">
+        <v>EC</v>
+      </c>
+      <c r="T2">
+        <v>7</v>
+      </c>
+      <c r="U2" t="str">
+        <v/>
+      </c>
+      <c r="V2" t="str">
+        <v/>
+      </c>
+      <c r="W2" t="str">
+        <v/>
+      </c>
+      <c r="X2" t="str">
+        <v/>
+      </c>
+      <c r="Y2" t="str">
+        <v/>
+      </c>
+      <c r="Z2" t="str">
+        <v/>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>T002</v>
+        <v>08854fa8-4969-4c2f-92f4-ca4aa8b4e73f</v>
       </c>
       <c r="B3" t="str">
-        <v>Mike Tech</v>
+        <v>Chinazo</v>
       </c>
       <c r="C3" t="str">
-        <v>TRUE</v>
+        <v>FALSE</v>
       </c>
       <c r="D3" t="str">
-        <v>09:00</v>
+        <v>15:00</v>
       </c>
       <c r="E3" t="str">
-        <v>18:00</v>
+        <v>19:00</v>
       </c>
       <c r="F3" t="str">
-        <v>09:00</v>
+        <v>[{"start":"15:00","end":"19:00"}]</v>
       </c>
       <c r="G3" t="str">
-        <v>18:00</v>
+        <v>15:00</v>
       </c>
       <c r="H3" t="str">
-        <v>09:00</v>
+        <v>19:00</v>
       </c>
       <c r="I3" t="str">
-        <v>18:00</v>
+        <v>[{"start":"15:00","end":"19:00"}]</v>
       </c>
       <c r="J3" t="str">
-        <v>09:00</v>
+        <v>15:00</v>
       </c>
       <c r="K3" t="str">
-        <v>18:00</v>
+        <v>19:00</v>
       </c>
       <c r="L3" t="str">
+        <v>[{"start":"15:00","end":"19:00"}]</v>
+      </c>
+      <c r="M3" t="str">
+        <v>15:00</v>
+      </c>
+      <c r="N3" t="str">
+        <v>19:00</v>
+      </c>
+      <c r="O3" t="str">
+        <v>[{"start":"15:00","end":"19:00"}]</v>
+      </c>
+      <c r="P3" t="str">
+        <v>15:00</v>
+      </c>
+      <c r="Q3" t="str">
+        <v>19:00</v>
+      </c>
+      <c r="R3" t="str">
+        <v>[{"start":"15:00","end":"19:00"}]</v>
+      </c>
+      <c r="S3" t="str">
+        <v>SB</v>
+      </c>
+      <c r="T3">
+        <v>10</v>
+      </c>
+      <c r="U3" t="str">
+        <v/>
+      </c>
+      <c r="V3" t="str">
+        <v/>
+      </c>
+      <c r="W3" t="str">
+        <v/>
+      </c>
+      <c r="X3" t="str">
+        <v/>
+      </c>
+      <c r="Y3" t="str">
+        <v/>
+      </c>
+      <c r="Z3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>e11d51be-a73f-489f-b1d6-d487c99b9376</v>
+      </c>
+      <c r="B4" t="str">
+        <v>Hannah</v>
+      </c>
+      <c r="C4" t="str">
+        <v>FALSE</v>
+      </c>
+      <c r="D4" t="str">
+        <v>08:00</v>
+      </c>
+      <c r="E4" t="str">
+        <v>19:00</v>
+      </c>
+      <c r="F4" t="str">
+        <v>[{"start":"08:00","end":"19:00"}]</v>
+      </c>
+      <c r="G4" t="str">
+        <v>08:00</v>
+      </c>
+      <c r="H4" t="str">
+        <v>19:00</v>
+      </c>
+      <c r="I4" t="str">
+        <v>[{"start":"08:00","end":"19:00"}]</v>
+      </c>
+      <c r="J4" t="str">
+        <v>08:00</v>
+      </c>
+      <c r="K4" t="str">
+        <v>19:00</v>
+      </c>
+      <c r="L4" t="str">
+        <v>[{"start":"08:00","end":"19:00"}]</v>
+      </c>
+      <c r="M4" t="str">
+        <v>08:00</v>
+      </c>
+      <c r="N4" t="str">
+        <v>19:00</v>
+      </c>
+      <c r="O4" t="str">
+        <v>[{"start":"08:00","end":"19:00"}]</v>
+      </c>
+      <c r="P4" t="str">
+        <v>08:00</v>
+      </c>
+      <c r="Q4" t="str">
+        <v>19:00</v>
+      </c>
+      <c r="R4" t="str">
+        <v>[{"start":"08:00","end":"19:00"}]</v>
+      </c>
+      <c r="S4" t="str">
+        <v>EC</v>
+      </c>
+      <c r="T4">
+        <v>7</v>
+      </c>
+      <c r="U4" t="str">
+        <v/>
+      </c>
+      <c r="V4" t="str">
+        <v>DL</v>
+      </c>
+      <c r="W4">
+        <v>12.5</v>
+      </c>
+      <c r="X4" t="str">
+        <v/>
+      </c>
+      <c r="Y4" t="str">
+        <v/>
+      </c>
+      <c r="Z4" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>2cf5705e-e773-49b3-9de1-d89f6dd6081b</v>
+      </c>
+      <c r="B5" t="str">
+        <v>John</v>
+      </c>
+      <c r="C5" t="str">
+        <v>FALSE</v>
+      </c>
+      <c r="D5" t="str">
+        <v>16:00</v>
+      </c>
+      <c r="E5" t="str">
+        <v>19:00</v>
+      </c>
+      <c r="F5" t="str">
+        <v>[{"start":"16:00","end":"19:00"}]</v>
+      </c>
+      <c r="G5" t="str">
+        <v/>
+      </c>
+      <c r="H5" t="str">
+        <v/>
+      </c>
+      <c r="I5" t="str">
+        <v/>
+      </c>
+      <c r="J5" t="str">
+        <v>16:00</v>
+      </c>
+      <c r="K5" t="str">
+        <v>19:00</v>
+      </c>
+      <c r="L5" t="str">
+        <v>[{"start":"16:00","end":"19:00"}]</v>
+      </c>
+      <c r="M5" t="str">
+        <v/>
+      </c>
+      <c r="N5" t="str">
+        <v/>
+      </c>
+      <c r="O5" t="str">
+        <v/>
+      </c>
+      <c r="P5" t="str">
+        <v/>
+      </c>
+      <c r="Q5" t="str">
+        <v/>
+      </c>
+      <c r="R5" t="str">
+        <v/>
+      </c>
+      <c r="S5" t="str">
+        <v>JO</v>
+      </c>
+      <c r="T5">
+        <v>6</v>
+      </c>
+      <c r="U5" t="str">
+        <v/>
+      </c>
+      <c r="V5" t="str">
+        <v/>
+      </c>
+      <c r="W5" t="str">
+        <v/>
+      </c>
+      <c r="X5" t="str">
         <v>10:00</v>
       </c>
-      <c r="M3" t="str">
-        <v>16:00</v>
-      </c>
-      <c r="N3" t="str">
-        <v>C001</v>
-      </c>
-      <c r="O3">
+      <c r="Y5" t="str">
+        <v>14:00</v>
+      </c>
+      <c r="Z5" t="str">
+        <v>[{"start":"10:00","end":"14:00"}]</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>9e071395-b01b-471c-8698-4fabb2eba05b</v>
+      </c>
+      <c r="B6" t="str">
+        <v>Julianna</v>
+      </c>
+      <c r="C6" t="str">
+        <v>FALSE</v>
+      </c>
+      <c r="D6" t="str">
+        <v>13:00</v>
+      </c>
+      <c r="E6" t="str">
+        <v>17:00</v>
+      </c>
+      <c r="F6" t="str">
+        <v>[{"start":"13:00","end":"17:00"}]</v>
+      </c>
+      <c r="G6" t="str">
+        <v>13:00</v>
+      </c>
+      <c r="H6" t="str">
+        <v>17:00</v>
+      </c>
+      <c r="I6" t="str">
+        <v>[{"start":"13:00","end":"17:00"}]</v>
+      </c>
+      <c r="J6" t="str">
+        <v>13:00</v>
+      </c>
+      <c r="K6" t="str">
+        <v>17:00</v>
+      </c>
+      <c r="L6" t="str">
+        <v>[{"start":"13:00","end":"17:00"}]</v>
+      </c>
+      <c r="M6" t="str">
+        <v>13:00</v>
+      </c>
+      <c r="N6" t="str">
+        <v>17:00</v>
+      </c>
+      <c r="O6" t="str">
+        <v>[{"start":"13:00","end":"17:00"}]</v>
+      </c>
+      <c r="P6" t="str">
+        <v>13:00</v>
+      </c>
+      <c r="Q6" t="str">
+        <v>17:00</v>
+      </c>
+      <c r="R6" t="str">
+        <v>[{"start":"13:00","end":"17:00"}]</v>
+      </c>
+      <c r="S6" t="str">
+        <v>EG</v>
+      </c>
+      <c r="T6">
+        <v>0</v>
+      </c>
+      <c r="U6" t="str">
+        <v/>
+      </c>
+      <c r="V6" t="str">
+        <v/>
+      </c>
+      <c r="W6" t="str">
+        <v/>
+      </c>
+      <c r="X6" t="str">
+        <v/>
+      </c>
+      <c r="Y6" t="str">
+        <v/>
+      </c>
+      <c r="Z6" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>4c2b5298-d2f3-466a-bede-738670dfbb44</v>
+      </c>
+      <c r="B7" t="str">
+        <v>Kaseem</v>
+      </c>
+      <c r="C7" t="str">
+        <v>FALSE</v>
+      </c>
+      <c r="D7" t="str">
+        <v>15:00</v>
+      </c>
+      <c r="E7" t="str">
+        <v>19:00</v>
+      </c>
+      <c r="F7" t="str">
+        <v>[{"start":"15:00","end":"19:00"}]</v>
+      </c>
+      <c r="G7" t="str">
+        <v>15:00</v>
+      </c>
+      <c r="H7" t="str">
+        <v>19:00</v>
+      </c>
+      <c r="I7" t="str">
+        <v>[{"start":"15:00","end":"19:00"}]</v>
+      </c>
+      <c r="J7" t="str">
+        <v>15:00</v>
+      </c>
+      <c r="K7" t="str">
+        <v>19:00</v>
+      </c>
+      <c r="L7" t="str">
+        <v>[{"start":"15:00","end":"19:00"}]</v>
+      </c>
+      <c r="M7" t="str">
+        <v>15:00</v>
+      </c>
+      <c r="N7" t="str">
+        <v>19:00</v>
+      </c>
+      <c r="O7" t="str">
+        <v>[{"start":"15:00","end":"19:00"}]</v>
+      </c>
+      <c r="P7" t="str">
+        <v>15:00</v>
+      </c>
+      <c r="Q7" t="str">
+        <v>19:00</v>
+      </c>
+      <c r="R7" t="str">
+        <v>[{"start":"15:00","end":"19:00"}]</v>
+      </c>
+      <c r="S7" t="str">
+        <v>BW</v>
+      </c>
+      <c r="T7">
         <v>10</v>
       </c>
-      <c r="P3" t="str">
-        <v>C002</v>
-      </c>
-      <c r="Q3">
-        <v>10</v>
-      </c>
-      <c r="R3" t="str">
-        <v>New RBT</v>
+      <c r="U7" t="str">
+        <v/>
+      </c>
+      <c r="V7" t="str">
+        <v/>
+      </c>
+      <c r="W7" t="str">
+        <v/>
+      </c>
+      <c r="X7" t="str">
+        <v/>
+      </c>
+      <c r="Y7" t="str">
+        <v/>
+      </c>
+      <c r="Z7" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>6a37d697-6d20-49e4-b136-0ca61a440468</v>
+      </c>
+      <c r="B8" t="str">
+        <v>Sidiatu</v>
+      </c>
+      <c r="C8" t="str">
+        <v>FALSE</v>
+      </c>
+      <c r="D8" t="str">
+        <v>10:00</v>
+      </c>
+      <c r="E8" t="str">
+        <v>15:00</v>
+      </c>
+      <c r="F8" t="str">
+        <v>[{"start":"10:00","end":"15:00"}]</v>
+      </c>
+      <c r="G8" t="str">
+        <v>10:00</v>
+      </c>
+      <c r="H8" t="str">
+        <v>15:00</v>
+      </c>
+      <c r="I8" t="str">
+        <v>[{"start":"10:00","end":"15:00"}]</v>
+      </c>
+      <c r="J8" t="str">
+        <v>10:00</v>
+      </c>
+      <c r="K8" t="str">
+        <v>15:00</v>
+      </c>
+      <c r="L8" t="str">
+        <v>[{"start":"10:00","end":"15:00"}]</v>
+      </c>
+      <c r="M8" t="str">
+        <v>10:00</v>
+      </c>
+      <c r="N8" t="str">
+        <v>15:00</v>
+      </c>
+      <c r="O8" t="str">
+        <v>[{"start":"10:00","end":"15:00"}]</v>
+      </c>
+      <c r="P8" t="str">
+        <v>10:00</v>
+      </c>
+      <c r="Q8" t="str">
+        <v>15:00</v>
+      </c>
+      <c r="R8" t="str">
+        <v>[{"start":"10:00","end":"15:00"}]</v>
+      </c>
+      <c r="S8" t="str">
+        <v>AB</v>
+      </c>
+      <c r="T8">
+        <v>16</v>
+      </c>
+      <c r="U8" t="str">
+        <v/>
+      </c>
+      <c r="V8" t="str">
+        <v/>
+      </c>
+      <c r="W8" t="str">
+        <v/>
+      </c>
+      <c r="X8" t="str">
+        <v/>
+      </c>
+      <c r="Y8" t="str">
+        <v/>
+      </c>
+      <c r="Z8" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>6c8956a8-7c19-4de8-a9e3-19e5fb10becb</v>
+      </c>
+      <c r="B9" t="str">
+        <v>Toniel</v>
+      </c>
+      <c r="C9" t="str">
+        <v>FALSE</v>
+      </c>
+      <c r="D9" t="str">
+        <v>15:30</v>
+      </c>
+      <c r="E9" t="str">
+        <v>19:00</v>
+      </c>
+      <c r="F9" t="str">
+        <v>[{"start":"15:30","end":"19:00"}]</v>
+      </c>
+      <c r="G9" t="str">
+        <v>15:30</v>
+      </c>
+      <c r="H9" t="str">
+        <v>19:00</v>
+      </c>
+      <c r="I9" t="str">
+        <v>[{"start":"15:30","end":"19:00"}]</v>
+      </c>
+      <c r="J9" t="str">
+        <v>15:30</v>
+      </c>
+      <c r="K9" t="str">
+        <v>19:00</v>
+      </c>
+      <c r="L9" t="str">
+        <v>[{"start":"15:30","end":"19:00"}]</v>
+      </c>
+      <c r="M9" t="str">
+        <v>15:30</v>
+      </c>
+      <c r="N9" t="str">
+        <v>19:00</v>
+      </c>
+      <c r="O9" t="str">
+        <v>[{"start":"15:30","end":"19:00"}]</v>
+      </c>
+      <c r="P9" t="str">
+        <v>15:30</v>
+      </c>
+      <c r="Q9" t="str">
+        <v>19:00</v>
+      </c>
+      <c r="R9" t="str">
+        <v>[{"start":"15:30","end":"19:00"}]</v>
+      </c>
+      <c r="S9" t="str">
+        <v>JO</v>
+      </c>
+      <c r="T9">
+        <v>6</v>
+      </c>
+      <c r="U9" t="str">
+        <v/>
+      </c>
+      <c r="V9" t="str">
+        <v/>
+      </c>
+      <c r="W9" t="str">
+        <v/>
+      </c>
+      <c r="X9" t="str">
+        <v/>
+      </c>
+      <c r="Y9" t="str">
+        <v/>
+      </c>
+      <c r="Z9" t="str">
+        <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:R3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:Z9"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:G2"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -731,13 +2044,19 @@
       <c r="E1" t="str">
         <v>parentTrainingTargetMax</v>
       </c>
+      <c r="F1" t="str">
+        <v>parentTrainingPeriodUnit</v>
+      </c>
+      <c r="G1" t="str">
+        <v>clinicianAvailability</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="B2">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="C2">
         <v>1.5</v>
@@ -748,17 +2067,23 @@
       <c r="E2">
         <v>4</v>
       </c>
+      <c r="F2" t="str">
+        <v>month</v>
+      </c>
+      <c r="G2" t="str">
+        <v>{"Monday":[{"start":"08:00","end":"14:00"},{"start":"15:00","end":"19:00"}],"Tuesday":[{"start":"08:00","end":"14:00"},{"start":"15:00","end":"19:00"}],"Wednesday":[{"start":"08:00","end":"14:00"},{"start":"15:00","end":"19:00"}],"Thursday":[{"start":"08:00","end":"14:00"},{"start":"15:00","end":"19:00"}],"Friday":[{"start":"08:00","end":"14:00"},{"start":"15:00","end":"19:00"}],"Saturday":[{"start":"10:00","end":"14:00"}]}</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G2"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L4"/>
+  <dimension ref="A1:T33"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -797,28 +2122,52 @@
       <c r="L1" t="str">
         <v>recurringPattern</v>
       </c>
+      <c r="M1" t="str">
+        <v>seriesId</v>
+      </c>
+      <c r="N1" t="str">
+        <v>status</v>
+      </c>
+      <c r="O1" t="str">
+        <v>cancellationSource</v>
+      </c>
+      <c r="P1" t="str">
+        <v>cancellationReason</v>
+      </c>
+      <c r="Q1" t="str">
+        <v>cancellationUnplanned</v>
+      </c>
+      <c r="R1" t="str">
+        <v>cancellationNoticeMet</v>
+      </c>
+      <c r="S1" t="str">
+        <v>cancellationAt</v>
+      </c>
+      <c r="T1" t="str">
+        <v>cancellationNotes</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>APT001</v>
+        <v>c4f33f78-7510-4ed3-b1b5-7fcf5e342526</v>
       </c>
       <c r="B2" t="str">
-        <v>Client A - Sarah (Mon)</v>
+        <v>DL / HS</v>
       </c>
       <c r="C2" t="str">
-        <v>Direct service</v>
+        <v/>
       </c>
       <c r="D2" t="str">
-        <v>Sarah Tech</v>
+        <v>Hannah</v>
       </c>
       <c r="E2" t="str">
-        <v>Client A</v>
+        <v>DL</v>
       </c>
       <c r="F2" t="str">
-        <v>2026-05-04T09:00:00</v>
+        <v>2026-06-01T08:45:00</v>
       </c>
       <c r="G2" t="str">
-        <v>2026-05-04T12:00:00</v>
+        <v>2026-06-01T12:15:00</v>
       </c>
       <c r="H2" t="str">
         <v>FALSE</v>
@@ -833,88 +2182,1958 @@
         <v>TRUE</v>
       </c>
       <c r="L2" t="str">
-        <v>weekly</v>
+        <v>custom</v>
+      </c>
+      <c r="M2" t="str">
+        <v>f62a31a0-1e5f-4f5c-a292-a1fcf8d4ec0d</v>
+      </c>
+      <c r="N2" t="str">
+        <v>scheduled</v>
+      </c>
+      <c r="O2" t="str">
+        <v/>
+      </c>
+      <c r="P2" t="str">
+        <v/>
+      </c>
+      <c r="Q2" t="str">
+        <v/>
+      </c>
+      <c r="R2" t="str">
+        <v/>
+      </c>
+      <c r="S2" t="str">
+        <v/>
+      </c>
+      <c r="T2" t="str">
+        <v/>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>APT002</v>
+        <v>41f8a519-11f5-4fac-8975-47515199096b</v>
       </c>
       <c r="B3" t="str">
-        <v>Supervision — Client A</v>
+        <v>DL / HS</v>
       </c>
       <c r="C3" t="str">
-        <v>Weekly case supervision; tech being supervised is whoever is in session</v>
+        <v/>
       </c>
       <c r="D3" t="str">
-        <v/>
+        <v>Hannah</v>
       </c>
       <c r="E3" t="str">
-        <v>Client A</v>
+        <v>DL</v>
       </c>
       <c r="F3" t="str">
-        <v>2026-05-04T10:00:00</v>
+        <v>2026-06-03T08:45:00</v>
       </c>
       <c r="G3" t="str">
-        <v>2026-05-04T11:00:00</v>
+        <v>2026-06-03T12:15:00</v>
       </c>
       <c r="H3" t="str">
         <v>FALSE</v>
       </c>
       <c r="I3" t="str">
-        <v>FALSE</v>
+        <v>TRUE</v>
       </c>
       <c r="J3" t="str">
-        <v>supervision</v>
+        <v>client-session</v>
       </c>
       <c r="K3" t="str">
         <v>TRUE</v>
       </c>
       <c r="L3" t="str">
-        <v>weekly</v>
+        <v>custom</v>
+      </c>
+      <c r="M3" t="str">
+        <v>f62a31a0-1e5f-4f5c-a292-a1fcf8d4ec0d</v>
+      </c>
+      <c r="N3" t="str">
+        <v>scheduled</v>
+      </c>
+      <c r="O3" t="str">
+        <v/>
+      </c>
+      <c r="P3" t="str">
+        <v/>
+      </c>
+      <c r="Q3" t="str">
+        <v/>
+      </c>
+      <c r="R3" t="str">
+        <v/>
+      </c>
+      <c r="S3" t="str">
+        <v/>
+      </c>
+      <c r="T3" t="str">
+        <v/>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>APT003</v>
+        <v>f03c70a1-92fc-4fa1-a831-f9198d8cee93</v>
       </c>
       <c r="B4" t="str">
-        <v>Parent Training</v>
+        <v>DL / HS</v>
       </c>
       <c r="C4" t="str">
-        <v>Monthly session</v>
+        <v/>
       </c>
       <c r="D4" t="str">
-        <v>Sarah Tech</v>
+        <v>Hannah</v>
       </c>
       <c r="E4" t="str">
-        <v>Client A</v>
+        <v>DL</v>
       </c>
       <c r="F4" t="str">
-        <v>2026-05-08T16:00:00</v>
+        <v>2026-06-05T08:45:00</v>
       </c>
       <c r="G4" t="str">
-        <v>2026-05-08T17:30:00</v>
+        <v>2026-06-05T12:15:00</v>
       </c>
       <c r="H4" t="str">
-        <v>TRUE</v>
+        <v>FALSE</v>
       </c>
       <c r="I4" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="J4" t="str">
+        <v>client-session</v>
+      </c>
+      <c r="K4" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="L4" t="str">
+        <v>custom</v>
+      </c>
+      <c r="M4" t="str">
+        <v>f62a31a0-1e5f-4f5c-a292-a1fcf8d4ec0d</v>
+      </c>
+      <c r="N4" t="str">
+        <v>scheduled</v>
+      </c>
+      <c r="O4" t="str">
+        <v/>
+      </c>
+      <c r="P4" t="str">
+        <v/>
+      </c>
+      <c r="Q4" t="str">
+        <v/>
+      </c>
+      <c r="R4" t="str">
+        <v/>
+      </c>
+      <c r="S4" t="str">
+        <v/>
+      </c>
+      <c r="T4" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>77b7beef-0140-4ce4-9eb6-93d404b0a91f</v>
+      </c>
+      <c r="B5" t="str">
+        <v>DL / HS</v>
+      </c>
+      <c r="C5" t="str">
+        <v/>
+      </c>
+      <c r="D5" t="str">
+        <v>Hannah</v>
+      </c>
+      <c r="E5" t="str">
+        <v>DL</v>
+      </c>
+      <c r="F5" t="str">
+        <v>2026-06-08T08:45:00</v>
+      </c>
+      <c r="G5" t="str">
+        <v>2026-06-08T12:15:00</v>
+      </c>
+      <c r="H5" t="str">
         <v>FALSE</v>
       </c>
-      <c r="J4" t="str">
-        <v>parent-training</v>
-      </c>
-      <c r="K4" t="str">
+      <c r="I5" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="J5" t="str">
+        <v>client-session</v>
+      </c>
+      <c r="K5" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="L5" t="str">
+        <v>custom</v>
+      </c>
+      <c r="M5" t="str">
+        <v>f62a31a0-1e5f-4f5c-a292-a1fcf8d4ec0d</v>
+      </c>
+      <c r="N5" t="str">
+        <v>scheduled</v>
+      </c>
+      <c r="O5" t="str">
+        <v/>
+      </c>
+      <c r="P5" t="str">
+        <v/>
+      </c>
+      <c r="Q5" t="str">
+        <v/>
+      </c>
+      <c r="R5" t="str">
+        <v/>
+      </c>
+      <c r="S5" t="str">
+        <v/>
+      </c>
+      <c r="T5" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>f55bcb1f-d846-496f-bc77-2b510087c1f9</v>
+      </c>
+      <c r="B6" t="str">
+        <v>DL / HS</v>
+      </c>
+      <c r="C6" t="str">
+        <v/>
+      </c>
+      <c r="D6" t="str">
+        <v>Hannah</v>
+      </c>
+      <c r="E6" t="str">
+        <v>DL</v>
+      </c>
+      <c r="F6" t="str">
+        <v>2026-06-10T08:45:00</v>
+      </c>
+      <c r="G6" t="str">
+        <v>2026-06-10T12:15:00</v>
+      </c>
+      <c r="H6" t="str">
         <v>FALSE</v>
       </c>
-      <c r="L4" t="str">
+      <c r="I6" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="J6" t="str">
+        <v>client-session</v>
+      </c>
+      <c r="K6" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="L6" t="str">
+        <v>custom</v>
+      </c>
+      <c r="M6" t="str">
+        <v>f62a31a0-1e5f-4f5c-a292-a1fcf8d4ec0d</v>
+      </c>
+      <c r="N6" t="str">
+        <v>scheduled</v>
+      </c>
+      <c r="O6" t="str">
+        <v/>
+      </c>
+      <c r="P6" t="str">
+        <v/>
+      </c>
+      <c r="Q6" t="str">
+        <v/>
+      </c>
+      <c r="R6" t="str">
+        <v/>
+      </c>
+      <c r="S6" t="str">
+        <v/>
+      </c>
+      <c r="T6" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>a1a3bbd3-ecca-4bca-802c-88d414dc894e</v>
+      </c>
+      <c r="B7" t="str">
+        <v>DL / HS</v>
+      </c>
+      <c r="C7" t="str">
+        <v/>
+      </c>
+      <c r="D7" t="str">
+        <v>Hannah</v>
+      </c>
+      <c r="E7" t="str">
+        <v>DL</v>
+      </c>
+      <c r="F7" t="str">
+        <v>2026-06-12T08:45:00</v>
+      </c>
+      <c r="G7" t="str">
+        <v>2026-06-12T12:15:00</v>
+      </c>
+      <c r="H7" t="str">
+        <v>FALSE</v>
+      </c>
+      <c r="I7" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="J7" t="str">
+        <v>client-session</v>
+      </c>
+      <c r="K7" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="L7" t="str">
+        <v>custom</v>
+      </c>
+      <c r="M7" t="str">
+        <v>f62a31a0-1e5f-4f5c-a292-a1fcf8d4ec0d</v>
+      </c>
+      <c r="N7" t="str">
+        <v>scheduled</v>
+      </c>
+      <c r="O7" t="str">
+        <v/>
+      </c>
+      <c r="P7" t="str">
+        <v/>
+      </c>
+      <c r="Q7" t="str">
+        <v/>
+      </c>
+      <c r="R7" t="str">
+        <v/>
+      </c>
+      <c r="S7" t="str">
+        <v/>
+      </c>
+      <c r="T7" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>11be6d4e-0bdc-4d9a-b1c1-1056f3f09456</v>
+      </c>
+      <c r="B8" t="str">
+        <v>DL / HS</v>
+      </c>
+      <c r="C8" t="str">
+        <v/>
+      </c>
+      <c r="D8" t="str">
+        <v>Hannah</v>
+      </c>
+      <c r="E8" t="str">
+        <v>DL</v>
+      </c>
+      <c r="F8" t="str">
+        <v>2026-06-15T08:45:00</v>
+      </c>
+      <c r="G8" t="str">
+        <v>2026-06-15T12:15:00</v>
+      </c>
+      <c r="H8" t="str">
+        <v>FALSE</v>
+      </c>
+      <c r="I8" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="J8" t="str">
+        <v>client-session</v>
+      </c>
+      <c r="K8" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="L8" t="str">
+        <v>custom</v>
+      </c>
+      <c r="M8" t="str">
+        <v>f62a31a0-1e5f-4f5c-a292-a1fcf8d4ec0d</v>
+      </c>
+      <c r="N8" t="str">
+        <v>scheduled</v>
+      </c>
+      <c r="O8" t="str">
+        <v/>
+      </c>
+      <c r="P8" t="str">
+        <v/>
+      </c>
+      <c r="Q8" t="str">
+        <v/>
+      </c>
+      <c r="R8" t="str">
+        <v/>
+      </c>
+      <c r="S8" t="str">
+        <v/>
+      </c>
+      <c r="T8" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>f4951d7b-ed8a-4c01-87e2-3d6fbd88f280</v>
+      </c>
+      <c r="B9" t="str">
+        <v>DL / HS</v>
+      </c>
+      <c r="C9" t="str">
+        <v/>
+      </c>
+      <c r="D9" t="str">
+        <v>Hannah</v>
+      </c>
+      <c r="E9" t="str">
+        <v>DL</v>
+      </c>
+      <c r="F9" t="str">
+        <v>2026-06-17T08:45:00</v>
+      </c>
+      <c r="G9" t="str">
+        <v>2026-06-17T12:15:00</v>
+      </c>
+      <c r="H9" t="str">
+        <v>FALSE</v>
+      </c>
+      <c r="I9" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="J9" t="str">
+        <v>client-session</v>
+      </c>
+      <c r="K9" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="L9" t="str">
+        <v>custom</v>
+      </c>
+      <c r="M9" t="str">
+        <v>f62a31a0-1e5f-4f5c-a292-a1fcf8d4ec0d</v>
+      </c>
+      <c r="N9" t="str">
+        <v>scheduled</v>
+      </c>
+      <c r="O9" t="str">
+        <v/>
+      </c>
+      <c r="P9" t="str">
+        <v/>
+      </c>
+      <c r="Q9" t="str">
+        <v/>
+      </c>
+      <c r="R9" t="str">
+        <v/>
+      </c>
+      <c r="S9" t="str">
+        <v/>
+      </c>
+      <c r="T9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>141718b1-4379-4186-b0c5-4b92f6c13951</v>
+      </c>
+      <c r="B10" t="str">
+        <v>DL / HS</v>
+      </c>
+      <c r="C10" t="str">
+        <v/>
+      </c>
+      <c r="D10" t="str">
+        <v>Hannah</v>
+      </c>
+      <c r="E10" t="str">
+        <v>DL</v>
+      </c>
+      <c r="F10" t="str">
+        <v>2026-06-19T08:45:00</v>
+      </c>
+      <c r="G10" t="str">
+        <v>2026-06-19T12:15:00</v>
+      </c>
+      <c r="H10" t="str">
+        <v>FALSE</v>
+      </c>
+      <c r="I10" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="J10" t="str">
+        <v>client-session</v>
+      </c>
+      <c r="K10" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="L10" t="str">
+        <v>custom</v>
+      </c>
+      <c r="M10" t="str">
+        <v>f62a31a0-1e5f-4f5c-a292-a1fcf8d4ec0d</v>
+      </c>
+      <c r="N10" t="str">
+        <v>scheduled</v>
+      </c>
+      <c r="O10" t="str">
+        <v/>
+      </c>
+      <c r="P10" t="str">
+        <v/>
+      </c>
+      <c r="Q10" t="str">
+        <v/>
+      </c>
+      <c r="R10" t="str">
+        <v/>
+      </c>
+      <c r="S10" t="str">
+        <v/>
+      </c>
+      <c r="T10" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>d8ff5fb6-af6f-4a61-84fa-bec4cb27acf2</v>
+      </c>
+      <c r="B11" t="str">
+        <v>DL / HS</v>
+      </c>
+      <c r="C11" t="str">
+        <v/>
+      </c>
+      <c r="D11" t="str">
+        <v>Hannah</v>
+      </c>
+      <c r="E11" t="str">
+        <v>DL</v>
+      </c>
+      <c r="F11" t="str">
+        <v>2026-06-22T08:45:00</v>
+      </c>
+      <c r="G11" t="str">
+        <v>2026-06-22T12:15:00</v>
+      </c>
+      <c r="H11" t="str">
+        <v>FALSE</v>
+      </c>
+      <c r="I11" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="J11" t="str">
+        <v>client-session</v>
+      </c>
+      <c r="K11" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="L11" t="str">
+        <v>custom</v>
+      </c>
+      <c r="M11" t="str">
+        <v>f62a31a0-1e5f-4f5c-a292-a1fcf8d4ec0d</v>
+      </c>
+      <c r="N11" t="str">
+        <v>scheduled</v>
+      </c>
+      <c r="O11" t="str">
+        <v/>
+      </c>
+      <c r="P11" t="str">
+        <v/>
+      </c>
+      <c r="Q11" t="str">
+        <v/>
+      </c>
+      <c r="R11" t="str">
+        <v/>
+      </c>
+      <c r="S11" t="str">
+        <v/>
+      </c>
+      <c r="T11" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>ce6bbbba-4bfe-4b56-8138-be0a8edfa3a4</v>
+      </c>
+      <c r="B12" t="str">
+        <v>DL / HS</v>
+      </c>
+      <c r="C12" t="str">
+        <v/>
+      </c>
+      <c r="D12" t="str">
+        <v>Hannah</v>
+      </c>
+      <c r="E12" t="str">
+        <v>DL</v>
+      </c>
+      <c r="F12" t="str">
+        <v>2026-06-24T08:45:00</v>
+      </c>
+      <c r="G12" t="str">
+        <v>2026-06-24T12:15:00</v>
+      </c>
+      <c r="H12" t="str">
+        <v>FALSE</v>
+      </c>
+      <c r="I12" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="J12" t="str">
+        <v>client-session</v>
+      </c>
+      <c r="K12" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="L12" t="str">
+        <v>custom</v>
+      </c>
+      <c r="M12" t="str">
+        <v>f62a31a0-1e5f-4f5c-a292-a1fcf8d4ec0d</v>
+      </c>
+      <c r="N12" t="str">
+        <v>scheduled</v>
+      </c>
+      <c r="O12" t="str">
+        <v/>
+      </c>
+      <c r="P12" t="str">
+        <v/>
+      </c>
+      <c r="Q12" t="str">
+        <v/>
+      </c>
+      <c r="R12" t="str">
+        <v/>
+      </c>
+      <c r="S12" t="str">
+        <v/>
+      </c>
+      <c r="T12" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>4b6c6613-29a1-40aa-886b-71c18bfa9de0</v>
+      </c>
+      <c r="B13" t="str">
+        <v>DL / HS</v>
+      </c>
+      <c r="C13" t="str">
+        <v/>
+      </c>
+      <c r="D13" t="str">
+        <v>Hannah</v>
+      </c>
+      <c r="E13" t="str">
+        <v>DL</v>
+      </c>
+      <c r="F13" t="str">
+        <v>2026-06-26T08:45:00</v>
+      </c>
+      <c r="G13" t="str">
+        <v>2026-06-26T12:15:00</v>
+      </c>
+      <c r="H13" t="str">
+        <v>FALSE</v>
+      </c>
+      <c r="I13" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="J13" t="str">
+        <v>client-session</v>
+      </c>
+      <c r="K13" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="L13" t="str">
+        <v>custom</v>
+      </c>
+      <c r="M13" t="str">
+        <v>f62a31a0-1e5f-4f5c-a292-a1fcf8d4ec0d</v>
+      </c>
+      <c r="N13" t="str">
+        <v>scheduled</v>
+      </c>
+      <c r="O13" t="str">
+        <v/>
+      </c>
+      <c r="P13" t="str">
+        <v/>
+      </c>
+      <c r="Q13" t="str">
+        <v/>
+      </c>
+      <c r="R13" t="str">
+        <v/>
+      </c>
+      <c r="S13" t="str">
+        <v/>
+      </c>
+      <c r="T13" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>c5a04a2f-a163-4c4f-8d72-51448349161c</v>
+      </c>
+      <c r="B14" t="str">
+        <v>DL / HS</v>
+      </c>
+      <c r="C14" t="str">
+        <v/>
+      </c>
+      <c r="D14" t="str">
+        <v>Hannah</v>
+      </c>
+      <c r="E14" t="str">
+        <v>DL</v>
+      </c>
+      <c r="F14" t="str">
+        <v>2026-06-29T08:45:00</v>
+      </c>
+      <c r="G14" t="str">
+        <v>2026-06-29T12:15:00</v>
+      </c>
+      <c r="H14" t="str">
+        <v>FALSE</v>
+      </c>
+      <c r="I14" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="J14" t="str">
+        <v>client-session</v>
+      </c>
+      <c r="K14" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="L14" t="str">
+        <v>custom</v>
+      </c>
+      <c r="M14" t="str">
+        <v>f62a31a0-1e5f-4f5c-a292-a1fcf8d4ec0d</v>
+      </c>
+      <c r="N14" t="str">
+        <v>scheduled</v>
+      </c>
+      <c r="O14" t="str">
+        <v/>
+      </c>
+      <c r="P14" t="str">
+        <v/>
+      </c>
+      <c r="Q14" t="str">
+        <v/>
+      </c>
+      <c r="R14" t="str">
+        <v/>
+      </c>
+      <c r="S14" t="str">
+        <v/>
+      </c>
+      <c r="T14" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>397d65f8-05bd-43b5-9403-ea9ea4519028</v>
+      </c>
+      <c r="B15" t="str">
+        <v>DL / HS</v>
+      </c>
+      <c r="C15" t="str">
+        <v/>
+      </c>
+      <c r="D15" t="str">
+        <v>Hannah</v>
+      </c>
+      <c r="E15" t="str">
+        <v>DL</v>
+      </c>
+      <c r="F15" t="str">
+        <v>2026-07-01T08:45:00</v>
+      </c>
+      <c r="G15" t="str">
+        <v>2026-07-01T12:15:00</v>
+      </c>
+      <c r="H15" t="str">
+        <v>FALSE</v>
+      </c>
+      <c r="I15" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="J15" t="str">
+        <v>client-session</v>
+      </c>
+      <c r="K15" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="L15" t="str">
+        <v>custom</v>
+      </c>
+      <c r="M15" t="str">
+        <v>f62a31a0-1e5f-4f5c-a292-a1fcf8d4ec0d</v>
+      </c>
+      <c r="N15" t="str">
+        <v>scheduled</v>
+      </c>
+      <c r="O15" t="str">
+        <v/>
+      </c>
+      <c r="P15" t="str">
+        <v/>
+      </c>
+      <c r="Q15" t="str">
+        <v/>
+      </c>
+      <c r="R15" t="str">
+        <v/>
+      </c>
+      <c r="S15" t="str">
+        <v/>
+      </c>
+      <c r="T15" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>763a236c-0f48-4bbf-9c26-f42b9e1f3b23</v>
+      </c>
+      <c r="B16" t="str">
+        <v>DL / HS</v>
+      </c>
+      <c r="C16" t="str">
+        <v/>
+      </c>
+      <c r="D16" t="str">
+        <v>Hannah</v>
+      </c>
+      <c r="E16" t="str">
+        <v>DL</v>
+      </c>
+      <c r="F16" t="str">
+        <v>2026-07-03T08:45:00</v>
+      </c>
+      <c r="G16" t="str">
+        <v>2026-07-03T12:15:00</v>
+      </c>
+      <c r="H16" t="str">
+        <v>FALSE</v>
+      </c>
+      <c r="I16" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="J16" t="str">
+        <v>client-session</v>
+      </c>
+      <c r="K16" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="L16" t="str">
+        <v>custom</v>
+      </c>
+      <c r="M16" t="str">
+        <v>f62a31a0-1e5f-4f5c-a292-a1fcf8d4ec0d</v>
+      </c>
+      <c r="N16" t="str">
+        <v>scheduled</v>
+      </c>
+      <c r="O16" t="str">
+        <v/>
+      </c>
+      <c r="P16" t="str">
+        <v/>
+      </c>
+      <c r="Q16" t="str">
+        <v/>
+      </c>
+      <c r="R16" t="str">
+        <v/>
+      </c>
+      <c r="S16" t="str">
+        <v/>
+      </c>
+      <c r="T16" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>2c1e8a34-9559-4004-976d-8aeba9aaf8e4</v>
+      </c>
+      <c r="B17" t="str">
+        <v>DL / HS</v>
+      </c>
+      <c r="C17" t="str">
+        <v/>
+      </c>
+      <c r="D17" t="str">
+        <v>Hannah</v>
+      </c>
+      <c r="E17" t="str">
+        <v>DL</v>
+      </c>
+      <c r="F17" t="str">
+        <v>2026-07-06T08:45:00</v>
+      </c>
+      <c r="G17" t="str">
+        <v>2026-07-06T12:15:00</v>
+      </c>
+      <c r="H17" t="str">
+        <v>FALSE</v>
+      </c>
+      <c r="I17" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="J17" t="str">
+        <v>client-session</v>
+      </c>
+      <c r="K17" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="L17" t="str">
+        <v>custom</v>
+      </c>
+      <c r="M17" t="str">
+        <v>f62a31a0-1e5f-4f5c-a292-a1fcf8d4ec0d</v>
+      </c>
+      <c r="N17" t="str">
+        <v>scheduled</v>
+      </c>
+      <c r="O17" t="str">
+        <v/>
+      </c>
+      <c r="P17" t="str">
+        <v/>
+      </c>
+      <c r="Q17" t="str">
+        <v/>
+      </c>
+      <c r="R17" t="str">
+        <v/>
+      </c>
+      <c r="S17" t="str">
+        <v/>
+      </c>
+      <c r="T17" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>9928eeed-a398-4dd5-bd6b-dc8c4da1b8d7</v>
+      </c>
+      <c r="B18" t="str">
+        <v>DL / HS</v>
+      </c>
+      <c r="C18" t="str">
+        <v/>
+      </c>
+      <c r="D18" t="str">
+        <v>Hannah</v>
+      </c>
+      <c r="E18" t="str">
+        <v>DL</v>
+      </c>
+      <c r="F18" t="str">
+        <v>2026-07-08T08:45:00</v>
+      </c>
+      <c r="G18" t="str">
+        <v>2026-07-08T12:15:00</v>
+      </c>
+      <c r="H18" t="str">
+        <v>FALSE</v>
+      </c>
+      <c r="I18" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="J18" t="str">
+        <v>client-session</v>
+      </c>
+      <c r="K18" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="L18" t="str">
+        <v>custom</v>
+      </c>
+      <c r="M18" t="str">
+        <v>f62a31a0-1e5f-4f5c-a292-a1fcf8d4ec0d</v>
+      </c>
+      <c r="N18" t="str">
+        <v>scheduled</v>
+      </c>
+      <c r="O18" t="str">
+        <v/>
+      </c>
+      <c r="P18" t="str">
+        <v/>
+      </c>
+      <c r="Q18" t="str">
+        <v/>
+      </c>
+      <c r="R18" t="str">
+        <v/>
+      </c>
+      <c r="S18" t="str">
+        <v/>
+      </c>
+      <c r="T18" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>dec17796-748f-4b82-ac9c-4c565cc0be8f</v>
+      </c>
+      <c r="B19" t="str">
+        <v>DL / HS</v>
+      </c>
+      <c r="C19" t="str">
+        <v/>
+      </c>
+      <c r="D19" t="str">
+        <v>Hannah</v>
+      </c>
+      <c r="E19" t="str">
+        <v>DL</v>
+      </c>
+      <c r="F19" t="str">
+        <v>2026-07-10T08:45:00</v>
+      </c>
+      <c r="G19" t="str">
+        <v>2026-07-10T12:15:00</v>
+      </c>
+      <c r="H19" t="str">
+        <v>FALSE</v>
+      </c>
+      <c r="I19" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="J19" t="str">
+        <v>client-session</v>
+      </c>
+      <c r="K19" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="L19" t="str">
+        <v>custom</v>
+      </c>
+      <c r="M19" t="str">
+        <v>f62a31a0-1e5f-4f5c-a292-a1fcf8d4ec0d</v>
+      </c>
+      <c r="N19" t="str">
+        <v>scheduled</v>
+      </c>
+      <c r="O19" t="str">
+        <v/>
+      </c>
+      <c r="P19" t="str">
+        <v/>
+      </c>
+      <c r="Q19" t="str">
+        <v/>
+      </c>
+      <c r="R19" t="str">
+        <v/>
+      </c>
+      <c r="S19" t="str">
+        <v/>
+      </c>
+      <c r="T19" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>66ae4829-2942-4346-bd53-7743ae3da44e</v>
+      </c>
+      <c r="B20" t="str">
+        <v>DL / HS</v>
+      </c>
+      <c r="C20" t="str">
+        <v/>
+      </c>
+      <c r="D20" t="str">
+        <v>Hannah</v>
+      </c>
+      <c r="E20" t="str">
+        <v>DL</v>
+      </c>
+      <c r="F20" t="str">
+        <v>2026-07-13T08:45:00</v>
+      </c>
+      <c r="G20" t="str">
+        <v>2026-07-13T12:15:00</v>
+      </c>
+      <c r="H20" t="str">
+        <v>FALSE</v>
+      </c>
+      <c r="I20" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="J20" t="str">
+        <v>client-session</v>
+      </c>
+      <c r="K20" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="L20" t="str">
+        <v>custom</v>
+      </c>
+      <c r="M20" t="str">
+        <v>f62a31a0-1e5f-4f5c-a292-a1fcf8d4ec0d</v>
+      </c>
+      <c r="N20" t="str">
+        <v>scheduled</v>
+      </c>
+      <c r="O20" t="str">
+        <v/>
+      </c>
+      <c r="P20" t="str">
+        <v/>
+      </c>
+      <c r="Q20" t="str">
+        <v/>
+      </c>
+      <c r="R20" t="str">
+        <v/>
+      </c>
+      <c r="S20" t="str">
+        <v/>
+      </c>
+      <c r="T20" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>ebf3754c-44c2-4d2b-aab5-eadbef962a67</v>
+      </c>
+      <c r="B21" t="str">
+        <v>DL / HS</v>
+      </c>
+      <c r="C21" t="str">
+        <v/>
+      </c>
+      <c r="D21" t="str">
+        <v>Hannah</v>
+      </c>
+      <c r="E21" t="str">
+        <v>DL</v>
+      </c>
+      <c r="F21" t="str">
+        <v>2026-07-15T08:45:00</v>
+      </c>
+      <c r="G21" t="str">
+        <v>2026-07-15T12:15:00</v>
+      </c>
+      <c r="H21" t="str">
+        <v>FALSE</v>
+      </c>
+      <c r="I21" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="J21" t="str">
+        <v>client-session</v>
+      </c>
+      <c r="K21" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="L21" t="str">
+        <v>custom</v>
+      </c>
+      <c r="M21" t="str">
+        <v>f62a31a0-1e5f-4f5c-a292-a1fcf8d4ec0d</v>
+      </c>
+      <c r="N21" t="str">
+        <v>scheduled</v>
+      </c>
+      <c r="O21" t="str">
+        <v/>
+      </c>
+      <c r="P21" t="str">
+        <v/>
+      </c>
+      <c r="Q21" t="str">
+        <v/>
+      </c>
+      <c r="R21" t="str">
+        <v/>
+      </c>
+      <c r="S21" t="str">
+        <v/>
+      </c>
+      <c r="T21" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>fab364e2-81a5-494f-a73f-82173d7d407a</v>
+      </c>
+      <c r="B22" t="str">
+        <v>DL / HS</v>
+      </c>
+      <c r="C22" t="str">
+        <v/>
+      </c>
+      <c r="D22" t="str">
+        <v>Hannah</v>
+      </c>
+      <c r="E22" t="str">
+        <v>DL</v>
+      </c>
+      <c r="F22" t="str">
+        <v>2026-07-17T08:45:00</v>
+      </c>
+      <c r="G22" t="str">
+        <v>2026-07-17T12:15:00</v>
+      </c>
+      <c r="H22" t="str">
+        <v>FALSE</v>
+      </c>
+      <c r="I22" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="J22" t="str">
+        <v>client-session</v>
+      </c>
+      <c r="K22" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="L22" t="str">
+        <v>custom</v>
+      </c>
+      <c r="M22" t="str">
+        <v>f62a31a0-1e5f-4f5c-a292-a1fcf8d4ec0d</v>
+      </c>
+      <c r="N22" t="str">
+        <v>scheduled</v>
+      </c>
+      <c r="O22" t="str">
+        <v/>
+      </c>
+      <c r="P22" t="str">
+        <v/>
+      </c>
+      <c r="Q22" t="str">
+        <v/>
+      </c>
+      <c r="R22" t="str">
+        <v/>
+      </c>
+      <c r="S22" t="str">
+        <v/>
+      </c>
+      <c r="T22" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>c06260b9-f5c8-4c57-ab35-dd870b39048f</v>
+      </c>
+      <c r="B23" t="str">
+        <v>DL / HS</v>
+      </c>
+      <c r="C23" t="str">
+        <v/>
+      </c>
+      <c r="D23" t="str">
+        <v>Hannah</v>
+      </c>
+      <c r="E23" t="str">
+        <v>DL</v>
+      </c>
+      <c r="F23" t="str">
+        <v>2026-07-20T08:45:00</v>
+      </c>
+      <c r="G23" t="str">
+        <v>2026-07-20T12:15:00</v>
+      </c>
+      <c r="H23" t="str">
+        <v>FALSE</v>
+      </c>
+      <c r="I23" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="J23" t="str">
+        <v>client-session</v>
+      </c>
+      <c r="K23" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="L23" t="str">
+        <v>custom</v>
+      </c>
+      <c r="M23" t="str">
+        <v>f62a31a0-1e5f-4f5c-a292-a1fcf8d4ec0d</v>
+      </c>
+      <c r="N23" t="str">
+        <v>scheduled</v>
+      </c>
+      <c r="O23" t="str">
+        <v/>
+      </c>
+      <c r="P23" t="str">
+        <v/>
+      </c>
+      <c r="Q23" t="str">
+        <v/>
+      </c>
+      <c r="R23" t="str">
+        <v/>
+      </c>
+      <c r="S23" t="str">
+        <v/>
+      </c>
+      <c r="T23" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>555eefc4-7dc5-4a30-b4d5-443e12f62443</v>
+      </c>
+      <c r="B24" t="str">
+        <v>DL / HS</v>
+      </c>
+      <c r="C24" t="str">
+        <v/>
+      </c>
+      <c r="D24" t="str">
+        <v>Hannah</v>
+      </c>
+      <c r="E24" t="str">
+        <v>DL</v>
+      </c>
+      <c r="F24" t="str">
+        <v>2026-07-22T08:45:00</v>
+      </c>
+      <c r="G24" t="str">
+        <v>2026-07-22T12:15:00</v>
+      </c>
+      <c r="H24" t="str">
+        <v>FALSE</v>
+      </c>
+      <c r="I24" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="J24" t="str">
+        <v>client-session</v>
+      </c>
+      <c r="K24" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="L24" t="str">
+        <v>custom</v>
+      </c>
+      <c r="M24" t="str">
+        <v>f62a31a0-1e5f-4f5c-a292-a1fcf8d4ec0d</v>
+      </c>
+      <c r="N24" t="str">
+        <v>scheduled</v>
+      </c>
+      <c r="O24" t="str">
+        <v/>
+      </c>
+      <c r="P24" t="str">
+        <v/>
+      </c>
+      <c r="Q24" t="str">
+        <v/>
+      </c>
+      <c r="R24" t="str">
+        <v/>
+      </c>
+      <c r="S24" t="str">
+        <v/>
+      </c>
+      <c r="T24" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>9ac7761d-eda5-4af3-abe1-6fa0ea083c6f</v>
+      </c>
+      <c r="B25" t="str">
+        <v>DL / HS</v>
+      </c>
+      <c r="C25" t="str">
+        <v/>
+      </c>
+      <c r="D25" t="str">
+        <v>Hannah</v>
+      </c>
+      <c r="E25" t="str">
+        <v>DL</v>
+      </c>
+      <c r="F25" t="str">
+        <v>2026-07-24T08:45:00</v>
+      </c>
+      <c r="G25" t="str">
+        <v>2026-07-24T12:15:00</v>
+      </c>
+      <c r="H25" t="str">
+        <v>FALSE</v>
+      </c>
+      <c r="I25" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="J25" t="str">
+        <v>client-session</v>
+      </c>
+      <c r="K25" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="L25" t="str">
+        <v>custom</v>
+      </c>
+      <c r="M25" t="str">
+        <v>f62a31a0-1e5f-4f5c-a292-a1fcf8d4ec0d</v>
+      </c>
+      <c r="N25" t="str">
+        <v>scheduled</v>
+      </c>
+      <c r="O25" t="str">
+        <v/>
+      </c>
+      <c r="P25" t="str">
+        <v/>
+      </c>
+      <c r="Q25" t="str">
+        <v/>
+      </c>
+      <c r="R25" t="str">
+        <v/>
+      </c>
+      <c r="S25" t="str">
+        <v/>
+      </c>
+      <c r="T25" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>90d371f1-8431-4e60-a719-7b36a99cf3e5</v>
+      </c>
+      <c r="B26" t="str">
+        <v>DL / HS</v>
+      </c>
+      <c r="C26" t="str">
+        <v/>
+      </c>
+      <c r="D26" t="str">
+        <v>Hannah</v>
+      </c>
+      <c r="E26" t="str">
+        <v>DL</v>
+      </c>
+      <c r="F26" t="str">
+        <v>2026-07-27T08:45:00</v>
+      </c>
+      <c r="G26" t="str">
+        <v>2026-07-27T12:15:00</v>
+      </c>
+      <c r="H26" t="str">
+        <v>FALSE</v>
+      </c>
+      <c r="I26" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="J26" t="str">
+        <v>client-session</v>
+      </c>
+      <c r="K26" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="L26" t="str">
+        <v>custom</v>
+      </c>
+      <c r="M26" t="str">
+        <v>f62a31a0-1e5f-4f5c-a292-a1fcf8d4ec0d</v>
+      </c>
+      <c r="N26" t="str">
+        <v>scheduled</v>
+      </c>
+      <c r="O26" t="str">
+        <v/>
+      </c>
+      <c r="P26" t="str">
+        <v/>
+      </c>
+      <c r="Q26" t="str">
+        <v/>
+      </c>
+      <c r="R26" t="str">
+        <v/>
+      </c>
+      <c r="S26" t="str">
+        <v/>
+      </c>
+      <c r="T26" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>cd5fa09a-f55b-4630-85bc-95868f833ea2</v>
+      </c>
+      <c r="B27" t="str">
+        <v>DL / HS</v>
+      </c>
+      <c r="C27" t="str">
+        <v/>
+      </c>
+      <c r="D27" t="str">
+        <v>Hannah</v>
+      </c>
+      <c r="E27" t="str">
+        <v>DL</v>
+      </c>
+      <c r="F27" t="str">
+        <v>2026-07-29T08:45:00</v>
+      </c>
+      <c r="G27" t="str">
+        <v>2026-07-29T12:15:00</v>
+      </c>
+      <c r="H27" t="str">
+        <v>FALSE</v>
+      </c>
+      <c r="I27" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="J27" t="str">
+        <v>client-session</v>
+      </c>
+      <c r="K27" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="L27" t="str">
+        <v>custom</v>
+      </c>
+      <c r="M27" t="str">
+        <v>f62a31a0-1e5f-4f5c-a292-a1fcf8d4ec0d</v>
+      </c>
+      <c r="N27" t="str">
+        <v>scheduled</v>
+      </c>
+      <c r="O27" t="str">
+        <v/>
+      </c>
+      <c r="P27" t="str">
+        <v/>
+      </c>
+      <c r="Q27" t="str">
+        <v/>
+      </c>
+      <c r="R27" t="str">
+        <v/>
+      </c>
+      <c r="S27" t="str">
+        <v/>
+      </c>
+      <c r="T27" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>3b8727ac-16d4-4666-ad7e-a35e1d6b2c49</v>
+      </c>
+      <c r="B28" t="str">
+        <v>DL / HS</v>
+      </c>
+      <c r="C28" t="str">
+        <v/>
+      </c>
+      <c r="D28" t="str">
+        <v>Hannah</v>
+      </c>
+      <c r="E28" t="str">
+        <v>DL</v>
+      </c>
+      <c r="F28" t="str">
+        <v>2026-07-31T08:45:00</v>
+      </c>
+      <c r="G28" t="str">
+        <v>2026-07-31T12:15:00</v>
+      </c>
+      <c r="H28" t="str">
+        <v>FALSE</v>
+      </c>
+      <c r="I28" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="J28" t="str">
+        <v>client-session</v>
+      </c>
+      <c r="K28" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="L28" t="str">
+        <v>custom</v>
+      </c>
+      <c r="M28" t="str">
+        <v>f62a31a0-1e5f-4f5c-a292-a1fcf8d4ec0d</v>
+      </c>
+      <c r="N28" t="str">
+        <v>scheduled</v>
+      </c>
+      <c r="O28" t="str">
+        <v/>
+      </c>
+      <c r="P28" t="str">
+        <v/>
+      </c>
+      <c r="Q28" t="str">
+        <v/>
+      </c>
+      <c r="R28" t="str">
+        <v/>
+      </c>
+      <c r="S28" t="str">
+        <v/>
+      </c>
+      <c r="T28" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>f41b99f0-04b4-4852-9a20-1634a5a85fc2</v>
+      </c>
+      <c r="B29" t="str">
+        <v>DL / HS</v>
+      </c>
+      <c r="C29" t="str">
+        <v/>
+      </c>
+      <c r="D29" t="str">
+        <v>Hannah</v>
+      </c>
+      <c r="E29" t="str">
+        <v>DL</v>
+      </c>
+      <c r="F29" t="str">
+        <v>2026-08-03T08:45:00</v>
+      </c>
+      <c r="G29" t="str">
+        <v>2026-08-03T12:15:00</v>
+      </c>
+      <c r="H29" t="str">
+        <v>FALSE</v>
+      </c>
+      <c r="I29" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="J29" t="str">
+        <v>client-session</v>
+      </c>
+      <c r="K29" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="L29" t="str">
+        <v>custom</v>
+      </c>
+      <c r="M29" t="str">
+        <v>f62a31a0-1e5f-4f5c-a292-a1fcf8d4ec0d</v>
+      </c>
+      <c r="N29" t="str">
+        <v>scheduled</v>
+      </c>
+      <c r="O29" t="str">
+        <v/>
+      </c>
+      <c r="P29" t="str">
+        <v/>
+      </c>
+      <c r="Q29" t="str">
+        <v/>
+      </c>
+      <c r="R29" t="str">
+        <v/>
+      </c>
+      <c r="S29" t="str">
+        <v/>
+      </c>
+      <c r="T29" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>65358987-a904-4dc6-9605-0e835c45547d</v>
+      </c>
+      <c r="B30" t="str">
+        <v>DL / HS</v>
+      </c>
+      <c r="C30" t="str">
+        <v/>
+      </c>
+      <c r="D30" t="str">
+        <v>Hannah</v>
+      </c>
+      <c r="E30" t="str">
+        <v>DL</v>
+      </c>
+      <c r="F30" t="str">
+        <v>2026-08-05T08:45:00</v>
+      </c>
+      <c r="G30" t="str">
+        <v>2026-08-05T12:15:00</v>
+      </c>
+      <c r="H30" t="str">
+        <v>FALSE</v>
+      </c>
+      <c r="I30" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="J30" t="str">
+        <v>client-session</v>
+      </c>
+      <c r="K30" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="L30" t="str">
+        <v>custom</v>
+      </c>
+      <c r="M30" t="str">
+        <v>f62a31a0-1e5f-4f5c-a292-a1fcf8d4ec0d</v>
+      </c>
+      <c r="N30" t="str">
+        <v>scheduled</v>
+      </c>
+      <c r="O30" t="str">
+        <v/>
+      </c>
+      <c r="P30" t="str">
+        <v/>
+      </c>
+      <c r="Q30" t="str">
+        <v/>
+      </c>
+      <c r="R30" t="str">
+        <v/>
+      </c>
+      <c r="S30" t="str">
+        <v/>
+      </c>
+      <c r="T30" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>56ec8570-d917-468c-8c86-26a76e077d79</v>
+      </c>
+      <c r="B31" t="str">
+        <v>DL / HS</v>
+      </c>
+      <c r="C31" t="str">
+        <v/>
+      </c>
+      <c r="D31" t="str">
+        <v>Hannah</v>
+      </c>
+      <c r="E31" t="str">
+        <v>DL</v>
+      </c>
+      <c r="F31" t="str">
+        <v>2026-08-07T08:45:00</v>
+      </c>
+      <c r="G31" t="str">
+        <v>2026-08-07T12:15:00</v>
+      </c>
+      <c r="H31" t="str">
+        <v>FALSE</v>
+      </c>
+      <c r="I31" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="J31" t="str">
+        <v>client-session</v>
+      </c>
+      <c r="K31" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="L31" t="str">
+        <v>custom</v>
+      </c>
+      <c r="M31" t="str">
+        <v>f62a31a0-1e5f-4f5c-a292-a1fcf8d4ec0d</v>
+      </c>
+      <c r="N31" t="str">
+        <v>scheduled</v>
+      </c>
+      <c r="O31" t="str">
+        <v/>
+      </c>
+      <c r="P31" t="str">
+        <v/>
+      </c>
+      <c r="Q31" t="str">
+        <v/>
+      </c>
+      <c r="R31" t="str">
+        <v/>
+      </c>
+      <c r="S31" t="str">
+        <v/>
+      </c>
+      <c r="T31" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>62629255-ec8a-4fa1-b2dd-ecaf9f714379</v>
+      </c>
+      <c r="B32" t="str">
+        <v>DL / HS</v>
+      </c>
+      <c r="C32" t="str">
+        <v/>
+      </c>
+      <c r="D32" t="str">
+        <v>Hannah</v>
+      </c>
+      <c r="E32" t="str">
+        <v>DL</v>
+      </c>
+      <c r="F32" t="str">
+        <v>2026-08-10T08:45:00</v>
+      </c>
+      <c r="G32" t="str">
+        <v>2026-08-10T12:15:00</v>
+      </c>
+      <c r="H32" t="str">
+        <v>FALSE</v>
+      </c>
+      <c r="I32" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="J32" t="str">
+        <v>client-session</v>
+      </c>
+      <c r="K32" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="L32" t="str">
+        <v>custom</v>
+      </c>
+      <c r="M32" t="str">
+        <v>f62a31a0-1e5f-4f5c-a292-a1fcf8d4ec0d</v>
+      </c>
+      <c r="N32" t="str">
+        <v>scheduled</v>
+      </c>
+      <c r="O32" t="str">
+        <v/>
+      </c>
+      <c r="P32" t="str">
+        <v/>
+      </c>
+      <c r="Q32" t="str">
+        <v/>
+      </c>
+      <c r="R32" t="str">
+        <v/>
+      </c>
+      <c r="S32" t="str">
+        <v/>
+      </c>
+      <c r="T32" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>2aa6b091-af77-4dcf-bf8d-d51a6a76f657</v>
+      </c>
+      <c r="B33" t="str">
+        <v>DL / HS</v>
+      </c>
+      <c r="C33" t="str">
+        <v/>
+      </c>
+      <c r="D33" t="str">
+        <v>Hannah</v>
+      </c>
+      <c r="E33" t="str">
+        <v>DL</v>
+      </c>
+      <c r="F33" t="str">
+        <v>2026-08-12T08:45:00</v>
+      </c>
+      <c r="G33" t="str">
+        <v>2026-08-12T12:15:00</v>
+      </c>
+      <c r="H33" t="str">
+        <v>FALSE</v>
+      </c>
+      <c r="I33" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="J33" t="str">
+        <v>client-session</v>
+      </c>
+      <c r="K33" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="L33" t="str">
+        <v>custom</v>
+      </c>
+      <c r="M33" t="str">
+        <v>f62a31a0-1e5f-4f5c-a292-a1fcf8d4ec0d</v>
+      </c>
+      <c r="N33" t="str">
+        <v>scheduled</v>
+      </c>
+      <c r="O33" t="str">
+        <v/>
+      </c>
+      <c r="P33" t="str">
+        <v/>
+      </c>
+      <c r="Q33" t="str">
+        <v/>
+      </c>
+      <c r="R33" t="str">
+        <v/>
+      </c>
+      <c r="S33" t="str">
+        <v/>
+      </c>
+      <c r="T33" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:T33"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/public-assets/sample_schedule.xlsx
+++ b/public-assets/sample_schedule.xlsx
@@ -9,11 +9,18 @@
     <sheet name="Availability" sheetId="4" r:id="rId4"/>
     <sheet name="Assignments" sheetId="5" r:id="rId5"/>
     <sheet name="Settings" sheetId="6" r:id="rId6"/>
-    <sheet name="Appointments" sheetId="7" r:id="rId7"/>
-    <sheet name="Cancellations" sheetId="8" r:id="rId8"/>
-    <sheet name="Blackouts" sheetId="9" r:id="rId9"/>
-    <sheet name="Authorizations" sheetId="10" r:id="rId10"/>
-    <sheet name="ManualUsage" sheetId="11" r:id="rId11"/>
+    <sheet name="CityCenters" sheetId="7" r:id="rId7"/>
+    <sheet name="TravelTimes" sheetId="8" r:id="rId8"/>
+    <sheet name="Appointments" sheetId="9" r:id="rId9"/>
+    <sheet name="Cancellations" sheetId="10" r:id="rId10"/>
+    <sheet name="CancellationCodes" sheetId="11" r:id="rId11"/>
+    <sheet name="Blackouts" sheetId="12" r:id="rId12"/>
+    <sheet name="Holidays" sheetId="13" r:id="rId13"/>
+    <sheet name="TimeOff" sheetId="14" r:id="rId14"/>
+    <sheet name="PtoAccruals" sheetId="15" r:id="rId15"/>
+    <sheet name="PtoOpeningBalances" sheetId="16" r:id="rId16"/>
+    <sheet name="Authorizations" sheetId="17" r:id="rId17"/>
+    <sheet name="ManualUsage" sheetId="18" r:id="rId18"/>
   </sheets>
 </workbook>
 </file>
@@ -437,7 +444,7 @@
         <v>2026-06-13T19:13:46.679Z</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-06-13T19:14:16.808Z</v>
+        <v>2026-07-06T21:53:38.828Z</v>
       </c>
       <c r="E2" t="str">
         <v>aba-dashboard</v>
@@ -452,6 +459,232 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:G1"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>appointmentId</v>
+      </c>
+      <c r="B1" t="str">
+        <v>source</v>
+      </c>
+      <c r="C1" t="str">
+        <v>reason</v>
+      </c>
+      <c r="D1" t="str">
+        <v>unplanned</v>
+      </c>
+      <c r="E1" t="str">
+        <v>noticeMet</v>
+      </c>
+      <c r="F1" t="str">
+        <v>canceledAt</v>
+      </c>
+      <c r="G1" t="str">
+        <v>notes</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:G1"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C1"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>value</v>
+      </c>
+      <c r="B1" t="str">
+        <v>label</v>
+      </c>
+      <c r="C1" t="str">
+        <v>retired</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C1"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:G1"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>id</v>
+      </c>
+      <c r="B1" t="str">
+        <v>entityType</v>
+      </c>
+      <c r="C1" t="str">
+        <v>entityId</v>
+      </c>
+      <c r="D1" t="str">
+        <v>entityName</v>
+      </c>
+      <c r="E1" t="str">
+        <v>date</v>
+      </c>
+      <c r="F1" t="str">
+        <v>reason</v>
+      </c>
+      <c r="G1" t="str">
+        <v>createdAt</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:G1"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:D1"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>id</v>
+      </c>
+      <c r="B1" t="str">
+        <v>date</v>
+      </c>
+      <c r="C1" t="str">
+        <v>name</v>
+      </c>
+      <c r="D1" t="str">
+        <v>createdAt</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:D1"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F1"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>id</v>
+      </c>
+      <c r="B1" t="str">
+        <v>date</v>
+      </c>
+      <c r="C1" t="str">
+        <v>hours</v>
+      </c>
+      <c r="D1" t="str">
+        <v>bucket</v>
+      </c>
+      <c r="E1" t="str">
+        <v>note</v>
+      </c>
+      <c r="F1" t="str">
+        <v>createdAt</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:F1"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:O1"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>id</v>
+      </c>
+      <c r="B1" t="str">
+        <v>kind</v>
+      </c>
+      <c r="C1" t="str">
+        <v>bucket</v>
+      </c>
+      <c r="D1" t="str">
+        <v>hours</v>
+      </c>
+      <c r="E1" t="str">
+        <v>everyWeeks</v>
+      </c>
+      <c r="F1" t="str">
+        <v>weekday</v>
+      </c>
+      <c r="G1" t="str">
+        <v>anchor</v>
+      </c>
+      <c r="H1" t="str">
+        <v>perHours</v>
+      </c>
+      <c r="I1" t="str">
+        <v>bonusHours</v>
+      </c>
+      <c r="J1" t="str">
+        <v>bonusInterval</v>
+      </c>
+      <c r="K1" t="str">
+        <v>bonusConsecutiveIntervals</v>
+      </c>
+      <c r="L1" t="str">
+        <v>bonusCriterion</v>
+      </c>
+      <c r="M1" t="str">
+        <v>bonusPerExtraHours</v>
+      </c>
+      <c r="N1" t="str">
+        <v>bonusPercentAboveGoal</v>
+      </c>
+      <c r="O1" t="str">
+        <v>enabled</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:O1"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C1"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>bucket</v>
+      </c>
+      <c r="B1" t="str">
+        <v>hours</v>
+      </c>
+      <c r="C1" t="str">
+        <v>asOf</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C1"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:P1"/>
   <sheetData>
     <row r="1">
@@ -511,7 +744,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:F1"/>
   <sheetData>
@@ -544,7 +777,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J13"/>
+  <dimension ref="A1:L13"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -577,6 +810,12 @@
       <c r="J1" t="str">
         <v>notes</v>
       </c>
+      <c r="K1" t="str">
+        <v>supervisionIdealPct</v>
+      </c>
+      <c r="L1" t="str">
+        <v>city</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
@@ -609,6 +848,12 @@
       <c r="J2" t="str">
         <v/>
       </c>
+      <c r="K2" t="str">
+        <v/>
+      </c>
+      <c r="L2" t="str">
+        <v>Springfield, IL</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
@@ -641,6 +886,12 @@
       <c r="J3" t="str">
         <v/>
       </c>
+      <c r="K3" t="str">
+        <v/>
+      </c>
+      <c r="L3" t="str">
+        <v>Springfield, IL</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
@@ -673,6 +924,12 @@
       <c r="J4" t="str">
         <v/>
       </c>
+      <c r="K4" t="str">
+        <v/>
+      </c>
+      <c r="L4" t="str">
+        <v>Springfield, IL</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
@@ -705,6 +962,12 @@
       <c r="J5" t="str">
         <v/>
       </c>
+      <c r="K5" t="str">
+        <v/>
+      </c>
+      <c r="L5" t="str">
+        <v>Shelbyville, IL</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
@@ -737,6 +1000,12 @@
       <c r="J6" t="str">
         <v/>
       </c>
+      <c r="K6" t="str">
+        <v/>
+      </c>
+      <c r="L6" t="str">
+        <v>Springfield, IL</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
@@ -769,6 +1038,12 @@
       <c r="J7" t="str">
         <v/>
       </c>
+      <c r="K7" t="str">
+        <v/>
+      </c>
+      <c r="L7" t="str">
+        <v>Springfield, IL</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
@@ -801,6 +1076,12 @@
       <c r="J8" t="str">
         <v/>
       </c>
+      <c r="K8" t="str">
+        <v/>
+      </c>
+      <c r="L8" t="str">
+        <v>Springfield, IL</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
@@ -833,6 +1114,12 @@
       <c r="J9" t="str">
         <v/>
       </c>
+      <c r="K9" t="str">
+        <v/>
+      </c>
+      <c r="L9" t="str">
+        <v>Shelbyville, IL</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
@@ -865,6 +1152,12 @@
       <c r="J10" t="str">
         <v/>
       </c>
+      <c r="K10" t="str">
+        <v/>
+      </c>
+      <c r="L10" t="str">
+        <v>Springfield, IL</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
@@ -897,6 +1190,12 @@
       <c r="J11" t="str">
         <v/>
       </c>
+      <c r="K11" t="str">
+        <v/>
+      </c>
+      <c r="L11" t="str">
+        <v>Springfield, IL</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
@@ -929,6 +1228,12 @@
       <c r="J12" t="str">
         <v/>
       </c>
+      <c r="K12" t="str">
+        <v/>
+      </c>
+      <c r="L12" t="str">
+        <v>Springfield, IL</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
@@ -961,17 +1266,23 @@
       <c r="J13" t="str">
         <v/>
       </c>
+      <c r="K13" t="str">
+        <v/>
+      </c>
+      <c r="L13" t="str">
+        <v>Shelbyville, IL</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J13"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L13"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:E9"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -984,6 +1295,9 @@
         <v>isRBT</v>
       </c>
       <c r="D1" t="str">
+        <v>isFieldworkSupervisee</v>
+      </c>
+      <c r="E1" t="str">
         <v>notes</v>
       </c>
     </row>
@@ -1000,6 +1314,9 @@
       <c r="D2" t="str">
         <v/>
       </c>
+      <c r="E2" t="str">
+        <v/>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
@@ -1014,6 +1331,9 @@
       <c r="D3" t="str">
         <v/>
       </c>
+      <c r="E3" t="str">
+        <v/>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
@@ -1028,6 +1348,9 @@
       <c r="D4" t="str">
         <v/>
       </c>
+      <c r="E4" t="str">
+        <v/>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
@@ -1042,6 +1365,9 @@
       <c r="D5" t="str">
         <v/>
       </c>
+      <c r="E5" t="str">
+        <v/>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
@@ -1056,6 +1382,9 @@
       <c r="D6" t="str">
         <v/>
       </c>
+      <c r="E6" t="str">
+        <v/>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
@@ -1070,6 +1399,9 @@
       <c r="D7" t="str">
         <v/>
       </c>
+      <c r="E7" t="str">
+        <v/>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
@@ -1084,6 +1416,9 @@
       <c r="D8" t="str">
         <v/>
       </c>
+      <c r="E8" t="str">
+        <v/>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
@@ -1098,10 +1433,13 @@
       <c r="D9" t="str">
         <v/>
       </c>
+      <c r="E9" t="str">
+        <v/>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D9"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E9"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -3499,7 +3837,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:G10"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -3520,6 +3858,9 @@
       <c r="F1" t="str">
         <v>billable</v>
       </c>
+      <c r="G1" t="str">
+        <v>availability</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
@@ -3540,6 +3881,9 @@
       <c r="F2" t="str">
         <v>TRUE</v>
       </c>
+      <c r="G2" t="str">
+        <v/>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
@@ -3560,6 +3904,9 @@
       <c r="F3" t="str">
         <v>TRUE</v>
       </c>
+      <c r="G3" t="str">
+        <v/>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
@@ -3580,6 +3927,9 @@
       <c r="F4" t="str">
         <v>TRUE</v>
       </c>
+      <c r="G4" t="str">
+        <v/>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
@@ -3600,6 +3950,9 @@
       <c r="F5" t="str">
         <v>TRUE</v>
       </c>
+      <c r="G5" t="str">
+        <v/>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
@@ -3620,6 +3973,9 @@
       <c r="F6" t="str">
         <v>TRUE</v>
       </c>
+      <c r="G6" t="str">
+        <v/>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
@@ -3640,6 +3996,9 @@
       <c r="F7" t="str">
         <v>TRUE</v>
       </c>
+      <c r="G7" t="str">
+        <v/>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
@@ -3660,6 +4019,9 @@
       <c r="F8" t="str">
         <v>TRUE</v>
       </c>
+      <c r="G8" t="str">
+        <v/>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
@@ -3680,6 +4042,9 @@
       <c r="F9" t="str">
         <v>TRUE</v>
       </c>
+      <c r="G9" t="str">
+        <v/>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
@@ -3700,17 +4065,20 @@
       <c r="F10" t="str">
         <v>TRUE</v>
       </c>
+      <c r="G10" t="str">
+        <v/>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F10"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G10"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:W2"/>
+  <dimension ref="A1:AS2"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -3738,49 +4106,115 @@
         <v>rbtMinContactsPerMonth</v>
       </c>
       <c r="I1" t="str">
+        <v>techMinContactsPerMonth</v>
+      </c>
+      <c r="J1" t="str">
+        <v>contactsMustOccurOnSeparateDays</v>
+      </c>
+      <c r="K1" t="str">
         <v>parentTrainingMinimum</v>
       </c>
-      <c r="J1" t="str">
+      <c r="L1" t="str">
         <v>parentTrainingTargetMin</v>
       </c>
-      <c r="K1" t="str">
+      <c r="M1" t="str">
         <v>parentTrainingTargetMax</v>
       </c>
-      <c r="L1" t="str">
+      <c r="N1" t="str">
         <v>parentTrainingPeriodUnit</v>
       </c>
-      <c r="M1" t="str">
+      <c r="O1" t="str">
         <v>bcbaWeeklyBillableHours</v>
       </c>
-      <c r="N1" t="str">
+      <c r="P1" t="str">
         <v>btWeeklyDirectHours</v>
       </c>
-      <c r="O1" t="str">
+      <c r="Q1" t="str">
         <v>bcbaMonthlyBillableHours</v>
       </c>
-      <c r="P1" t="str">
+      <c r="R1" t="str">
         <v>bcbaMonthlyBillableHours5Week</v>
       </c>
-      <c r="Q1" t="str">
+      <c r="S1" t="str">
         <v>bcbaWeeklyBillableMin</v>
       </c>
-      <c r="R1" t="str">
+      <c r="T1" t="str">
         <v>cancellationUnplannedHoursThreshold</v>
       </c>
-      <c r="S1" t="str">
+      <c r="U1" t="str">
         <v>cancellationPlannedDaysThreshold</v>
       </c>
-      <c r="T1" t="str">
+      <c r="V1" t="str">
         <v>reportDraftLeadValue</v>
       </c>
-      <c r="U1" t="str">
+      <c r="W1" t="str">
         <v>reportDraftLeadUnit</v>
       </c>
-      <c r="V1" t="str">
+      <c r="X1" t="str">
         <v>reportFinalLeadValue</v>
       </c>
-      <c r="W1" t="str">
+      <c r="Y1" t="str">
         <v>reportFinalLeadUnit</v>
+      </c>
+      <c r="Z1" t="str">
+        <v>ptoBillableDeductionRatio</v>
+      </c>
+      <c r="AA1" t="str">
+        <v>ptoMode</v>
+      </c>
+      <c r="AB1" t="str">
+        <v>ptoBuckets</v>
+      </c>
+      <c r="AC1" t="str">
+        <v>ptoUnpaidEnabled</v>
+      </c>
+      <c r="AD1" t="str">
+        <v>bcbaSupervisionPctOfDirect</v>
+      </c>
+      <c r="AE1" t="str">
+        <v>bcbaReassessmentHours</v>
+      </c>
+      <c r="AF1" t="str">
+        <v>bcbaCasePlanningHours</v>
+      </c>
+      <c r="AG1" t="str">
+        <v>bcbaParentTrainingHours</v>
+      </c>
+      <c r="AH1" t="str">
+        <v>bcbaOtherHours</v>
+      </c>
+      <c r="AI1" t="str">
+        <v>homeBaseLabel</v>
+      </c>
+      <c r="AJ1" t="str">
+        <v>homeBaseAddress</v>
+      </c>
+      <c r="AK1" t="str">
+        <v>homeBaseCity</v>
+      </c>
+      <c r="AL1" t="str">
+        <v>homeBaseLat</v>
+      </c>
+      <c r="AM1" t="str">
+        <v>homeBaseLng</v>
+      </c>
+      <c r="AN1" t="str">
+        <v>travelEnabled</v>
+      </c>
+      <c r="AO1" t="str">
+        <v>travelWithinCityMin</v>
+      </c>
+      <c r="AP1" t="str">
+        <v>travelPadPercent</v>
+      </c>
+      <c r="AQ1" t="str">
+        <v>travelAvgSpeedMph</v>
+      </c>
+      <c r="AR1" t="str">
+        <v>travelDefaultUnknownMin</v>
+      </c>
+      <c r="AS1" t="str">
+        <v>travelHourBucketSize</v>
       </c>
     </row>
     <row r="2">
@@ -3808,24 +4242,24 @@
       <c r="H2" t="str">
         <v/>
       </c>
-      <c r="I2">
+      <c r="I2" t="str">
+        <v/>
+      </c>
+      <c r="J2" t="str">
+        <v/>
+      </c>
+      <c r="K2">
         <v>1.5</v>
       </c>
-      <c r="J2">
+      <c r="L2">
         <v>2</v>
       </c>
-      <c r="K2">
+      <c r="M2">
         <v>4</v>
       </c>
-      <c r="L2" t="str">
+      <c r="N2" t="str">
         <v>month</v>
       </c>
-      <c r="M2" t="str">
-        <v/>
-      </c>
-      <c r="N2" t="str">
-        <v/>
-      </c>
       <c r="O2" t="str">
         <v/>
       </c>
@@ -3852,1839 +4286,2725 @@
       </c>
       <c r="W2" t="str">
         <v/>
+      </c>
+      <c r="X2" t="str">
+        <v/>
+      </c>
+      <c r="Y2" t="str">
+        <v/>
+      </c>
+      <c r="Z2" t="str">
+        <v/>
+      </c>
+      <c r="AA2" t="str">
+        <v/>
+      </c>
+      <c r="AB2" t="str">
+        <v/>
+      </c>
+      <c r="AC2" t="str">
+        <v/>
+      </c>
+      <c r="AD2" t="str">
+        <v/>
+      </c>
+      <c r="AE2" t="str">
+        <v/>
+      </c>
+      <c r="AF2" t="str">
+        <v/>
+      </c>
+      <c r="AG2" t="str">
+        <v/>
+      </c>
+      <c r="AH2" t="str">
+        <v/>
+      </c>
+      <c r="AI2" t="str">
+        <v>Home</v>
+      </c>
+      <c r="AJ2" t="str">
+        <v>100 Center St, Springfield, IL</v>
+      </c>
+      <c r="AK2" t="str">
+        <v>Springfield, IL</v>
+      </c>
+      <c r="AL2">
+        <v>39.7817</v>
+      </c>
+      <c r="AM2">
+        <v>-89.6501</v>
+      </c>
+      <c r="AN2" t="str">
+        <v>FALSE</v>
+      </c>
+      <c r="AO2">
+        <v>15</v>
+      </c>
+      <c r="AP2">
+        <v>5</v>
+      </c>
+      <c r="AQ2">
+        <v>30</v>
+      </c>
+      <c r="AR2">
+        <v>45</v>
+      </c>
+      <c r="AS2">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:W2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:AS2"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Q33"/>
+  <dimension ref="A1:C3"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>id</v>
+        <v>city</v>
       </c>
       <c r="B1" t="str">
-        <v>title</v>
+        <v>lat</v>
       </c>
       <c r="C1" t="str">
-        <v>description</v>
-      </c>
-      <c r="D1" t="str">
-        <v>technician</v>
-      </c>
-      <c r="E1" t="str">
-        <v>client</v>
-      </c>
-      <c r="F1" t="str">
-        <v>startTime</v>
-      </c>
-      <c r="G1" t="str">
-        <v>endTime</v>
-      </c>
-      <c r="H1" t="str">
-        <v>isFixed</v>
-      </c>
-      <c r="I1" t="str">
-        <v>isBillable</v>
-      </c>
-      <c r="J1" t="str">
-        <v>type</v>
-      </c>
-      <c r="K1" t="str">
-        <v>isMakeUp</v>
-      </c>
-      <c r="L1" t="str">
-        <v>makeupForId</v>
-      </c>
-      <c r="M1" t="str">
-        <v>isGhost</v>
-      </c>
-      <c r="N1" t="str">
-        <v>isRecurring</v>
-      </c>
-      <c r="O1" t="str">
-        <v>recurringPattern</v>
-      </c>
-      <c r="P1" t="str">
-        <v>seriesId</v>
-      </c>
-      <c r="Q1" t="str">
-        <v>status</v>
+        <v>lng</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>c4f33f78-7510-4ed3-b1b5-7fcf5e342526</v>
-      </c>
-      <c r="B2" t="str">
-        <v>DL / HS</v>
-      </c>
-      <c r="C2" t="str">
-        <v/>
-      </c>
-      <c r="D2" t="str">
-        <v>Hannah</v>
-      </c>
-      <c r="E2" t="str">
-        <v>DL</v>
-      </c>
-      <c r="F2" t="str">
-        <v>2026-06-01T08:45:00</v>
-      </c>
-      <c r="G2" t="str">
-        <v>2026-06-01T12:15:00</v>
-      </c>
-      <c r="H2" t="str">
-        <v>FALSE</v>
-      </c>
-      <c r="I2" t="str">
-        <v>TRUE</v>
-      </c>
-      <c r="J2" t="str">
-        <v>client-session</v>
-      </c>
-      <c r="K2" t="str">
-        <v/>
-      </c>
-      <c r="L2" t="str">
-        <v/>
-      </c>
-      <c r="M2" t="str">
-        <v/>
-      </c>
-      <c r="N2" t="str">
-        <v>TRUE</v>
-      </c>
-      <c r="O2" t="str">
-        <v>custom</v>
-      </c>
-      <c r="P2" t="str">
-        <v>f62a31a0-1e5f-4f5c-a292-a1fcf8d4ec0d</v>
-      </c>
-      <c r="Q2" t="str">
-        <v>scheduled</v>
+        <v>springfield, il</v>
+      </c>
+      <c r="B2">
+        <v>39.7817</v>
+      </c>
+      <c r="C2">
+        <v>-89.6501</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>41f8a519-11f5-4fac-8975-47515199096b</v>
-      </c>
-      <c r="B3" t="str">
-        <v>DL / HS</v>
-      </c>
-      <c r="C3" t="str">
-        <v/>
-      </c>
-      <c r="D3" t="str">
-        <v>Hannah</v>
-      </c>
-      <c r="E3" t="str">
-        <v>DL</v>
-      </c>
-      <c r="F3" t="str">
-        <v>2026-06-03T08:45:00</v>
-      </c>
-      <c r="G3" t="str">
-        <v>2026-06-03T12:15:00</v>
-      </c>
-      <c r="H3" t="str">
-        <v>FALSE</v>
-      </c>
-      <c r="I3" t="str">
-        <v>TRUE</v>
-      </c>
-      <c r="J3" t="str">
-        <v>client-session</v>
-      </c>
-      <c r="K3" t="str">
-        <v/>
-      </c>
-      <c r="L3" t="str">
-        <v/>
-      </c>
-      <c r="M3" t="str">
-        <v/>
-      </c>
-      <c r="N3" t="str">
-        <v>TRUE</v>
-      </c>
-      <c r="O3" t="str">
-        <v>custom</v>
-      </c>
-      <c r="P3" t="str">
-        <v>f62a31a0-1e5f-4f5c-a292-a1fcf8d4ec0d</v>
-      </c>
-      <c r="Q3" t="str">
-        <v>scheduled</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>f03c70a1-92fc-4fa1-a831-f9198d8cee93</v>
-      </c>
-      <c r="B4" t="str">
-        <v>DL / HS</v>
-      </c>
-      <c r="C4" t="str">
-        <v/>
-      </c>
-      <c r="D4" t="str">
-        <v>Hannah</v>
-      </c>
-      <c r="E4" t="str">
-        <v>DL</v>
-      </c>
-      <c r="F4" t="str">
-        <v>2026-06-05T08:45:00</v>
-      </c>
-      <c r="G4" t="str">
-        <v>2026-06-05T12:15:00</v>
-      </c>
-      <c r="H4" t="str">
-        <v>FALSE</v>
-      </c>
-      <c r="I4" t="str">
-        <v>TRUE</v>
-      </c>
-      <c r="J4" t="str">
-        <v>client-session</v>
-      </c>
-      <c r="K4" t="str">
-        <v/>
-      </c>
-      <c r="L4" t="str">
-        <v/>
-      </c>
-      <c r="M4" t="str">
-        <v/>
-      </c>
-      <c r="N4" t="str">
-        <v>TRUE</v>
-      </c>
-      <c r="O4" t="str">
-        <v>custom</v>
-      </c>
-      <c r="P4" t="str">
-        <v>f62a31a0-1e5f-4f5c-a292-a1fcf8d4ec0d</v>
-      </c>
-      <c r="Q4" t="str">
-        <v>scheduled</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>77b7beef-0140-4ce4-9eb6-93d404b0a91f</v>
-      </c>
-      <c r="B5" t="str">
-        <v>DL / HS</v>
-      </c>
-      <c r="C5" t="str">
-        <v/>
-      </c>
-      <c r="D5" t="str">
-        <v>Hannah</v>
-      </c>
-      <c r="E5" t="str">
-        <v>DL</v>
-      </c>
-      <c r="F5" t="str">
-        <v>2026-06-08T08:45:00</v>
-      </c>
-      <c r="G5" t="str">
-        <v>2026-06-08T12:15:00</v>
-      </c>
-      <c r="H5" t="str">
-        <v>FALSE</v>
-      </c>
-      <c r="I5" t="str">
-        <v>TRUE</v>
-      </c>
-      <c r="J5" t="str">
-        <v>client-session</v>
-      </c>
-      <c r="K5" t="str">
-        <v/>
-      </c>
-      <c r="L5" t="str">
-        <v/>
-      </c>
-      <c r="M5" t="str">
-        <v/>
-      </c>
-      <c r="N5" t="str">
-        <v>TRUE</v>
-      </c>
-      <c r="O5" t="str">
-        <v>custom</v>
-      </c>
-      <c r="P5" t="str">
-        <v>f62a31a0-1e5f-4f5c-a292-a1fcf8d4ec0d</v>
-      </c>
-      <c r="Q5" t="str">
-        <v>scheduled</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>f55bcb1f-d846-496f-bc77-2b510087c1f9</v>
-      </c>
-      <c r="B6" t="str">
-        <v>DL / HS</v>
-      </c>
-      <c r="C6" t="str">
-        <v/>
-      </c>
-      <c r="D6" t="str">
-        <v>Hannah</v>
-      </c>
-      <c r="E6" t="str">
-        <v>DL</v>
-      </c>
-      <c r="F6" t="str">
-        <v>2026-06-10T08:45:00</v>
-      </c>
-      <c r="G6" t="str">
-        <v>2026-06-10T12:15:00</v>
-      </c>
-      <c r="H6" t="str">
-        <v>FALSE</v>
-      </c>
-      <c r="I6" t="str">
-        <v>TRUE</v>
-      </c>
-      <c r="J6" t="str">
-        <v>client-session</v>
-      </c>
-      <c r="K6" t="str">
-        <v/>
-      </c>
-      <c r="L6" t="str">
-        <v/>
-      </c>
-      <c r="M6" t="str">
-        <v/>
-      </c>
-      <c r="N6" t="str">
-        <v>TRUE</v>
-      </c>
-      <c r="O6" t="str">
-        <v>custom</v>
-      </c>
-      <c r="P6" t="str">
-        <v>f62a31a0-1e5f-4f5c-a292-a1fcf8d4ec0d</v>
-      </c>
-      <c r="Q6" t="str">
-        <v>scheduled</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>a1a3bbd3-ecca-4bca-802c-88d414dc894e</v>
-      </c>
-      <c r="B7" t="str">
-        <v>DL / HS</v>
-      </c>
-      <c r="C7" t="str">
-        <v/>
-      </c>
-      <c r="D7" t="str">
-        <v>Hannah</v>
-      </c>
-      <c r="E7" t="str">
-        <v>DL</v>
-      </c>
-      <c r="F7" t="str">
-        <v>2026-06-12T08:45:00</v>
-      </c>
-      <c r="G7" t="str">
-        <v>2026-06-12T12:15:00</v>
-      </c>
-      <c r="H7" t="str">
-        <v>FALSE</v>
-      </c>
-      <c r="I7" t="str">
-        <v>TRUE</v>
-      </c>
-      <c r="J7" t="str">
-        <v>client-session</v>
-      </c>
-      <c r="K7" t="str">
-        <v/>
-      </c>
-      <c r="L7" t="str">
-        <v/>
-      </c>
-      <c r="M7" t="str">
-        <v/>
-      </c>
-      <c r="N7" t="str">
-        <v>TRUE</v>
-      </c>
-      <c r="O7" t="str">
-        <v>custom</v>
-      </c>
-      <c r="P7" t="str">
-        <v>f62a31a0-1e5f-4f5c-a292-a1fcf8d4ec0d</v>
-      </c>
-      <c r="Q7" t="str">
-        <v>scheduled</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>11be6d4e-0bdc-4d9a-b1c1-1056f3f09456</v>
-      </c>
-      <c r="B8" t="str">
-        <v>DL / HS</v>
-      </c>
-      <c r="C8" t="str">
-        <v/>
-      </c>
-      <c r="D8" t="str">
-        <v>Hannah</v>
-      </c>
-      <c r="E8" t="str">
-        <v>DL</v>
-      </c>
-      <c r="F8" t="str">
-        <v>2026-06-15T08:45:00</v>
-      </c>
-      <c r="G8" t="str">
-        <v>2026-06-15T12:15:00</v>
-      </c>
-      <c r="H8" t="str">
-        <v>FALSE</v>
-      </c>
-      <c r="I8" t="str">
-        <v>TRUE</v>
-      </c>
-      <c r="J8" t="str">
-        <v>client-session</v>
-      </c>
-      <c r="K8" t="str">
-        <v/>
-      </c>
-      <c r="L8" t="str">
-        <v/>
-      </c>
-      <c r="M8" t="str">
-        <v/>
-      </c>
-      <c r="N8" t="str">
-        <v>TRUE</v>
-      </c>
-      <c r="O8" t="str">
-        <v>custom</v>
-      </c>
-      <c r="P8" t="str">
-        <v>f62a31a0-1e5f-4f5c-a292-a1fcf8d4ec0d</v>
-      </c>
-      <c r="Q8" t="str">
-        <v>scheduled</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>f4951d7b-ed8a-4c01-87e2-3d6fbd88f280</v>
-      </c>
-      <c r="B9" t="str">
-        <v>DL / HS</v>
-      </c>
-      <c r="C9" t="str">
-        <v/>
-      </c>
-      <c r="D9" t="str">
-        <v>Hannah</v>
-      </c>
-      <c r="E9" t="str">
-        <v>DL</v>
-      </c>
-      <c r="F9" t="str">
-        <v>2026-06-17T08:45:00</v>
-      </c>
-      <c r="G9" t="str">
-        <v>2026-06-17T12:15:00</v>
-      </c>
-      <c r="H9" t="str">
-        <v>FALSE</v>
-      </c>
-      <c r="I9" t="str">
-        <v>TRUE</v>
-      </c>
-      <c r="J9" t="str">
-        <v>client-session</v>
-      </c>
-      <c r="K9" t="str">
-        <v/>
-      </c>
-      <c r="L9" t="str">
-        <v/>
-      </c>
-      <c r="M9" t="str">
-        <v/>
-      </c>
-      <c r="N9" t="str">
-        <v>TRUE</v>
-      </c>
-      <c r="O9" t="str">
-        <v>custom</v>
-      </c>
-      <c r="P9" t="str">
-        <v>f62a31a0-1e5f-4f5c-a292-a1fcf8d4ec0d</v>
-      </c>
-      <c r="Q9" t="str">
-        <v>scheduled</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>141718b1-4379-4186-b0c5-4b92f6c13951</v>
-      </c>
-      <c r="B10" t="str">
-        <v>DL / HS</v>
-      </c>
-      <c r="C10" t="str">
-        <v/>
-      </c>
-      <c r="D10" t="str">
-        <v>Hannah</v>
-      </c>
-      <c r="E10" t="str">
-        <v>DL</v>
-      </c>
-      <c r="F10" t="str">
-        <v>2026-06-19T08:45:00</v>
-      </c>
-      <c r="G10" t="str">
-        <v>2026-06-19T12:15:00</v>
-      </c>
-      <c r="H10" t="str">
-        <v>FALSE</v>
-      </c>
-      <c r="I10" t="str">
-        <v>TRUE</v>
-      </c>
-      <c r="J10" t="str">
-        <v>client-session</v>
-      </c>
-      <c r="K10" t="str">
-        <v/>
-      </c>
-      <c r="L10" t="str">
-        <v/>
-      </c>
-      <c r="M10" t="str">
-        <v/>
-      </c>
-      <c r="N10" t="str">
-        <v>TRUE</v>
-      </c>
-      <c r="O10" t="str">
-        <v>custom</v>
-      </c>
-      <c r="P10" t="str">
-        <v>f62a31a0-1e5f-4f5c-a292-a1fcf8d4ec0d</v>
-      </c>
-      <c r="Q10" t="str">
-        <v>scheduled</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>d8ff5fb6-af6f-4a61-84fa-bec4cb27acf2</v>
-      </c>
-      <c r="B11" t="str">
-        <v>DL / HS</v>
-      </c>
-      <c r="C11" t="str">
-        <v/>
-      </c>
-      <c r="D11" t="str">
-        <v>Hannah</v>
-      </c>
-      <c r="E11" t="str">
-        <v>DL</v>
-      </c>
-      <c r="F11" t="str">
-        <v>2026-06-22T08:45:00</v>
-      </c>
-      <c r="G11" t="str">
-        <v>2026-06-22T12:15:00</v>
-      </c>
-      <c r="H11" t="str">
-        <v>FALSE</v>
-      </c>
-      <c r="I11" t="str">
-        <v>TRUE</v>
-      </c>
-      <c r="J11" t="str">
-        <v>client-session</v>
-      </c>
-      <c r="K11" t="str">
-        <v/>
-      </c>
-      <c r="L11" t="str">
-        <v/>
-      </c>
-      <c r="M11" t="str">
-        <v/>
-      </c>
-      <c r="N11" t="str">
-        <v>TRUE</v>
-      </c>
-      <c r="O11" t="str">
-        <v>custom</v>
-      </c>
-      <c r="P11" t="str">
-        <v>f62a31a0-1e5f-4f5c-a292-a1fcf8d4ec0d</v>
-      </c>
-      <c r="Q11" t="str">
-        <v>scheduled</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>ce6bbbba-4bfe-4b56-8138-be0a8edfa3a4</v>
-      </c>
-      <c r="B12" t="str">
-        <v>DL / HS</v>
-      </c>
-      <c r="C12" t="str">
-        <v/>
-      </c>
-      <c r="D12" t="str">
-        <v>Hannah</v>
-      </c>
-      <c r="E12" t="str">
-        <v>DL</v>
-      </c>
-      <c r="F12" t="str">
-        <v>2026-06-24T08:45:00</v>
-      </c>
-      <c r="G12" t="str">
-        <v>2026-06-24T12:15:00</v>
-      </c>
-      <c r="H12" t="str">
-        <v>FALSE</v>
-      </c>
-      <c r="I12" t="str">
-        <v>TRUE</v>
-      </c>
-      <c r="J12" t="str">
-        <v>client-session</v>
-      </c>
-      <c r="K12" t="str">
-        <v/>
-      </c>
-      <c r="L12" t="str">
-        <v/>
-      </c>
-      <c r="M12" t="str">
-        <v/>
-      </c>
-      <c r="N12" t="str">
-        <v>TRUE</v>
-      </c>
-      <c r="O12" t="str">
-        <v>custom</v>
-      </c>
-      <c r="P12" t="str">
-        <v>f62a31a0-1e5f-4f5c-a292-a1fcf8d4ec0d</v>
-      </c>
-      <c r="Q12" t="str">
-        <v>scheduled</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>4b6c6613-29a1-40aa-886b-71c18bfa9de0</v>
-      </c>
-      <c r="B13" t="str">
-        <v>DL / HS</v>
-      </c>
-      <c r="C13" t="str">
-        <v/>
-      </c>
-      <c r="D13" t="str">
-        <v>Hannah</v>
-      </c>
-      <c r="E13" t="str">
-        <v>DL</v>
-      </c>
-      <c r="F13" t="str">
-        <v>2026-06-26T08:45:00</v>
-      </c>
-      <c r="G13" t="str">
-        <v>2026-06-26T12:15:00</v>
-      </c>
-      <c r="H13" t="str">
-        <v>FALSE</v>
-      </c>
-      <c r="I13" t="str">
-        <v>TRUE</v>
-      </c>
-      <c r="J13" t="str">
-        <v>client-session</v>
-      </c>
-      <c r="K13" t="str">
-        <v/>
-      </c>
-      <c r="L13" t="str">
-        <v/>
-      </c>
-      <c r="M13" t="str">
-        <v/>
-      </c>
-      <c r="N13" t="str">
-        <v>TRUE</v>
-      </c>
-      <c r="O13" t="str">
-        <v>custom</v>
-      </c>
-      <c r="P13" t="str">
-        <v>f62a31a0-1e5f-4f5c-a292-a1fcf8d4ec0d</v>
-      </c>
-      <c r="Q13" t="str">
-        <v>scheduled</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>c5a04a2f-a163-4c4f-8d72-51448349161c</v>
-      </c>
-      <c r="B14" t="str">
-        <v>DL / HS</v>
-      </c>
-      <c r="C14" t="str">
-        <v/>
-      </c>
-      <c r="D14" t="str">
-        <v>Hannah</v>
-      </c>
-      <c r="E14" t="str">
-        <v>DL</v>
-      </c>
-      <c r="F14" t="str">
-        <v>2026-06-29T08:45:00</v>
-      </c>
-      <c r="G14" t="str">
-        <v>2026-06-29T12:15:00</v>
-      </c>
-      <c r="H14" t="str">
-        <v>FALSE</v>
-      </c>
-      <c r="I14" t="str">
-        <v>TRUE</v>
-      </c>
-      <c r="J14" t="str">
-        <v>client-session</v>
-      </c>
-      <c r="K14" t="str">
-        <v/>
-      </c>
-      <c r="L14" t="str">
-        <v/>
-      </c>
-      <c r="M14" t="str">
-        <v/>
-      </c>
-      <c r="N14" t="str">
-        <v>TRUE</v>
-      </c>
-      <c r="O14" t="str">
-        <v>custom</v>
-      </c>
-      <c r="P14" t="str">
-        <v>f62a31a0-1e5f-4f5c-a292-a1fcf8d4ec0d</v>
-      </c>
-      <c r="Q14" t="str">
-        <v>scheduled</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>397d65f8-05bd-43b5-9403-ea9ea4519028</v>
-      </c>
-      <c r="B15" t="str">
-        <v>DL / HS</v>
-      </c>
-      <c r="C15" t="str">
-        <v/>
-      </c>
-      <c r="D15" t="str">
-        <v>Hannah</v>
-      </c>
-      <c r="E15" t="str">
-        <v>DL</v>
-      </c>
-      <c r="F15" t="str">
-        <v>2026-07-01T08:45:00</v>
-      </c>
-      <c r="G15" t="str">
-        <v>2026-07-01T12:15:00</v>
-      </c>
-      <c r="H15" t="str">
-        <v>FALSE</v>
-      </c>
-      <c r="I15" t="str">
-        <v>TRUE</v>
-      </c>
-      <c r="J15" t="str">
-        <v>client-session</v>
-      </c>
-      <c r="K15" t="str">
-        <v/>
-      </c>
-      <c r="L15" t="str">
-        <v/>
-      </c>
-      <c r="M15" t="str">
-        <v/>
-      </c>
-      <c r="N15" t="str">
-        <v>TRUE</v>
-      </c>
-      <c r="O15" t="str">
-        <v>custom</v>
-      </c>
-      <c r="P15" t="str">
-        <v>f62a31a0-1e5f-4f5c-a292-a1fcf8d4ec0d</v>
-      </c>
-      <c r="Q15" t="str">
-        <v>scheduled</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>763a236c-0f48-4bbf-9c26-f42b9e1f3b23</v>
-      </c>
-      <c r="B16" t="str">
-        <v>DL / HS</v>
-      </c>
-      <c r="C16" t="str">
-        <v/>
-      </c>
-      <c r="D16" t="str">
-        <v>Hannah</v>
-      </c>
-      <c r="E16" t="str">
-        <v>DL</v>
-      </c>
-      <c r="F16" t="str">
-        <v>2026-07-03T08:45:00</v>
-      </c>
-      <c r="G16" t="str">
-        <v>2026-07-03T12:15:00</v>
-      </c>
-      <c r="H16" t="str">
-        <v>FALSE</v>
-      </c>
-      <c r="I16" t="str">
-        <v>TRUE</v>
-      </c>
-      <c r="J16" t="str">
-        <v>client-session</v>
-      </c>
-      <c r="K16" t="str">
-        <v/>
-      </c>
-      <c r="L16" t="str">
-        <v/>
-      </c>
-      <c r="M16" t="str">
-        <v/>
-      </c>
-      <c r="N16" t="str">
-        <v>TRUE</v>
-      </c>
-      <c r="O16" t="str">
-        <v>custom</v>
-      </c>
-      <c r="P16" t="str">
-        <v>f62a31a0-1e5f-4f5c-a292-a1fcf8d4ec0d</v>
-      </c>
-      <c r="Q16" t="str">
-        <v>scheduled</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="str">
-        <v>2c1e8a34-9559-4004-976d-8aeba9aaf8e4</v>
-      </c>
-      <c r="B17" t="str">
-        <v>DL / HS</v>
-      </c>
-      <c r="C17" t="str">
-        <v/>
-      </c>
-      <c r="D17" t="str">
-        <v>Hannah</v>
-      </c>
-      <c r="E17" t="str">
-        <v>DL</v>
-      </c>
-      <c r="F17" t="str">
-        <v>2026-07-06T08:45:00</v>
-      </c>
-      <c r="G17" t="str">
-        <v>2026-07-06T12:15:00</v>
-      </c>
-      <c r="H17" t="str">
-        <v>FALSE</v>
-      </c>
-      <c r="I17" t="str">
-        <v>TRUE</v>
-      </c>
-      <c r="J17" t="str">
-        <v>client-session</v>
-      </c>
-      <c r="K17" t="str">
-        <v/>
-      </c>
-      <c r="L17" t="str">
-        <v/>
-      </c>
-      <c r="M17" t="str">
-        <v/>
-      </c>
-      <c r="N17" t="str">
-        <v>TRUE</v>
-      </c>
-      <c r="O17" t="str">
-        <v>custom</v>
-      </c>
-      <c r="P17" t="str">
-        <v>f62a31a0-1e5f-4f5c-a292-a1fcf8d4ec0d</v>
-      </c>
-      <c r="Q17" t="str">
-        <v>scheduled</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="str">
-        <v>9928eeed-a398-4dd5-bd6b-dc8c4da1b8d7</v>
-      </c>
-      <c r="B18" t="str">
-        <v>DL / HS</v>
-      </c>
-      <c r="C18" t="str">
-        <v/>
-      </c>
-      <c r="D18" t="str">
-        <v>Hannah</v>
-      </c>
-      <c r="E18" t="str">
-        <v>DL</v>
-      </c>
-      <c r="F18" t="str">
-        <v>2026-07-08T08:45:00</v>
-      </c>
-      <c r="G18" t="str">
-        <v>2026-07-08T12:15:00</v>
-      </c>
-      <c r="H18" t="str">
-        <v>FALSE</v>
-      </c>
-      <c r="I18" t="str">
-        <v>TRUE</v>
-      </c>
-      <c r="J18" t="str">
-        <v>client-session</v>
-      </c>
-      <c r="K18" t="str">
-        <v/>
-      </c>
-      <c r="L18" t="str">
-        <v/>
-      </c>
-      <c r="M18" t="str">
-        <v/>
-      </c>
-      <c r="N18" t="str">
-        <v>TRUE</v>
-      </c>
-      <c r="O18" t="str">
-        <v>custom</v>
-      </c>
-      <c r="P18" t="str">
-        <v>f62a31a0-1e5f-4f5c-a292-a1fcf8d4ec0d</v>
-      </c>
-      <c r="Q18" t="str">
-        <v>scheduled</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="str">
-        <v>dec17796-748f-4b82-ac9c-4c565cc0be8f</v>
-      </c>
-      <c r="B19" t="str">
-        <v>DL / HS</v>
-      </c>
-      <c r="C19" t="str">
-        <v/>
-      </c>
-      <c r="D19" t="str">
-        <v>Hannah</v>
-      </c>
-      <c r="E19" t="str">
-        <v>DL</v>
-      </c>
-      <c r="F19" t="str">
-        <v>2026-07-10T08:45:00</v>
-      </c>
-      <c r="G19" t="str">
-        <v>2026-07-10T12:15:00</v>
-      </c>
-      <c r="H19" t="str">
-        <v>FALSE</v>
-      </c>
-      <c r="I19" t="str">
-        <v>TRUE</v>
-      </c>
-      <c r="J19" t="str">
-        <v>client-session</v>
-      </c>
-      <c r="K19" t="str">
-        <v/>
-      </c>
-      <c r="L19" t="str">
-        <v/>
-      </c>
-      <c r="M19" t="str">
-        <v/>
-      </c>
-      <c r="N19" t="str">
-        <v>TRUE</v>
-      </c>
-      <c r="O19" t="str">
-        <v>custom</v>
-      </c>
-      <c r="P19" t="str">
-        <v>f62a31a0-1e5f-4f5c-a292-a1fcf8d4ec0d</v>
-      </c>
-      <c r="Q19" t="str">
-        <v>scheduled</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="str">
-        <v>66ae4829-2942-4346-bd53-7743ae3da44e</v>
-      </c>
-      <c r="B20" t="str">
-        <v>DL / HS</v>
-      </c>
-      <c r="C20" t="str">
-        <v/>
-      </c>
-      <c r="D20" t="str">
-        <v>Hannah</v>
-      </c>
-      <c r="E20" t="str">
-        <v>DL</v>
-      </c>
-      <c r="F20" t="str">
-        <v>2026-07-13T08:45:00</v>
-      </c>
-      <c r="G20" t="str">
-        <v>2026-07-13T12:15:00</v>
-      </c>
-      <c r="H20" t="str">
-        <v>FALSE</v>
-      </c>
-      <c r="I20" t="str">
-        <v>TRUE</v>
-      </c>
-      <c r="J20" t="str">
-        <v>client-session</v>
-      </c>
-      <c r="K20" t="str">
-        <v/>
-      </c>
-      <c r="L20" t="str">
-        <v/>
-      </c>
-      <c r="M20" t="str">
-        <v/>
-      </c>
-      <c r="N20" t="str">
-        <v>TRUE</v>
-      </c>
-      <c r="O20" t="str">
-        <v>custom</v>
-      </c>
-      <c r="P20" t="str">
-        <v>f62a31a0-1e5f-4f5c-a292-a1fcf8d4ec0d</v>
-      </c>
-      <c r="Q20" t="str">
-        <v>scheduled</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="str">
-        <v>ebf3754c-44c2-4d2b-aab5-eadbef962a67</v>
-      </c>
-      <c r="B21" t="str">
-        <v>DL / HS</v>
-      </c>
-      <c r="C21" t="str">
-        <v/>
-      </c>
-      <c r="D21" t="str">
-        <v>Hannah</v>
-      </c>
-      <c r="E21" t="str">
-        <v>DL</v>
-      </c>
-      <c r="F21" t="str">
-        <v>2026-07-15T08:45:00</v>
-      </c>
-      <c r="G21" t="str">
-        <v>2026-07-15T12:15:00</v>
-      </c>
-      <c r="H21" t="str">
-        <v>FALSE</v>
-      </c>
-      <c r="I21" t="str">
-        <v>TRUE</v>
-      </c>
-      <c r="J21" t="str">
-        <v>client-session</v>
-      </c>
-      <c r="K21" t="str">
-        <v/>
-      </c>
-      <c r="L21" t="str">
-        <v/>
-      </c>
-      <c r="M21" t="str">
-        <v/>
-      </c>
-      <c r="N21" t="str">
-        <v>TRUE</v>
-      </c>
-      <c r="O21" t="str">
-        <v>custom</v>
-      </c>
-      <c r="P21" t="str">
-        <v>f62a31a0-1e5f-4f5c-a292-a1fcf8d4ec0d</v>
-      </c>
-      <c r="Q21" t="str">
-        <v>scheduled</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="str">
-        <v>fab364e2-81a5-494f-a73f-82173d7d407a</v>
-      </c>
-      <c r="B22" t="str">
-        <v>DL / HS</v>
-      </c>
-      <c r="C22" t="str">
-        <v/>
-      </c>
-      <c r="D22" t="str">
-        <v>Hannah</v>
-      </c>
-      <c r="E22" t="str">
-        <v>DL</v>
-      </c>
-      <c r="F22" t="str">
-        <v>2026-07-17T08:45:00</v>
-      </c>
-      <c r="G22" t="str">
-        <v>2026-07-17T12:15:00</v>
-      </c>
-      <c r="H22" t="str">
-        <v>FALSE</v>
-      </c>
-      <c r="I22" t="str">
-        <v>TRUE</v>
-      </c>
-      <c r="J22" t="str">
-        <v>client-session</v>
-      </c>
-      <c r="K22" t="str">
-        <v/>
-      </c>
-      <c r="L22" t="str">
-        <v/>
-      </c>
-      <c r="M22" t="str">
-        <v/>
-      </c>
-      <c r="N22" t="str">
-        <v>TRUE</v>
-      </c>
-      <c r="O22" t="str">
-        <v>custom</v>
-      </c>
-      <c r="P22" t="str">
-        <v>f62a31a0-1e5f-4f5c-a292-a1fcf8d4ec0d</v>
-      </c>
-      <c r="Q22" t="str">
-        <v>scheduled</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="str">
-        <v>c06260b9-f5c8-4c57-ab35-dd870b39048f</v>
-      </c>
-      <c r="B23" t="str">
-        <v>DL / HS</v>
-      </c>
-      <c r="C23" t="str">
-        <v/>
-      </c>
-      <c r="D23" t="str">
-        <v>Hannah</v>
-      </c>
-      <c r="E23" t="str">
-        <v>DL</v>
-      </c>
-      <c r="F23" t="str">
-        <v>2026-07-20T08:45:00</v>
-      </c>
-      <c r="G23" t="str">
-        <v>2026-07-20T12:15:00</v>
-      </c>
-      <c r="H23" t="str">
-        <v>FALSE</v>
-      </c>
-      <c r="I23" t="str">
-        <v>TRUE</v>
-      </c>
-      <c r="J23" t="str">
-        <v>client-session</v>
-      </c>
-      <c r="K23" t="str">
-        <v/>
-      </c>
-      <c r="L23" t="str">
-        <v/>
-      </c>
-      <c r="M23" t="str">
-        <v/>
-      </c>
-      <c r="N23" t="str">
-        <v>TRUE</v>
-      </c>
-      <c r="O23" t="str">
-        <v>custom</v>
-      </c>
-      <c r="P23" t="str">
-        <v>f62a31a0-1e5f-4f5c-a292-a1fcf8d4ec0d</v>
-      </c>
-      <c r="Q23" t="str">
-        <v>scheduled</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="str">
-        <v>555eefc4-7dc5-4a30-b4d5-443e12f62443</v>
-      </c>
-      <c r="B24" t="str">
-        <v>DL / HS</v>
-      </c>
-      <c r="C24" t="str">
-        <v/>
-      </c>
-      <c r="D24" t="str">
-        <v>Hannah</v>
-      </c>
-      <c r="E24" t="str">
-        <v>DL</v>
-      </c>
-      <c r="F24" t="str">
-        <v>2026-07-22T08:45:00</v>
-      </c>
-      <c r="G24" t="str">
-        <v>2026-07-22T12:15:00</v>
-      </c>
-      <c r="H24" t="str">
-        <v>FALSE</v>
-      </c>
-      <c r="I24" t="str">
-        <v>TRUE</v>
-      </c>
-      <c r="J24" t="str">
-        <v>client-session</v>
-      </c>
-      <c r="K24" t="str">
-        <v/>
-      </c>
-      <c r="L24" t="str">
-        <v/>
-      </c>
-      <c r="M24" t="str">
-        <v/>
-      </c>
-      <c r="N24" t="str">
-        <v>TRUE</v>
-      </c>
-      <c r="O24" t="str">
-        <v>custom</v>
-      </c>
-      <c r="P24" t="str">
-        <v>f62a31a0-1e5f-4f5c-a292-a1fcf8d4ec0d</v>
-      </c>
-      <c r="Q24" t="str">
-        <v>scheduled</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="str">
-        <v>9ac7761d-eda5-4af3-abe1-6fa0ea083c6f</v>
-      </c>
-      <c r="B25" t="str">
-        <v>DL / HS</v>
-      </c>
-      <c r="C25" t="str">
-        <v/>
-      </c>
-      <c r="D25" t="str">
-        <v>Hannah</v>
-      </c>
-      <c r="E25" t="str">
-        <v>DL</v>
-      </c>
-      <c r="F25" t="str">
-        <v>2026-07-24T08:45:00</v>
-      </c>
-      <c r="G25" t="str">
-        <v>2026-07-24T12:15:00</v>
-      </c>
-      <c r="H25" t="str">
-        <v>FALSE</v>
-      </c>
-      <c r="I25" t="str">
-        <v>TRUE</v>
-      </c>
-      <c r="J25" t="str">
-        <v>client-session</v>
-      </c>
-      <c r="K25" t="str">
-        <v/>
-      </c>
-      <c r="L25" t="str">
-        <v/>
-      </c>
-      <c r="M25" t="str">
-        <v/>
-      </c>
-      <c r="N25" t="str">
-        <v>TRUE</v>
-      </c>
-      <c r="O25" t="str">
-        <v>custom</v>
-      </c>
-      <c r="P25" t="str">
-        <v>f62a31a0-1e5f-4f5c-a292-a1fcf8d4ec0d</v>
-      </c>
-      <c r="Q25" t="str">
-        <v>scheduled</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="str">
-        <v>90d371f1-8431-4e60-a719-7b36a99cf3e5</v>
-      </c>
-      <c r="B26" t="str">
-        <v>DL / HS</v>
-      </c>
-      <c r="C26" t="str">
-        <v/>
-      </c>
-      <c r="D26" t="str">
-        <v>Hannah</v>
-      </c>
-      <c r="E26" t="str">
-        <v>DL</v>
-      </c>
-      <c r="F26" t="str">
-        <v>2026-07-27T08:45:00</v>
-      </c>
-      <c r="G26" t="str">
-        <v>2026-07-27T12:15:00</v>
-      </c>
-      <c r="H26" t="str">
-        <v>FALSE</v>
-      </c>
-      <c r="I26" t="str">
-        <v>TRUE</v>
-      </c>
-      <c r="J26" t="str">
-        <v>client-session</v>
-      </c>
-      <c r="K26" t="str">
-        <v/>
-      </c>
-      <c r="L26" t="str">
-        <v/>
-      </c>
-      <c r="M26" t="str">
-        <v/>
-      </c>
-      <c r="N26" t="str">
-        <v>TRUE</v>
-      </c>
-      <c r="O26" t="str">
-        <v>custom</v>
-      </c>
-      <c r="P26" t="str">
-        <v>f62a31a0-1e5f-4f5c-a292-a1fcf8d4ec0d</v>
-      </c>
-      <c r="Q26" t="str">
-        <v>scheduled</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="str">
-        <v>cd5fa09a-f55b-4630-85bc-95868f833ea2</v>
-      </c>
-      <c r="B27" t="str">
-        <v>DL / HS</v>
-      </c>
-      <c r="C27" t="str">
-        <v/>
-      </c>
-      <c r="D27" t="str">
-        <v>Hannah</v>
-      </c>
-      <c r="E27" t="str">
-        <v>DL</v>
-      </c>
-      <c r="F27" t="str">
-        <v>2026-07-29T08:45:00</v>
-      </c>
-      <c r="G27" t="str">
-        <v>2026-07-29T12:15:00</v>
-      </c>
-      <c r="H27" t="str">
-        <v>FALSE</v>
-      </c>
-      <c r="I27" t="str">
-        <v>TRUE</v>
-      </c>
-      <c r="J27" t="str">
-        <v>client-session</v>
-      </c>
-      <c r="K27" t="str">
-        <v/>
-      </c>
-      <c r="L27" t="str">
-        <v/>
-      </c>
-      <c r="M27" t="str">
-        <v/>
-      </c>
-      <c r="N27" t="str">
-        <v>TRUE</v>
-      </c>
-      <c r="O27" t="str">
-        <v>custom</v>
-      </c>
-      <c r="P27" t="str">
-        <v>f62a31a0-1e5f-4f5c-a292-a1fcf8d4ec0d</v>
-      </c>
-      <c r="Q27" t="str">
-        <v>scheduled</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="str">
-        <v>3b8727ac-16d4-4666-ad7e-a35e1d6b2c49</v>
-      </c>
-      <c r="B28" t="str">
-        <v>DL / HS</v>
-      </c>
-      <c r="C28" t="str">
-        <v/>
-      </c>
-      <c r="D28" t="str">
-        <v>Hannah</v>
-      </c>
-      <c r="E28" t="str">
-        <v>DL</v>
-      </c>
-      <c r="F28" t="str">
-        <v>2026-07-31T08:45:00</v>
-      </c>
-      <c r="G28" t="str">
-        <v>2026-07-31T12:15:00</v>
-      </c>
-      <c r="H28" t="str">
-        <v>FALSE</v>
-      </c>
-      <c r="I28" t="str">
-        <v>TRUE</v>
-      </c>
-      <c r="J28" t="str">
-        <v>client-session</v>
-      </c>
-      <c r="K28" t="str">
-        <v/>
-      </c>
-      <c r="L28" t="str">
-        <v/>
-      </c>
-      <c r="M28" t="str">
-        <v/>
-      </c>
-      <c r="N28" t="str">
-        <v>TRUE</v>
-      </c>
-      <c r="O28" t="str">
-        <v>custom</v>
-      </c>
-      <c r="P28" t="str">
-        <v>f62a31a0-1e5f-4f5c-a292-a1fcf8d4ec0d</v>
-      </c>
-      <c r="Q28" t="str">
-        <v>scheduled</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="str">
-        <v>f41b99f0-04b4-4852-9a20-1634a5a85fc2</v>
-      </c>
-      <c r="B29" t="str">
-        <v>DL / HS</v>
-      </c>
-      <c r="C29" t="str">
-        <v/>
-      </c>
-      <c r="D29" t="str">
-        <v>Hannah</v>
-      </c>
-      <c r="E29" t="str">
-        <v>DL</v>
-      </c>
-      <c r="F29" t="str">
-        <v>2026-08-03T08:45:00</v>
-      </c>
-      <c r="G29" t="str">
-        <v>2026-08-03T12:15:00</v>
-      </c>
-      <c r="H29" t="str">
-        <v>FALSE</v>
-      </c>
-      <c r="I29" t="str">
-        <v>TRUE</v>
-      </c>
-      <c r="J29" t="str">
-        <v>client-session</v>
-      </c>
-      <c r="K29" t="str">
-        <v/>
-      </c>
-      <c r="L29" t="str">
-        <v/>
-      </c>
-      <c r="M29" t="str">
-        <v/>
-      </c>
-      <c r="N29" t="str">
-        <v>TRUE</v>
-      </c>
-      <c r="O29" t="str">
-        <v>custom</v>
-      </c>
-      <c r="P29" t="str">
-        <v>f62a31a0-1e5f-4f5c-a292-a1fcf8d4ec0d</v>
-      </c>
-      <c r="Q29" t="str">
-        <v>scheduled</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="str">
-        <v>65358987-a904-4dc6-9605-0e835c45547d</v>
-      </c>
-      <c r="B30" t="str">
-        <v>DL / HS</v>
-      </c>
-      <c r="C30" t="str">
-        <v/>
-      </c>
-      <c r="D30" t="str">
-        <v>Hannah</v>
-      </c>
-      <c r="E30" t="str">
-        <v>DL</v>
-      </c>
-      <c r="F30" t="str">
-        <v>2026-08-05T08:45:00</v>
-      </c>
-      <c r="G30" t="str">
-        <v>2026-08-05T12:15:00</v>
-      </c>
-      <c r="H30" t="str">
-        <v>FALSE</v>
-      </c>
-      <c r="I30" t="str">
-        <v>TRUE</v>
-      </c>
-      <c r="J30" t="str">
-        <v>client-session</v>
-      </c>
-      <c r="K30" t="str">
-        <v/>
-      </c>
-      <c r="L30" t="str">
-        <v/>
-      </c>
-      <c r="M30" t="str">
-        <v/>
-      </c>
-      <c r="N30" t="str">
-        <v>TRUE</v>
-      </c>
-      <c r="O30" t="str">
-        <v>custom</v>
-      </c>
-      <c r="P30" t="str">
-        <v>f62a31a0-1e5f-4f5c-a292-a1fcf8d4ec0d</v>
-      </c>
-      <c r="Q30" t="str">
-        <v>scheduled</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="str">
-        <v>56ec8570-d917-468c-8c86-26a76e077d79</v>
-      </c>
-      <c r="B31" t="str">
-        <v>DL / HS</v>
-      </c>
-      <c r="C31" t="str">
-        <v/>
-      </c>
-      <c r="D31" t="str">
-        <v>Hannah</v>
-      </c>
-      <c r="E31" t="str">
-        <v>DL</v>
-      </c>
-      <c r="F31" t="str">
-        <v>2026-08-07T08:45:00</v>
-      </c>
-      <c r="G31" t="str">
-        <v>2026-08-07T12:15:00</v>
-      </c>
-      <c r="H31" t="str">
-        <v>FALSE</v>
-      </c>
-      <c r="I31" t="str">
-        <v>TRUE</v>
-      </c>
-      <c r="J31" t="str">
-        <v>client-session</v>
-      </c>
-      <c r="K31" t="str">
-        <v/>
-      </c>
-      <c r="L31" t="str">
-        <v/>
-      </c>
-      <c r="M31" t="str">
-        <v/>
-      </c>
-      <c r="N31" t="str">
-        <v>TRUE</v>
-      </c>
-      <c r="O31" t="str">
-        <v>custom</v>
-      </c>
-      <c r="P31" t="str">
-        <v>f62a31a0-1e5f-4f5c-a292-a1fcf8d4ec0d</v>
-      </c>
-      <c r="Q31" t="str">
-        <v>scheduled</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="str">
-        <v>62629255-ec8a-4fa1-b2dd-ecaf9f714379</v>
-      </c>
-      <c r="B32" t="str">
-        <v>DL / HS</v>
-      </c>
-      <c r="C32" t="str">
-        <v/>
-      </c>
-      <c r="D32" t="str">
-        <v>Hannah</v>
-      </c>
-      <c r="E32" t="str">
-        <v>DL</v>
-      </c>
-      <c r="F32" t="str">
-        <v>2026-08-10T08:45:00</v>
-      </c>
-      <c r="G32" t="str">
-        <v>2026-08-10T12:15:00</v>
-      </c>
-      <c r="H32" t="str">
-        <v>FALSE</v>
-      </c>
-      <c r="I32" t="str">
-        <v>TRUE</v>
-      </c>
-      <c r="J32" t="str">
-        <v>client-session</v>
-      </c>
-      <c r="K32" t="str">
-        <v/>
-      </c>
-      <c r="L32" t="str">
-        <v/>
-      </c>
-      <c r="M32" t="str">
-        <v/>
-      </c>
-      <c r="N32" t="str">
-        <v>TRUE</v>
-      </c>
-      <c r="O32" t="str">
-        <v>custom</v>
-      </c>
-      <c r="P32" t="str">
-        <v>f62a31a0-1e5f-4f5c-a292-a1fcf8d4ec0d</v>
-      </c>
-      <c r="Q32" t="str">
-        <v>scheduled</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="str">
-        <v>2aa6b091-af77-4dcf-bf8d-d51a6a76f657</v>
-      </c>
-      <c r="B33" t="str">
-        <v>DL / HS</v>
-      </c>
-      <c r="C33" t="str">
-        <v/>
-      </c>
-      <c r="D33" t="str">
-        <v>Hannah</v>
-      </c>
-      <c r="E33" t="str">
-        <v>DL</v>
-      </c>
-      <c r="F33" t="str">
-        <v>2026-08-12T08:45:00</v>
-      </c>
-      <c r="G33" t="str">
-        <v>2026-08-12T12:15:00</v>
-      </c>
-      <c r="H33" t="str">
-        <v>FALSE</v>
-      </c>
-      <c r="I33" t="str">
-        <v>TRUE</v>
-      </c>
-      <c r="J33" t="str">
-        <v>client-session</v>
-      </c>
-      <c r="K33" t="str">
-        <v/>
-      </c>
-      <c r="L33" t="str">
-        <v/>
-      </c>
-      <c r="M33" t="str">
-        <v/>
-      </c>
-      <c r="N33" t="str">
-        <v>TRUE</v>
-      </c>
-      <c r="O33" t="str">
-        <v>custom</v>
-      </c>
-      <c r="P33" t="str">
-        <v>f62a31a0-1e5f-4f5c-a292-a1fcf8d4ec0d</v>
-      </c>
-      <c r="Q33" t="str">
-        <v>scheduled</v>
+        <v>shelbyville, il</v>
+      </c>
+      <c r="B3">
+        <v>39.4067</v>
+      </c>
+      <c r="C3">
+        <v>-88.79</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:Q33"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C3"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:E49"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>appointmentId</v>
+        <v>from</v>
       </c>
       <c r="B1" t="str">
-        <v>source</v>
+        <v>to</v>
       </c>
       <c r="C1" t="str">
-        <v>reason</v>
+        <v>dow</v>
       </c>
       <c r="D1" t="str">
-        <v>unplanned</v>
+        <v>hour</v>
       </c>
       <c r="E1" t="str">
-        <v>noticeMet</v>
-      </c>
-      <c r="F1" t="str">
-        <v>canceledAt</v>
-      </c>
-      <c r="G1" t="str">
-        <v>notes</v>
+        <v>minutes</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>springfield, il</v>
+      </c>
+      <c r="B2" t="str">
+        <v>shelbyville, il</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>16</v>
+      </c>
+      <c r="E2">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>shelbyville, il</v>
+      </c>
+      <c r="B3" t="str">
+        <v>springfield, il</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>16</v>
+      </c>
+      <c r="E3">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>HOME</v>
+      </c>
+      <c r="B4" t="str">
+        <v>shelbyville, il</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="D4">
+        <v>16</v>
+      </c>
+      <c r="E4">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>HOME</v>
+      </c>
+      <c r="B5" t="str">
+        <v>springfield, il</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5">
+        <v>16</v>
+      </c>
+      <c r="E5">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>springfield, il</v>
+      </c>
+      <c r="B6" t="str">
+        <v>shelbyville, il</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="D6">
+        <v>17</v>
+      </c>
+      <c r="E6">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>shelbyville, il</v>
+      </c>
+      <c r="B7" t="str">
+        <v>springfield, il</v>
+      </c>
+      <c r="C7">
+        <v>1</v>
+      </c>
+      <c r="D7">
+        <v>17</v>
+      </c>
+      <c r="E7">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>HOME</v>
+      </c>
+      <c r="B8" t="str">
+        <v>shelbyville, il</v>
+      </c>
+      <c r="C8">
+        <v>1</v>
+      </c>
+      <c r="D8">
+        <v>17</v>
+      </c>
+      <c r="E8">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>HOME</v>
+      </c>
+      <c r="B9" t="str">
+        <v>springfield, il</v>
+      </c>
+      <c r="C9">
+        <v>1</v>
+      </c>
+      <c r="D9">
+        <v>17</v>
+      </c>
+      <c r="E9">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>springfield, il</v>
+      </c>
+      <c r="B10" t="str">
+        <v>shelbyville, il</v>
+      </c>
+      <c r="C10">
+        <v>1</v>
+      </c>
+      <c r="D10">
+        <v>18</v>
+      </c>
+      <c r="E10">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>shelbyville, il</v>
+      </c>
+      <c r="B11" t="str">
+        <v>springfield, il</v>
+      </c>
+      <c r="C11">
+        <v>1</v>
+      </c>
+      <c r="D11">
+        <v>18</v>
+      </c>
+      <c r="E11">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>HOME</v>
+      </c>
+      <c r="B12" t="str">
+        <v>shelbyville, il</v>
+      </c>
+      <c r="C12">
+        <v>1</v>
+      </c>
+      <c r="D12">
+        <v>18</v>
+      </c>
+      <c r="E12">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>HOME</v>
+      </c>
+      <c r="B13" t="str">
+        <v>springfield, il</v>
+      </c>
+      <c r="C13">
+        <v>1</v>
+      </c>
+      <c r="D13">
+        <v>18</v>
+      </c>
+      <c r="E13">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>springfield, il</v>
+      </c>
+      <c r="B14" t="str">
+        <v>shelbyville, il</v>
+      </c>
+      <c r="C14">
+        <v>2</v>
+      </c>
+      <c r="D14">
+        <v>16</v>
+      </c>
+      <c r="E14">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>shelbyville, il</v>
+      </c>
+      <c r="B15" t="str">
+        <v>springfield, il</v>
+      </c>
+      <c r="C15">
+        <v>2</v>
+      </c>
+      <c r="D15">
+        <v>16</v>
+      </c>
+      <c r="E15">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>HOME</v>
+      </c>
+      <c r="B16" t="str">
+        <v>shelbyville, il</v>
+      </c>
+      <c r="C16">
+        <v>2</v>
+      </c>
+      <c r="D16">
+        <v>16</v>
+      </c>
+      <c r="E16">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>HOME</v>
+      </c>
+      <c r="B17" t="str">
+        <v>springfield, il</v>
+      </c>
+      <c r="C17">
+        <v>2</v>
+      </c>
+      <c r="D17">
+        <v>16</v>
+      </c>
+      <c r="E17">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>springfield, il</v>
+      </c>
+      <c r="B18" t="str">
+        <v>shelbyville, il</v>
+      </c>
+      <c r="C18">
+        <v>2</v>
+      </c>
+      <c r="D18">
+        <v>17</v>
+      </c>
+      <c r="E18">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>shelbyville, il</v>
+      </c>
+      <c r="B19" t="str">
+        <v>springfield, il</v>
+      </c>
+      <c r="C19">
+        <v>2</v>
+      </c>
+      <c r="D19">
+        <v>17</v>
+      </c>
+      <c r="E19">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>HOME</v>
+      </c>
+      <c r="B20" t="str">
+        <v>shelbyville, il</v>
+      </c>
+      <c r="C20">
+        <v>2</v>
+      </c>
+      <c r="D20">
+        <v>17</v>
+      </c>
+      <c r="E20">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>HOME</v>
+      </c>
+      <c r="B21" t="str">
+        <v>springfield, il</v>
+      </c>
+      <c r="C21">
+        <v>2</v>
+      </c>
+      <c r="D21">
+        <v>17</v>
+      </c>
+      <c r="E21">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>springfield, il</v>
+      </c>
+      <c r="B22" t="str">
+        <v>shelbyville, il</v>
+      </c>
+      <c r="C22">
+        <v>2</v>
+      </c>
+      <c r="D22">
+        <v>18</v>
+      </c>
+      <c r="E22">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>shelbyville, il</v>
+      </c>
+      <c r="B23" t="str">
+        <v>springfield, il</v>
+      </c>
+      <c r="C23">
+        <v>2</v>
+      </c>
+      <c r="D23">
+        <v>18</v>
+      </c>
+      <c r="E23">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>HOME</v>
+      </c>
+      <c r="B24" t="str">
+        <v>shelbyville, il</v>
+      </c>
+      <c r="C24">
+        <v>2</v>
+      </c>
+      <c r="D24">
+        <v>18</v>
+      </c>
+      <c r="E24">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>HOME</v>
+      </c>
+      <c r="B25" t="str">
+        <v>springfield, il</v>
+      </c>
+      <c r="C25">
+        <v>2</v>
+      </c>
+      <c r="D25">
+        <v>18</v>
+      </c>
+      <c r="E25">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>springfield, il</v>
+      </c>
+      <c r="B26" t="str">
+        <v>shelbyville, il</v>
+      </c>
+      <c r="C26">
+        <v>3</v>
+      </c>
+      <c r="D26">
+        <v>16</v>
+      </c>
+      <c r="E26">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>shelbyville, il</v>
+      </c>
+      <c r="B27" t="str">
+        <v>springfield, il</v>
+      </c>
+      <c r="C27">
+        <v>3</v>
+      </c>
+      <c r="D27">
+        <v>16</v>
+      </c>
+      <c r="E27">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>HOME</v>
+      </c>
+      <c r="B28" t="str">
+        <v>shelbyville, il</v>
+      </c>
+      <c r="C28">
+        <v>3</v>
+      </c>
+      <c r="D28">
+        <v>16</v>
+      </c>
+      <c r="E28">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>HOME</v>
+      </c>
+      <c r="B29" t="str">
+        <v>springfield, il</v>
+      </c>
+      <c r="C29">
+        <v>3</v>
+      </c>
+      <c r="D29">
+        <v>16</v>
+      </c>
+      <c r="E29">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>springfield, il</v>
+      </c>
+      <c r="B30" t="str">
+        <v>shelbyville, il</v>
+      </c>
+      <c r="C30">
+        <v>3</v>
+      </c>
+      <c r="D30">
+        <v>17</v>
+      </c>
+      <c r="E30">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>shelbyville, il</v>
+      </c>
+      <c r="B31" t="str">
+        <v>springfield, il</v>
+      </c>
+      <c r="C31">
+        <v>3</v>
+      </c>
+      <c r="D31">
+        <v>17</v>
+      </c>
+      <c r="E31">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>HOME</v>
+      </c>
+      <c r="B32" t="str">
+        <v>shelbyville, il</v>
+      </c>
+      <c r="C32">
+        <v>3</v>
+      </c>
+      <c r="D32">
+        <v>17</v>
+      </c>
+      <c r="E32">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>HOME</v>
+      </c>
+      <c r="B33" t="str">
+        <v>springfield, il</v>
+      </c>
+      <c r="C33">
+        <v>3</v>
+      </c>
+      <c r="D33">
+        <v>17</v>
+      </c>
+      <c r="E33">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>springfield, il</v>
+      </c>
+      <c r="B34" t="str">
+        <v>shelbyville, il</v>
+      </c>
+      <c r="C34">
+        <v>3</v>
+      </c>
+      <c r="D34">
+        <v>18</v>
+      </c>
+      <c r="E34">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>shelbyville, il</v>
+      </c>
+      <c r="B35" t="str">
+        <v>springfield, il</v>
+      </c>
+      <c r="C35">
+        <v>3</v>
+      </c>
+      <c r="D35">
+        <v>18</v>
+      </c>
+      <c r="E35">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>HOME</v>
+      </c>
+      <c r="B36" t="str">
+        <v>shelbyville, il</v>
+      </c>
+      <c r="C36">
+        <v>3</v>
+      </c>
+      <c r="D36">
+        <v>18</v>
+      </c>
+      <c r="E36">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>HOME</v>
+      </c>
+      <c r="B37" t="str">
+        <v>springfield, il</v>
+      </c>
+      <c r="C37">
+        <v>3</v>
+      </c>
+      <c r="D37">
+        <v>18</v>
+      </c>
+      <c r="E37">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>springfield, il</v>
+      </c>
+      <c r="B38" t="str">
+        <v>shelbyville, il</v>
+      </c>
+      <c r="C38">
+        <v>4</v>
+      </c>
+      <c r="D38">
+        <v>16</v>
+      </c>
+      <c r="E38">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>shelbyville, il</v>
+      </c>
+      <c r="B39" t="str">
+        <v>springfield, il</v>
+      </c>
+      <c r="C39">
+        <v>4</v>
+      </c>
+      <c r="D39">
+        <v>16</v>
+      </c>
+      <c r="E39">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>HOME</v>
+      </c>
+      <c r="B40" t="str">
+        <v>shelbyville, il</v>
+      </c>
+      <c r="C40">
+        <v>4</v>
+      </c>
+      <c r="D40">
+        <v>16</v>
+      </c>
+      <c r="E40">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v>HOME</v>
+      </c>
+      <c r="B41" t="str">
+        <v>springfield, il</v>
+      </c>
+      <c r="C41">
+        <v>4</v>
+      </c>
+      <c r="D41">
+        <v>16</v>
+      </c>
+      <c r="E41">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v>springfield, il</v>
+      </c>
+      <c r="B42" t="str">
+        <v>shelbyville, il</v>
+      </c>
+      <c r="C42">
+        <v>4</v>
+      </c>
+      <c r="D42">
+        <v>17</v>
+      </c>
+      <c r="E42">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v>shelbyville, il</v>
+      </c>
+      <c r="B43" t="str">
+        <v>springfield, il</v>
+      </c>
+      <c r="C43">
+        <v>4</v>
+      </c>
+      <c r="D43">
+        <v>17</v>
+      </c>
+      <c r="E43">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v>HOME</v>
+      </c>
+      <c r="B44" t="str">
+        <v>shelbyville, il</v>
+      </c>
+      <c r="C44">
+        <v>4</v>
+      </c>
+      <c r="D44">
+        <v>17</v>
+      </c>
+      <c r="E44">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="str">
+        <v>HOME</v>
+      </c>
+      <c r="B45" t="str">
+        <v>springfield, il</v>
+      </c>
+      <c r="C45">
+        <v>4</v>
+      </c>
+      <c r="D45">
+        <v>17</v>
+      </c>
+      <c r="E45">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="str">
+        <v>springfield, il</v>
+      </c>
+      <c r="B46" t="str">
+        <v>shelbyville, il</v>
+      </c>
+      <c r="C46">
+        <v>4</v>
+      </c>
+      <c r="D46">
+        <v>18</v>
+      </c>
+      <c r="E46">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="str">
+        <v>shelbyville, il</v>
+      </c>
+      <c r="B47" t="str">
+        <v>springfield, il</v>
+      </c>
+      <c r="C47">
+        <v>4</v>
+      </c>
+      <c r="D47">
+        <v>18</v>
+      </c>
+      <c r="E47">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="str">
+        <v>HOME</v>
+      </c>
+      <c r="B48" t="str">
+        <v>shelbyville, il</v>
+      </c>
+      <c r="C48">
+        <v>4</v>
+      </c>
+      <c r="D48">
+        <v>18</v>
+      </c>
+      <c r="E48">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="str">
+        <v>HOME</v>
+      </c>
+      <c r="B49" t="str">
+        <v>springfield, il</v>
+      </c>
+      <c r="C49">
+        <v>4</v>
+      </c>
+      <c r="D49">
+        <v>18</v>
+      </c>
+      <c r="E49">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G1"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E49"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:Q33"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
         <v>id</v>
       </c>
       <c r="B1" t="str">
-        <v>entityType</v>
+        <v>title</v>
       </c>
       <c r="C1" t="str">
-        <v>entityId</v>
+        <v>description</v>
       </c>
       <c r="D1" t="str">
-        <v>entityName</v>
+        <v>technician</v>
       </c>
       <c r="E1" t="str">
-        <v>date</v>
+        <v>client</v>
       </c>
       <c r="F1" t="str">
-        <v>reason</v>
+        <v>startTime</v>
       </c>
       <c r="G1" t="str">
-        <v>createdAt</v>
+        <v>endTime</v>
+      </c>
+      <c r="H1" t="str">
+        <v>isFixed</v>
+      </c>
+      <c r="I1" t="str">
+        <v>isBillable</v>
+      </c>
+      <c r="J1" t="str">
+        <v>type</v>
+      </c>
+      <c r="K1" t="str">
+        <v>isMakeUp</v>
+      </c>
+      <c r="L1" t="str">
+        <v>makeupForId</v>
+      </c>
+      <c r="M1" t="str">
+        <v>isGhost</v>
+      </c>
+      <c r="N1" t="str">
+        <v>isRecurring</v>
+      </c>
+      <c r="O1" t="str">
+        <v>recurringPattern</v>
+      </c>
+      <c r="P1" t="str">
+        <v>seriesId</v>
+      </c>
+      <c r="Q1" t="str">
+        <v>status</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>c4f33f78-7510-4ed3-b1b5-7fcf5e342526</v>
+      </c>
+      <c r="B2" t="str">
+        <v>DL / HS</v>
+      </c>
+      <c r="C2" t="str">
+        <v/>
+      </c>
+      <c r="D2" t="str">
+        <v>Hannah</v>
+      </c>
+      <c r="E2" t="str">
+        <v>DL</v>
+      </c>
+      <c r="F2" t="str">
+        <v>2026-06-01T08:45:00</v>
+      </c>
+      <c r="G2" t="str">
+        <v>2026-06-01T12:15:00</v>
+      </c>
+      <c r="H2" t="str">
+        <v>FALSE</v>
+      </c>
+      <c r="I2" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="J2" t="str">
+        <v>client-session</v>
+      </c>
+      <c r="K2" t="str">
+        <v/>
+      </c>
+      <c r="L2" t="str">
+        <v/>
+      </c>
+      <c r="M2" t="str">
+        <v/>
+      </c>
+      <c r="N2" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="O2" t="str">
+        <v>custom</v>
+      </c>
+      <c r="P2" t="str">
+        <v>f62a31a0-1e5f-4f5c-a292-a1fcf8d4ec0d</v>
+      </c>
+      <c r="Q2" t="str">
+        <v>scheduled</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>41f8a519-11f5-4fac-8975-47515199096b</v>
+      </c>
+      <c r="B3" t="str">
+        <v>DL / HS</v>
+      </c>
+      <c r="C3" t="str">
+        <v/>
+      </c>
+      <c r="D3" t="str">
+        <v>Hannah</v>
+      </c>
+      <c r="E3" t="str">
+        <v>DL</v>
+      </c>
+      <c r="F3" t="str">
+        <v>2026-06-03T08:45:00</v>
+      </c>
+      <c r="G3" t="str">
+        <v>2026-06-03T12:15:00</v>
+      </c>
+      <c r="H3" t="str">
+        <v>FALSE</v>
+      </c>
+      <c r="I3" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="J3" t="str">
+        <v>client-session</v>
+      </c>
+      <c r="K3" t="str">
+        <v/>
+      </c>
+      <c r="L3" t="str">
+        <v/>
+      </c>
+      <c r="M3" t="str">
+        <v/>
+      </c>
+      <c r="N3" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="O3" t="str">
+        <v>custom</v>
+      </c>
+      <c r="P3" t="str">
+        <v>f62a31a0-1e5f-4f5c-a292-a1fcf8d4ec0d</v>
+      </c>
+      <c r="Q3" t="str">
+        <v>scheduled</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>f03c70a1-92fc-4fa1-a831-f9198d8cee93</v>
+      </c>
+      <c r="B4" t="str">
+        <v>DL / HS</v>
+      </c>
+      <c r="C4" t="str">
+        <v/>
+      </c>
+      <c r="D4" t="str">
+        <v>Hannah</v>
+      </c>
+      <c r="E4" t="str">
+        <v>DL</v>
+      </c>
+      <c r="F4" t="str">
+        <v>2026-06-05T08:45:00</v>
+      </c>
+      <c r="G4" t="str">
+        <v>2026-06-05T12:15:00</v>
+      </c>
+      <c r="H4" t="str">
+        <v>FALSE</v>
+      </c>
+      <c r="I4" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="J4" t="str">
+        <v>client-session</v>
+      </c>
+      <c r="K4" t="str">
+        <v/>
+      </c>
+      <c r="L4" t="str">
+        <v/>
+      </c>
+      <c r="M4" t="str">
+        <v/>
+      </c>
+      <c r="N4" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="O4" t="str">
+        <v>custom</v>
+      </c>
+      <c r="P4" t="str">
+        <v>f62a31a0-1e5f-4f5c-a292-a1fcf8d4ec0d</v>
+      </c>
+      <c r="Q4" t="str">
+        <v>scheduled</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>77b7beef-0140-4ce4-9eb6-93d404b0a91f</v>
+      </c>
+      <c r="B5" t="str">
+        <v>DL / HS</v>
+      </c>
+      <c r="C5" t="str">
+        <v/>
+      </c>
+      <c r="D5" t="str">
+        <v>Hannah</v>
+      </c>
+      <c r="E5" t="str">
+        <v>DL</v>
+      </c>
+      <c r="F5" t="str">
+        <v>2026-06-08T08:45:00</v>
+      </c>
+      <c r="G5" t="str">
+        <v>2026-06-08T12:15:00</v>
+      </c>
+      <c r="H5" t="str">
+        <v>FALSE</v>
+      </c>
+      <c r="I5" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="J5" t="str">
+        <v>client-session</v>
+      </c>
+      <c r="K5" t="str">
+        <v/>
+      </c>
+      <c r="L5" t="str">
+        <v/>
+      </c>
+      <c r="M5" t="str">
+        <v/>
+      </c>
+      <c r="N5" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="O5" t="str">
+        <v>custom</v>
+      </c>
+      <c r="P5" t="str">
+        <v>f62a31a0-1e5f-4f5c-a292-a1fcf8d4ec0d</v>
+      </c>
+      <c r="Q5" t="str">
+        <v>scheduled</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>f55bcb1f-d846-496f-bc77-2b510087c1f9</v>
+      </c>
+      <c r="B6" t="str">
+        <v>DL / HS</v>
+      </c>
+      <c r="C6" t="str">
+        <v/>
+      </c>
+      <c r="D6" t="str">
+        <v>Hannah</v>
+      </c>
+      <c r="E6" t="str">
+        <v>DL</v>
+      </c>
+      <c r="F6" t="str">
+        <v>2026-06-10T08:45:00</v>
+      </c>
+      <c r="G6" t="str">
+        <v>2026-06-10T12:15:00</v>
+      </c>
+      <c r="H6" t="str">
+        <v>FALSE</v>
+      </c>
+      <c r="I6" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="J6" t="str">
+        <v>client-session</v>
+      </c>
+      <c r="K6" t="str">
+        <v/>
+      </c>
+      <c r="L6" t="str">
+        <v/>
+      </c>
+      <c r="M6" t="str">
+        <v/>
+      </c>
+      <c r="N6" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="O6" t="str">
+        <v>custom</v>
+      </c>
+      <c r="P6" t="str">
+        <v>f62a31a0-1e5f-4f5c-a292-a1fcf8d4ec0d</v>
+      </c>
+      <c r="Q6" t="str">
+        <v>scheduled</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>a1a3bbd3-ecca-4bca-802c-88d414dc894e</v>
+      </c>
+      <c r="B7" t="str">
+        <v>DL / HS</v>
+      </c>
+      <c r="C7" t="str">
+        <v/>
+      </c>
+      <c r="D7" t="str">
+        <v>Hannah</v>
+      </c>
+      <c r="E7" t="str">
+        <v>DL</v>
+      </c>
+      <c r="F7" t="str">
+        <v>2026-06-12T08:45:00</v>
+      </c>
+      <c r="G7" t="str">
+        <v>2026-06-12T12:15:00</v>
+      </c>
+      <c r="H7" t="str">
+        <v>FALSE</v>
+      </c>
+      <c r="I7" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="J7" t="str">
+        <v>client-session</v>
+      </c>
+      <c r="K7" t="str">
+        <v/>
+      </c>
+      <c r="L7" t="str">
+        <v/>
+      </c>
+      <c r="M7" t="str">
+        <v/>
+      </c>
+      <c r="N7" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="O7" t="str">
+        <v>custom</v>
+      </c>
+      <c r="P7" t="str">
+        <v>f62a31a0-1e5f-4f5c-a292-a1fcf8d4ec0d</v>
+      </c>
+      <c r="Q7" t="str">
+        <v>scheduled</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>11be6d4e-0bdc-4d9a-b1c1-1056f3f09456</v>
+      </c>
+      <c r="B8" t="str">
+        <v>DL / HS</v>
+      </c>
+      <c r="C8" t="str">
+        <v/>
+      </c>
+      <c r="D8" t="str">
+        <v>Hannah</v>
+      </c>
+      <c r="E8" t="str">
+        <v>DL</v>
+      </c>
+      <c r="F8" t="str">
+        <v>2026-06-15T08:45:00</v>
+      </c>
+      <c r="G8" t="str">
+        <v>2026-06-15T12:15:00</v>
+      </c>
+      <c r="H8" t="str">
+        <v>FALSE</v>
+      </c>
+      <c r="I8" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="J8" t="str">
+        <v>client-session</v>
+      </c>
+      <c r="K8" t="str">
+        <v/>
+      </c>
+      <c r="L8" t="str">
+        <v/>
+      </c>
+      <c r="M8" t="str">
+        <v/>
+      </c>
+      <c r="N8" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="O8" t="str">
+        <v>custom</v>
+      </c>
+      <c r="P8" t="str">
+        <v>f62a31a0-1e5f-4f5c-a292-a1fcf8d4ec0d</v>
+      </c>
+      <c r="Q8" t="str">
+        <v>scheduled</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>f4951d7b-ed8a-4c01-87e2-3d6fbd88f280</v>
+      </c>
+      <c r="B9" t="str">
+        <v>DL / HS</v>
+      </c>
+      <c r="C9" t="str">
+        <v/>
+      </c>
+      <c r="D9" t="str">
+        <v>Hannah</v>
+      </c>
+      <c r="E9" t="str">
+        <v>DL</v>
+      </c>
+      <c r="F9" t="str">
+        <v>2026-06-17T08:45:00</v>
+      </c>
+      <c r="G9" t="str">
+        <v>2026-06-17T12:15:00</v>
+      </c>
+      <c r="H9" t="str">
+        <v>FALSE</v>
+      </c>
+      <c r="I9" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="J9" t="str">
+        <v>client-session</v>
+      </c>
+      <c r="K9" t="str">
+        <v/>
+      </c>
+      <c r="L9" t="str">
+        <v/>
+      </c>
+      <c r="M9" t="str">
+        <v/>
+      </c>
+      <c r="N9" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="O9" t="str">
+        <v>custom</v>
+      </c>
+      <c r="P9" t="str">
+        <v>f62a31a0-1e5f-4f5c-a292-a1fcf8d4ec0d</v>
+      </c>
+      <c r="Q9" t="str">
+        <v>scheduled</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>141718b1-4379-4186-b0c5-4b92f6c13951</v>
+      </c>
+      <c r="B10" t="str">
+        <v>DL / HS</v>
+      </c>
+      <c r="C10" t="str">
+        <v/>
+      </c>
+      <c r="D10" t="str">
+        <v>Hannah</v>
+      </c>
+      <c r="E10" t="str">
+        <v>DL</v>
+      </c>
+      <c r="F10" t="str">
+        <v>2026-06-19T08:45:00</v>
+      </c>
+      <c r="G10" t="str">
+        <v>2026-06-19T12:15:00</v>
+      </c>
+      <c r="H10" t="str">
+        <v>FALSE</v>
+      </c>
+      <c r="I10" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="J10" t="str">
+        <v>client-session</v>
+      </c>
+      <c r="K10" t="str">
+        <v/>
+      </c>
+      <c r="L10" t="str">
+        <v/>
+      </c>
+      <c r="M10" t="str">
+        <v/>
+      </c>
+      <c r="N10" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="O10" t="str">
+        <v>custom</v>
+      </c>
+      <c r="P10" t="str">
+        <v>f62a31a0-1e5f-4f5c-a292-a1fcf8d4ec0d</v>
+      </c>
+      <c r="Q10" t="str">
+        <v>scheduled</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>d8ff5fb6-af6f-4a61-84fa-bec4cb27acf2</v>
+      </c>
+      <c r="B11" t="str">
+        <v>DL / HS</v>
+      </c>
+      <c r="C11" t="str">
+        <v/>
+      </c>
+      <c r="D11" t="str">
+        <v>Hannah</v>
+      </c>
+      <c r="E11" t="str">
+        <v>DL</v>
+      </c>
+      <c r="F11" t="str">
+        <v>2026-06-22T08:45:00</v>
+      </c>
+      <c r="G11" t="str">
+        <v>2026-06-22T12:15:00</v>
+      </c>
+      <c r="H11" t="str">
+        <v>FALSE</v>
+      </c>
+      <c r="I11" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="J11" t="str">
+        <v>client-session</v>
+      </c>
+      <c r="K11" t="str">
+        <v/>
+      </c>
+      <c r="L11" t="str">
+        <v/>
+      </c>
+      <c r="M11" t="str">
+        <v/>
+      </c>
+      <c r="N11" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="O11" t="str">
+        <v>custom</v>
+      </c>
+      <c r="P11" t="str">
+        <v>f62a31a0-1e5f-4f5c-a292-a1fcf8d4ec0d</v>
+      </c>
+      <c r="Q11" t="str">
+        <v>scheduled</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>ce6bbbba-4bfe-4b56-8138-be0a8edfa3a4</v>
+      </c>
+      <c r="B12" t="str">
+        <v>DL / HS</v>
+      </c>
+      <c r="C12" t="str">
+        <v/>
+      </c>
+      <c r="D12" t="str">
+        <v>Hannah</v>
+      </c>
+      <c r="E12" t="str">
+        <v>DL</v>
+      </c>
+      <c r="F12" t="str">
+        <v>2026-06-24T08:45:00</v>
+      </c>
+      <c r="G12" t="str">
+        <v>2026-06-24T12:15:00</v>
+      </c>
+      <c r="H12" t="str">
+        <v>FALSE</v>
+      </c>
+      <c r="I12" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="J12" t="str">
+        <v>client-session</v>
+      </c>
+      <c r="K12" t="str">
+        <v/>
+      </c>
+      <c r="L12" t="str">
+        <v/>
+      </c>
+      <c r="M12" t="str">
+        <v/>
+      </c>
+      <c r="N12" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="O12" t="str">
+        <v>custom</v>
+      </c>
+      <c r="P12" t="str">
+        <v>f62a31a0-1e5f-4f5c-a292-a1fcf8d4ec0d</v>
+      </c>
+      <c r="Q12" t="str">
+        <v>scheduled</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>4b6c6613-29a1-40aa-886b-71c18bfa9de0</v>
+      </c>
+      <c r="B13" t="str">
+        <v>DL / HS</v>
+      </c>
+      <c r="C13" t="str">
+        <v/>
+      </c>
+      <c r="D13" t="str">
+        <v>Hannah</v>
+      </c>
+      <c r="E13" t="str">
+        <v>DL</v>
+      </c>
+      <c r="F13" t="str">
+        <v>2026-06-26T08:45:00</v>
+      </c>
+      <c r="G13" t="str">
+        <v>2026-06-26T12:15:00</v>
+      </c>
+      <c r="H13" t="str">
+        <v>FALSE</v>
+      </c>
+      <c r="I13" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="J13" t="str">
+        <v>client-session</v>
+      </c>
+      <c r="K13" t="str">
+        <v/>
+      </c>
+      <c r="L13" t="str">
+        <v/>
+      </c>
+      <c r="M13" t="str">
+        <v/>
+      </c>
+      <c r="N13" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="O13" t="str">
+        <v>custom</v>
+      </c>
+      <c r="P13" t="str">
+        <v>f62a31a0-1e5f-4f5c-a292-a1fcf8d4ec0d</v>
+      </c>
+      <c r="Q13" t="str">
+        <v>scheduled</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>c5a04a2f-a163-4c4f-8d72-51448349161c</v>
+      </c>
+      <c r="B14" t="str">
+        <v>DL / HS</v>
+      </c>
+      <c r="C14" t="str">
+        <v/>
+      </c>
+      <c r="D14" t="str">
+        <v>Hannah</v>
+      </c>
+      <c r="E14" t="str">
+        <v>DL</v>
+      </c>
+      <c r="F14" t="str">
+        <v>2026-06-29T08:45:00</v>
+      </c>
+      <c r="G14" t="str">
+        <v>2026-06-29T12:15:00</v>
+      </c>
+      <c r="H14" t="str">
+        <v>FALSE</v>
+      </c>
+      <c r="I14" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="J14" t="str">
+        <v>client-session</v>
+      </c>
+      <c r="K14" t="str">
+        <v/>
+      </c>
+      <c r="L14" t="str">
+        <v/>
+      </c>
+      <c r="M14" t="str">
+        <v/>
+      </c>
+      <c r="N14" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="O14" t="str">
+        <v>custom</v>
+      </c>
+      <c r="P14" t="str">
+        <v>f62a31a0-1e5f-4f5c-a292-a1fcf8d4ec0d</v>
+      </c>
+      <c r="Q14" t="str">
+        <v>scheduled</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>397d65f8-05bd-43b5-9403-ea9ea4519028</v>
+      </c>
+      <c r="B15" t="str">
+        <v>DL / HS</v>
+      </c>
+      <c r="C15" t="str">
+        <v/>
+      </c>
+      <c r="D15" t="str">
+        <v>Hannah</v>
+      </c>
+      <c r="E15" t="str">
+        <v>DL</v>
+      </c>
+      <c r="F15" t="str">
+        <v>2026-07-01T08:45:00</v>
+      </c>
+      <c r="G15" t="str">
+        <v>2026-07-01T12:15:00</v>
+      </c>
+      <c r="H15" t="str">
+        <v>FALSE</v>
+      </c>
+      <c r="I15" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="J15" t="str">
+        <v>client-session</v>
+      </c>
+      <c r="K15" t="str">
+        <v/>
+      </c>
+      <c r="L15" t="str">
+        <v/>
+      </c>
+      <c r="M15" t="str">
+        <v/>
+      </c>
+      <c r="N15" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="O15" t="str">
+        <v>custom</v>
+      </c>
+      <c r="P15" t="str">
+        <v>f62a31a0-1e5f-4f5c-a292-a1fcf8d4ec0d</v>
+      </c>
+      <c r="Q15" t="str">
+        <v>scheduled</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>763a236c-0f48-4bbf-9c26-f42b9e1f3b23</v>
+      </c>
+      <c r="B16" t="str">
+        <v>DL / HS</v>
+      </c>
+      <c r="C16" t="str">
+        <v/>
+      </c>
+      <c r="D16" t="str">
+        <v>Hannah</v>
+      </c>
+      <c r="E16" t="str">
+        <v>DL</v>
+      </c>
+      <c r="F16" t="str">
+        <v>2026-07-03T08:45:00</v>
+      </c>
+      <c r="G16" t="str">
+        <v>2026-07-03T12:15:00</v>
+      </c>
+      <c r="H16" t="str">
+        <v>FALSE</v>
+      </c>
+      <c r="I16" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="J16" t="str">
+        <v>client-session</v>
+      </c>
+      <c r="K16" t="str">
+        <v/>
+      </c>
+      <c r="L16" t="str">
+        <v/>
+      </c>
+      <c r="M16" t="str">
+        <v/>
+      </c>
+      <c r="N16" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="O16" t="str">
+        <v>custom</v>
+      </c>
+      <c r="P16" t="str">
+        <v>f62a31a0-1e5f-4f5c-a292-a1fcf8d4ec0d</v>
+      </c>
+      <c r="Q16" t="str">
+        <v>scheduled</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>2c1e8a34-9559-4004-976d-8aeba9aaf8e4</v>
+      </c>
+      <c r="B17" t="str">
+        <v>DL / HS</v>
+      </c>
+      <c r="C17" t="str">
+        <v/>
+      </c>
+      <c r="D17" t="str">
+        <v>Hannah</v>
+      </c>
+      <c r="E17" t="str">
+        <v>DL</v>
+      </c>
+      <c r="F17" t="str">
+        <v>2026-07-06T08:45:00</v>
+      </c>
+      <c r="G17" t="str">
+        <v>2026-07-06T12:15:00</v>
+      </c>
+      <c r="H17" t="str">
+        <v>FALSE</v>
+      </c>
+      <c r="I17" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="J17" t="str">
+        <v>client-session</v>
+      </c>
+      <c r="K17" t="str">
+        <v/>
+      </c>
+      <c r="L17" t="str">
+        <v/>
+      </c>
+      <c r="M17" t="str">
+        <v/>
+      </c>
+      <c r="N17" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="O17" t="str">
+        <v>custom</v>
+      </c>
+      <c r="P17" t="str">
+        <v>f62a31a0-1e5f-4f5c-a292-a1fcf8d4ec0d</v>
+      </c>
+      <c r="Q17" t="str">
+        <v>scheduled</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>9928eeed-a398-4dd5-bd6b-dc8c4da1b8d7</v>
+      </c>
+      <c r="B18" t="str">
+        <v>DL / HS</v>
+      </c>
+      <c r="C18" t="str">
+        <v/>
+      </c>
+      <c r="D18" t="str">
+        <v>Hannah</v>
+      </c>
+      <c r="E18" t="str">
+        <v>DL</v>
+      </c>
+      <c r="F18" t="str">
+        <v>2026-07-08T08:45:00</v>
+      </c>
+      <c r="G18" t="str">
+        <v>2026-07-08T12:15:00</v>
+      </c>
+      <c r="H18" t="str">
+        <v>FALSE</v>
+      </c>
+      <c r="I18" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="J18" t="str">
+        <v>client-session</v>
+      </c>
+      <c r="K18" t="str">
+        <v/>
+      </c>
+      <c r="L18" t="str">
+        <v/>
+      </c>
+      <c r="M18" t="str">
+        <v/>
+      </c>
+      <c r="N18" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="O18" t="str">
+        <v>custom</v>
+      </c>
+      <c r="P18" t="str">
+        <v>f62a31a0-1e5f-4f5c-a292-a1fcf8d4ec0d</v>
+      </c>
+      <c r="Q18" t="str">
+        <v>scheduled</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>dec17796-748f-4b82-ac9c-4c565cc0be8f</v>
+      </c>
+      <c r="B19" t="str">
+        <v>DL / HS</v>
+      </c>
+      <c r="C19" t="str">
+        <v/>
+      </c>
+      <c r="D19" t="str">
+        <v>Hannah</v>
+      </c>
+      <c r="E19" t="str">
+        <v>DL</v>
+      </c>
+      <c r="F19" t="str">
+        <v>2026-07-10T08:45:00</v>
+      </c>
+      <c r="G19" t="str">
+        <v>2026-07-10T12:15:00</v>
+      </c>
+      <c r="H19" t="str">
+        <v>FALSE</v>
+      </c>
+      <c r="I19" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="J19" t="str">
+        <v>client-session</v>
+      </c>
+      <c r="K19" t="str">
+        <v/>
+      </c>
+      <c r="L19" t="str">
+        <v/>
+      </c>
+      <c r="M19" t="str">
+        <v/>
+      </c>
+      <c r="N19" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="O19" t="str">
+        <v>custom</v>
+      </c>
+      <c r="P19" t="str">
+        <v>f62a31a0-1e5f-4f5c-a292-a1fcf8d4ec0d</v>
+      </c>
+      <c r="Q19" t="str">
+        <v>scheduled</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>66ae4829-2942-4346-bd53-7743ae3da44e</v>
+      </c>
+      <c r="B20" t="str">
+        <v>DL / HS</v>
+      </c>
+      <c r="C20" t="str">
+        <v/>
+      </c>
+      <c r="D20" t="str">
+        <v>Hannah</v>
+      </c>
+      <c r="E20" t="str">
+        <v>DL</v>
+      </c>
+      <c r="F20" t="str">
+        <v>2026-07-13T08:45:00</v>
+      </c>
+      <c r="G20" t="str">
+        <v>2026-07-13T12:15:00</v>
+      </c>
+      <c r="H20" t="str">
+        <v>FALSE</v>
+      </c>
+      <c r="I20" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="J20" t="str">
+        <v>client-session</v>
+      </c>
+      <c r="K20" t="str">
+        <v/>
+      </c>
+      <c r="L20" t="str">
+        <v/>
+      </c>
+      <c r="M20" t="str">
+        <v/>
+      </c>
+      <c r="N20" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="O20" t="str">
+        <v>custom</v>
+      </c>
+      <c r="P20" t="str">
+        <v>f62a31a0-1e5f-4f5c-a292-a1fcf8d4ec0d</v>
+      </c>
+      <c r="Q20" t="str">
+        <v>scheduled</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>ebf3754c-44c2-4d2b-aab5-eadbef962a67</v>
+      </c>
+      <c r="B21" t="str">
+        <v>DL / HS</v>
+      </c>
+      <c r="C21" t="str">
+        <v/>
+      </c>
+      <c r="D21" t="str">
+        <v>Hannah</v>
+      </c>
+      <c r="E21" t="str">
+        <v>DL</v>
+      </c>
+      <c r="F21" t="str">
+        <v>2026-07-15T08:45:00</v>
+      </c>
+      <c r="G21" t="str">
+        <v>2026-07-15T12:15:00</v>
+      </c>
+      <c r="H21" t="str">
+        <v>FALSE</v>
+      </c>
+      <c r="I21" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="J21" t="str">
+        <v>client-session</v>
+      </c>
+      <c r="K21" t="str">
+        <v/>
+      </c>
+      <c r="L21" t="str">
+        <v/>
+      </c>
+      <c r="M21" t="str">
+        <v/>
+      </c>
+      <c r="N21" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="O21" t="str">
+        <v>custom</v>
+      </c>
+      <c r="P21" t="str">
+        <v>f62a31a0-1e5f-4f5c-a292-a1fcf8d4ec0d</v>
+      </c>
+      <c r="Q21" t="str">
+        <v>scheduled</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>fab364e2-81a5-494f-a73f-82173d7d407a</v>
+      </c>
+      <c r="B22" t="str">
+        <v>DL / HS</v>
+      </c>
+      <c r="C22" t="str">
+        <v/>
+      </c>
+      <c r="D22" t="str">
+        <v>Hannah</v>
+      </c>
+      <c r="E22" t="str">
+        <v>DL</v>
+      </c>
+      <c r="F22" t="str">
+        <v>2026-07-17T08:45:00</v>
+      </c>
+      <c r="G22" t="str">
+        <v>2026-07-17T12:15:00</v>
+      </c>
+      <c r="H22" t="str">
+        <v>FALSE</v>
+      </c>
+      <c r="I22" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="J22" t="str">
+        <v>client-session</v>
+      </c>
+      <c r="K22" t="str">
+        <v/>
+      </c>
+      <c r="L22" t="str">
+        <v/>
+      </c>
+      <c r="M22" t="str">
+        <v/>
+      </c>
+      <c r="N22" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="O22" t="str">
+        <v>custom</v>
+      </c>
+      <c r="P22" t="str">
+        <v>f62a31a0-1e5f-4f5c-a292-a1fcf8d4ec0d</v>
+      </c>
+      <c r="Q22" t="str">
+        <v>scheduled</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>c06260b9-f5c8-4c57-ab35-dd870b39048f</v>
+      </c>
+      <c r="B23" t="str">
+        <v>DL / HS</v>
+      </c>
+      <c r="C23" t="str">
+        <v/>
+      </c>
+      <c r="D23" t="str">
+        <v>Hannah</v>
+      </c>
+      <c r="E23" t="str">
+        <v>DL</v>
+      </c>
+      <c r="F23" t="str">
+        <v>2026-07-20T08:45:00</v>
+      </c>
+      <c r="G23" t="str">
+        <v>2026-07-20T12:15:00</v>
+      </c>
+      <c r="H23" t="str">
+        <v>FALSE</v>
+      </c>
+      <c r="I23" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="J23" t="str">
+        <v>client-session</v>
+      </c>
+      <c r="K23" t="str">
+        <v/>
+      </c>
+      <c r="L23" t="str">
+        <v/>
+      </c>
+      <c r="M23" t="str">
+        <v/>
+      </c>
+      <c r="N23" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="O23" t="str">
+        <v>custom</v>
+      </c>
+      <c r="P23" t="str">
+        <v>f62a31a0-1e5f-4f5c-a292-a1fcf8d4ec0d</v>
+      </c>
+      <c r="Q23" t="str">
+        <v>scheduled</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>555eefc4-7dc5-4a30-b4d5-443e12f62443</v>
+      </c>
+      <c r="B24" t="str">
+        <v>DL / HS</v>
+      </c>
+      <c r="C24" t="str">
+        <v/>
+      </c>
+      <c r="D24" t="str">
+        <v>Hannah</v>
+      </c>
+      <c r="E24" t="str">
+        <v>DL</v>
+      </c>
+      <c r="F24" t="str">
+        <v>2026-07-22T08:45:00</v>
+      </c>
+      <c r="G24" t="str">
+        <v>2026-07-22T12:15:00</v>
+      </c>
+      <c r="H24" t="str">
+        <v>FALSE</v>
+      </c>
+      <c r="I24" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="J24" t="str">
+        <v>client-session</v>
+      </c>
+      <c r="K24" t="str">
+        <v/>
+      </c>
+      <c r="L24" t="str">
+        <v/>
+      </c>
+      <c r="M24" t="str">
+        <v/>
+      </c>
+      <c r="N24" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="O24" t="str">
+        <v>custom</v>
+      </c>
+      <c r="P24" t="str">
+        <v>f62a31a0-1e5f-4f5c-a292-a1fcf8d4ec0d</v>
+      </c>
+      <c r="Q24" t="str">
+        <v>scheduled</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>9ac7761d-eda5-4af3-abe1-6fa0ea083c6f</v>
+      </c>
+      <c r="B25" t="str">
+        <v>DL / HS</v>
+      </c>
+      <c r="C25" t="str">
+        <v/>
+      </c>
+      <c r="D25" t="str">
+        <v>Hannah</v>
+      </c>
+      <c r="E25" t="str">
+        <v>DL</v>
+      </c>
+      <c r="F25" t="str">
+        <v>2026-07-24T08:45:00</v>
+      </c>
+      <c r="G25" t="str">
+        <v>2026-07-24T12:15:00</v>
+      </c>
+      <c r="H25" t="str">
+        <v>FALSE</v>
+      </c>
+      <c r="I25" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="J25" t="str">
+        <v>client-session</v>
+      </c>
+      <c r="K25" t="str">
+        <v/>
+      </c>
+      <c r="L25" t="str">
+        <v/>
+      </c>
+      <c r="M25" t="str">
+        <v/>
+      </c>
+      <c r="N25" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="O25" t="str">
+        <v>custom</v>
+      </c>
+      <c r="P25" t="str">
+        <v>f62a31a0-1e5f-4f5c-a292-a1fcf8d4ec0d</v>
+      </c>
+      <c r="Q25" t="str">
+        <v>scheduled</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>90d371f1-8431-4e60-a719-7b36a99cf3e5</v>
+      </c>
+      <c r="B26" t="str">
+        <v>DL / HS</v>
+      </c>
+      <c r="C26" t="str">
+        <v/>
+      </c>
+      <c r="D26" t="str">
+        <v>Hannah</v>
+      </c>
+      <c r="E26" t="str">
+        <v>DL</v>
+      </c>
+      <c r="F26" t="str">
+        <v>2026-07-27T08:45:00</v>
+      </c>
+      <c r="G26" t="str">
+        <v>2026-07-27T12:15:00</v>
+      </c>
+      <c r="H26" t="str">
+        <v>FALSE</v>
+      </c>
+      <c r="I26" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="J26" t="str">
+        <v>client-session</v>
+      </c>
+      <c r="K26" t="str">
+        <v/>
+      </c>
+      <c r="L26" t="str">
+        <v/>
+      </c>
+      <c r="M26" t="str">
+        <v/>
+      </c>
+      <c r="N26" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="O26" t="str">
+        <v>custom</v>
+      </c>
+      <c r="P26" t="str">
+        <v>f62a31a0-1e5f-4f5c-a292-a1fcf8d4ec0d</v>
+      </c>
+      <c r="Q26" t="str">
+        <v>scheduled</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>cd5fa09a-f55b-4630-85bc-95868f833ea2</v>
+      </c>
+      <c r="B27" t="str">
+        <v>DL / HS</v>
+      </c>
+      <c r="C27" t="str">
+        <v/>
+      </c>
+      <c r="D27" t="str">
+        <v>Hannah</v>
+      </c>
+      <c r="E27" t="str">
+        <v>DL</v>
+      </c>
+      <c r="F27" t="str">
+        <v>2026-07-29T08:45:00</v>
+      </c>
+      <c r="G27" t="str">
+        <v>2026-07-29T12:15:00</v>
+      </c>
+      <c r="H27" t="str">
+        <v>FALSE</v>
+      </c>
+      <c r="I27" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="J27" t="str">
+        <v>client-session</v>
+      </c>
+      <c r="K27" t="str">
+        <v/>
+      </c>
+      <c r="L27" t="str">
+        <v/>
+      </c>
+      <c r="M27" t="str">
+        <v/>
+      </c>
+      <c r="N27" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="O27" t="str">
+        <v>custom</v>
+      </c>
+      <c r="P27" t="str">
+        <v>f62a31a0-1e5f-4f5c-a292-a1fcf8d4ec0d</v>
+      </c>
+      <c r="Q27" t="str">
+        <v>scheduled</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>3b8727ac-16d4-4666-ad7e-a35e1d6b2c49</v>
+      </c>
+      <c r="B28" t="str">
+        <v>DL / HS</v>
+      </c>
+      <c r="C28" t="str">
+        <v/>
+      </c>
+      <c r="D28" t="str">
+        <v>Hannah</v>
+      </c>
+      <c r="E28" t="str">
+        <v>DL</v>
+      </c>
+      <c r="F28" t="str">
+        <v>2026-07-31T08:45:00</v>
+      </c>
+      <c r="G28" t="str">
+        <v>2026-07-31T12:15:00</v>
+      </c>
+      <c r="H28" t="str">
+        <v>FALSE</v>
+      </c>
+      <c r="I28" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="J28" t="str">
+        <v>client-session</v>
+      </c>
+      <c r="K28" t="str">
+        <v/>
+      </c>
+      <c r="L28" t="str">
+        <v/>
+      </c>
+      <c r="M28" t="str">
+        <v/>
+      </c>
+      <c r="N28" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="O28" t="str">
+        <v>custom</v>
+      </c>
+      <c r="P28" t="str">
+        <v>f62a31a0-1e5f-4f5c-a292-a1fcf8d4ec0d</v>
+      </c>
+      <c r="Q28" t="str">
+        <v>scheduled</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>f41b99f0-04b4-4852-9a20-1634a5a85fc2</v>
+      </c>
+      <c r="B29" t="str">
+        <v>DL / HS</v>
+      </c>
+      <c r="C29" t="str">
+        <v/>
+      </c>
+      <c r="D29" t="str">
+        <v>Hannah</v>
+      </c>
+      <c r="E29" t="str">
+        <v>DL</v>
+      </c>
+      <c r="F29" t="str">
+        <v>2026-08-03T08:45:00</v>
+      </c>
+      <c r="G29" t="str">
+        <v>2026-08-03T12:15:00</v>
+      </c>
+      <c r="H29" t="str">
+        <v>FALSE</v>
+      </c>
+      <c r="I29" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="J29" t="str">
+        <v>client-session</v>
+      </c>
+      <c r="K29" t="str">
+        <v/>
+      </c>
+      <c r="L29" t="str">
+        <v/>
+      </c>
+      <c r="M29" t="str">
+        <v/>
+      </c>
+      <c r="N29" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="O29" t="str">
+        <v>custom</v>
+      </c>
+      <c r="P29" t="str">
+        <v>f62a31a0-1e5f-4f5c-a292-a1fcf8d4ec0d</v>
+      </c>
+      <c r="Q29" t="str">
+        <v>scheduled</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>65358987-a904-4dc6-9605-0e835c45547d</v>
+      </c>
+      <c r="B30" t="str">
+        <v>DL / HS</v>
+      </c>
+      <c r="C30" t="str">
+        <v/>
+      </c>
+      <c r="D30" t="str">
+        <v>Hannah</v>
+      </c>
+      <c r="E30" t="str">
+        <v>DL</v>
+      </c>
+      <c r="F30" t="str">
+        <v>2026-08-05T08:45:00</v>
+      </c>
+      <c r="G30" t="str">
+        <v>2026-08-05T12:15:00</v>
+      </c>
+      <c r="H30" t="str">
+        <v>FALSE</v>
+      </c>
+      <c r="I30" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="J30" t="str">
+        <v>client-session</v>
+      </c>
+      <c r="K30" t="str">
+        <v/>
+      </c>
+      <c r="L30" t="str">
+        <v/>
+      </c>
+      <c r="M30" t="str">
+        <v/>
+      </c>
+      <c r="N30" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="O30" t="str">
+        <v>custom</v>
+      </c>
+      <c r="P30" t="str">
+        <v>f62a31a0-1e5f-4f5c-a292-a1fcf8d4ec0d</v>
+      </c>
+      <c r="Q30" t="str">
+        <v>scheduled</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>56ec8570-d917-468c-8c86-26a76e077d79</v>
+      </c>
+      <c r="B31" t="str">
+        <v>DL / HS</v>
+      </c>
+      <c r="C31" t="str">
+        <v/>
+      </c>
+      <c r="D31" t="str">
+        <v>Hannah</v>
+      </c>
+      <c r="E31" t="str">
+        <v>DL</v>
+      </c>
+      <c r="F31" t="str">
+        <v>2026-08-07T08:45:00</v>
+      </c>
+      <c r="G31" t="str">
+        <v>2026-08-07T12:15:00</v>
+      </c>
+      <c r="H31" t="str">
+        <v>FALSE</v>
+      </c>
+      <c r="I31" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="J31" t="str">
+        <v>client-session</v>
+      </c>
+      <c r="K31" t="str">
+        <v/>
+      </c>
+      <c r="L31" t="str">
+        <v/>
+      </c>
+      <c r="M31" t="str">
+        <v/>
+      </c>
+      <c r="N31" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="O31" t="str">
+        <v>custom</v>
+      </c>
+      <c r="P31" t="str">
+        <v>f62a31a0-1e5f-4f5c-a292-a1fcf8d4ec0d</v>
+      </c>
+      <c r="Q31" t="str">
+        <v>scheduled</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>62629255-ec8a-4fa1-b2dd-ecaf9f714379</v>
+      </c>
+      <c r="B32" t="str">
+        <v>DL / HS</v>
+      </c>
+      <c r="C32" t="str">
+        <v/>
+      </c>
+      <c r="D32" t="str">
+        <v>Hannah</v>
+      </c>
+      <c r="E32" t="str">
+        <v>DL</v>
+      </c>
+      <c r="F32" t="str">
+        <v>2026-08-10T08:45:00</v>
+      </c>
+      <c r="G32" t="str">
+        <v>2026-08-10T12:15:00</v>
+      </c>
+      <c r="H32" t="str">
+        <v>FALSE</v>
+      </c>
+      <c r="I32" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="J32" t="str">
+        <v>client-session</v>
+      </c>
+      <c r="K32" t="str">
+        <v/>
+      </c>
+      <c r="L32" t="str">
+        <v/>
+      </c>
+      <c r="M32" t="str">
+        <v/>
+      </c>
+      <c r="N32" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="O32" t="str">
+        <v>custom</v>
+      </c>
+      <c r="P32" t="str">
+        <v>f62a31a0-1e5f-4f5c-a292-a1fcf8d4ec0d</v>
+      </c>
+      <c r="Q32" t="str">
+        <v>scheduled</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>2aa6b091-af77-4dcf-bf8d-d51a6a76f657</v>
+      </c>
+      <c r="B33" t="str">
+        <v>DL / HS</v>
+      </c>
+      <c r="C33" t="str">
+        <v/>
+      </c>
+      <c r="D33" t="str">
+        <v>Hannah</v>
+      </c>
+      <c r="E33" t="str">
+        <v>DL</v>
+      </c>
+      <c r="F33" t="str">
+        <v>2026-08-12T08:45:00</v>
+      </c>
+      <c r="G33" t="str">
+        <v>2026-08-12T12:15:00</v>
+      </c>
+      <c r="H33" t="str">
+        <v>FALSE</v>
+      </c>
+      <c r="I33" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="J33" t="str">
+        <v>client-session</v>
+      </c>
+      <c r="K33" t="str">
+        <v/>
+      </c>
+      <c r="L33" t="str">
+        <v/>
+      </c>
+      <c r="M33" t="str">
+        <v/>
+      </c>
+      <c r="N33" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="O33" t="str">
+        <v>custom</v>
+      </c>
+      <c r="P33" t="str">
+        <v>f62a31a0-1e5f-4f5c-a292-a1fcf8d4ec0d</v>
+      </c>
+      <c r="Q33" t="str">
+        <v>scheduled</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G1"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:Q33"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/public-assets/sample_schedule.xlsx
+++ b/public-assets/sample_schedule.xlsx
@@ -444,7 +444,7 @@
         <v>2026-06-13T19:13:46.679Z</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-07-06T21:53:38.828Z</v>
+        <v>2026-07-09T03:31:11.965Z</v>
       </c>
       <c r="E2" t="str">
         <v>aba-dashboard</v>
@@ -777,7 +777,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L13"/>
+  <dimension ref="A1:Q13"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -816,6 +816,21 @@
       <c r="L1" t="str">
         <v>city</v>
       </c>
+      <c r="M1" t="str">
+        <v>supervisionStyle</v>
+      </c>
+      <c r="N1" t="str">
+        <v>preferredDaypart</v>
+      </c>
+      <c r="O1" t="str">
+        <v>hintNote</v>
+      </c>
+      <c r="P1" t="str">
+        <v>archived</v>
+      </c>
+      <c r="Q1" t="str">
+        <v>archivedAsOf</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
@@ -854,6 +869,21 @@
       <c r="L2" t="str">
         <v>Springfield, IL</v>
       </c>
+      <c r="M2" t="str">
+        <v/>
+      </c>
+      <c r="N2" t="str">
+        <v/>
+      </c>
+      <c r="O2" t="str">
+        <v/>
+      </c>
+      <c r="P2" t="str">
+        <v/>
+      </c>
+      <c r="Q2" t="str">
+        <v/>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
@@ -892,6 +922,21 @@
       <c r="L3" t="str">
         <v>Springfield, IL</v>
       </c>
+      <c r="M3" t="str">
+        <v/>
+      </c>
+      <c r="N3" t="str">
+        <v/>
+      </c>
+      <c r="O3" t="str">
+        <v/>
+      </c>
+      <c r="P3" t="str">
+        <v/>
+      </c>
+      <c r="Q3" t="str">
+        <v/>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
@@ -930,6 +975,21 @@
       <c r="L4" t="str">
         <v>Springfield, IL</v>
       </c>
+      <c r="M4" t="str">
+        <v/>
+      </c>
+      <c r="N4" t="str">
+        <v/>
+      </c>
+      <c r="O4" t="str">
+        <v/>
+      </c>
+      <c r="P4" t="str">
+        <v/>
+      </c>
+      <c r="Q4" t="str">
+        <v/>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
@@ -968,6 +1028,21 @@
       <c r="L5" t="str">
         <v>Shelbyville, IL</v>
       </c>
+      <c r="M5" t="str">
+        <v/>
+      </c>
+      <c r="N5" t="str">
+        <v/>
+      </c>
+      <c r="O5" t="str">
+        <v/>
+      </c>
+      <c r="P5" t="str">
+        <v/>
+      </c>
+      <c r="Q5" t="str">
+        <v/>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
@@ -1006,6 +1081,21 @@
       <c r="L6" t="str">
         <v>Springfield, IL</v>
       </c>
+      <c r="M6" t="str">
+        <v/>
+      </c>
+      <c r="N6" t="str">
+        <v/>
+      </c>
+      <c r="O6" t="str">
+        <v/>
+      </c>
+      <c r="P6" t="str">
+        <v/>
+      </c>
+      <c r="Q6" t="str">
+        <v/>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
@@ -1044,6 +1134,21 @@
       <c r="L7" t="str">
         <v>Springfield, IL</v>
       </c>
+      <c r="M7" t="str">
+        <v/>
+      </c>
+      <c r="N7" t="str">
+        <v/>
+      </c>
+      <c r="O7" t="str">
+        <v/>
+      </c>
+      <c r="P7" t="str">
+        <v/>
+      </c>
+      <c r="Q7" t="str">
+        <v/>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
@@ -1082,6 +1187,21 @@
       <c r="L8" t="str">
         <v>Springfield, IL</v>
       </c>
+      <c r="M8" t="str">
+        <v/>
+      </c>
+      <c r="N8" t="str">
+        <v/>
+      </c>
+      <c r="O8" t="str">
+        <v/>
+      </c>
+      <c r="P8" t="str">
+        <v/>
+      </c>
+      <c r="Q8" t="str">
+        <v/>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
@@ -1120,6 +1240,21 @@
       <c r="L9" t="str">
         <v>Shelbyville, IL</v>
       </c>
+      <c r="M9" t="str">
+        <v/>
+      </c>
+      <c r="N9" t="str">
+        <v/>
+      </c>
+      <c r="O9" t="str">
+        <v/>
+      </c>
+      <c r="P9" t="str">
+        <v/>
+      </c>
+      <c r="Q9" t="str">
+        <v/>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
@@ -1158,6 +1293,21 @@
       <c r="L10" t="str">
         <v>Springfield, IL</v>
       </c>
+      <c r="M10" t="str">
+        <v/>
+      </c>
+      <c r="N10" t="str">
+        <v/>
+      </c>
+      <c r="O10" t="str">
+        <v/>
+      </c>
+      <c r="P10" t="str">
+        <v/>
+      </c>
+      <c r="Q10" t="str">
+        <v/>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
@@ -1196,6 +1346,21 @@
       <c r="L11" t="str">
         <v>Springfield, IL</v>
       </c>
+      <c r="M11" t="str">
+        <v/>
+      </c>
+      <c r="N11" t="str">
+        <v/>
+      </c>
+      <c r="O11" t="str">
+        <v/>
+      </c>
+      <c r="P11" t="str">
+        <v/>
+      </c>
+      <c r="Q11" t="str">
+        <v/>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
@@ -1234,6 +1399,21 @@
       <c r="L12" t="str">
         <v>Springfield, IL</v>
       </c>
+      <c r="M12" t="str">
+        <v/>
+      </c>
+      <c r="N12" t="str">
+        <v/>
+      </c>
+      <c r="O12" t="str">
+        <v/>
+      </c>
+      <c r="P12" t="str">
+        <v/>
+      </c>
+      <c r="Q12" t="str">
+        <v/>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
@@ -1272,10 +1452,25 @@
       <c r="L13" t="str">
         <v>Shelbyville, IL</v>
       </c>
+      <c r="M13" t="str">
+        <v/>
+      </c>
+      <c r="N13" t="str">
+        <v/>
+      </c>
+      <c r="O13" t="str">
+        <v/>
+      </c>
+      <c r="P13" t="str">
+        <v/>
+      </c>
+      <c r="Q13" t="str">
+        <v/>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L13"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:Q13"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -4078,7 +4273,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AS2"/>
+  <dimension ref="A1:AW2"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -4184,36 +4379,48 @@
         <v>bcbaOtherHours</v>
       </c>
       <c r="AI1" t="str">
+        <v>minSessionSupervision</v>
+      </c>
+      <c r="AJ1" t="str">
+        <v>minSessionParentTraining</v>
+      </c>
+      <c r="AK1" t="str">
+        <v>minSessionCasePlanning</v>
+      </c>
+      <c r="AL1" t="str">
+        <v>minSessionClientSession</v>
+      </c>
+      <c r="AM1" t="str">
         <v>homeBaseLabel</v>
       </c>
-      <c r="AJ1" t="str">
+      <c r="AN1" t="str">
         <v>homeBaseAddress</v>
       </c>
-      <c r="AK1" t="str">
+      <c r="AO1" t="str">
         <v>homeBaseCity</v>
       </c>
-      <c r="AL1" t="str">
+      <c r="AP1" t="str">
         <v>homeBaseLat</v>
       </c>
-      <c r="AM1" t="str">
+      <c r="AQ1" t="str">
         <v>homeBaseLng</v>
       </c>
-      <c r="AN1" t="str">
+      <c r="AR1" t="str">
         <v>travelEnabled</v>
       </c>
-      <c r="AO1" t="str">
+      <c r="AS1" t="str">
         <v>travelWithinCityMin</v>
       </c>
-      <c r="AP1" t="str">
+      <c r="AT1" t="str">
         <v>travelPadPercent</v>
       </c>
-      <c r="AQ1" t="str">
+      <c r="AU1" t="str">
         <v>travelAvgSpeedMph</v>
       </c>
-      <c r="AR1" t="str">
+      <c r="AV1" t="str">
         <v>travelDefaultUnknownMin</v>
       </c>
-      <c r="AS1" t="str">
+      <c r="AW1" t="str">
         <v>travelHourBucketSize</v>
       </c>
     </row>
@@ -4320,43 +4527,55 @@
       <c r="AH2" t="str">
         <v/>
       </c>
-      <c r="AI2" t="str">
+      <c r="AI2">
+        <v>30</v>
+      </c>
+      <c r="AJ2">
+        <v>30</v>
+      </c>
+      <c r="AK2">
+        <v>30</v>
+      </c>
+      <c r="AL2">
+        <v>30</v>
+      </c>
+      <c r="AM2" t="str">
         <v>Home</v>
       </c>
-      <c r="AJ2" t="str">
+      <c r="AN2" t="str">
         <v>100 Center St, Springfield, IL</v>
       </c>
-      <c r="AK2" t="str">
+      <c r="AO2" t="str">
         <v>Springfield, IL</v>
       </c>
-      <c r="AL2">
+      <c r="AP2">
         <v>39.7817</v>
       </c>
-      <c r="AM2">
+      <c r="AQ2">
         <v>-89.6501</v>
       </c>
-      <c r="AN2" t="str">
+      <c r="AR2" t="str">
         <v>FALSE</v>
       </c>
-      <c r="AO2">
+      <c r="AS2">
         <v>15</v>
       </c>
-      <c r="AP2">
+      <c r="AT2">
         <v>5</v>
       </c>
-      <c r="AQ2">
+      <c r="AU2">
         <v>30</v>
       </c>
-      <c r="AR2">
+      <c r="AV2">
         <v>45</v>
       </c>
-      <c r="AS2">
+      <c r="AW2">
         <v>1</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:AS2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:AW2"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -5251,7 +5470,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Q33"/>
+  <dimension ref="A1:S33"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -5267,42 +5486,48 @@
         <v>technician</v>
       </c>
       <c r="E1" t="str">
+        <v>technicianName</v>
+      </c>
+      <c r="F1" t="str">
         <v>client</v>
       </c>
-      <c r="F1" t="str">
+      <c r="G1" t="str">
+        <v>clientName</v>
+      </c>
+      <c r="H1" t="str">
         <v>startTime</v>
       </c>
-      <c r="G1" t="str">
+      <c r="I1" t="str">
         <v>endTime</v>
       </c>
-      <c r="H1" t="str">
+      <c r="J1" t="str">
         <v>isFixed</v>
       </c>
-      <c r="I1" t="str">
+      <c r="K1" t="str">
         <v>isBillable</v>
       </c>
-      <c r="J1" t="str">
+      <c r="L1" t="str">
         <v>type</v>
       </c>
-      <c r="K1" t="str">
+      <c r="M1" t="str">
         <v>isMakeUp</v>
       </c>
-      <c r="L1" t="str">
+      <c r="N1" t="str">
         <v>makeupForId</v>
       </c>
-      <c r="M1" t="str">
+      <c r="O1" t="str">
         <v>isGhost</v>
       </c>
-      <c r="N1" t="str">
+      <c r="P1" t="str">
         <v>isRecurring</v>
       </c>
-      <c r="O1" t="str">
+      <c r="Q1" t="str">
         <v>recurringPattern</v>
       </c>
-      <c r="P1" t="str">
+      <c r="R1" t="str">
         <v>seriesId</v>
       </c>
-      <c r="Q1" t="str">
+      <c r="S1" t="str">
         <v>status</v>
       </c>
     </row>
@@ -5320,42 +5545,48 @@
         <v>Hannah</v>
       </c>
       <c r="E2" t="str">
+        <v/>
+      </c>
+      <c r="F2" t="str">
         <v>DL</v>
       </c>
-      <c r="F2" t="str">
+      <c r="G2" t="str">
+        <v/>
+      </c>
+      <c r="H2" t="str">
         <v>2026-06-01T08:45:00</v>
       </c>
-      <c r="G2" t="str">
+      <c r="I2" t="str">
         <v>2026-06-01T12:15:00</v>
       </c>
-      <c r="H2" t="str">
+      <c r="J2" t="str">
         <v>FALSE</v>
       </c>
-      <c r="I2" t="str">
+      <c r="K2" t="str">
         <v>TRUE</v>
       </c>
-      <c r="J2" t="str">
+      <c r="L2" t="str">
         <v>client-session</v>
       </c>
-      <c r="K2" t="str">
-        <v/>
-      </c>
-      <c r="L2" t="str">
-        <v/>
-      </c>
       <c r="M2" t="str">
         <v/>
       </c>
       <c r="N2" t="str">
+        <v/>
+      </c>
+      <c r="O2" t="str">
+        <v/>
+      </c>
+      <c r="P2" t="str">
         <v>TRUE</v>
       </c>
-      <c r="O2" t="str">
+      <c r="Q2" t="str">
         <v>custom</v>
       </c>
-      <c r="P2" t="str">
+      <c r="R2" t="str">
         <v>f62a31a0-1e5f-4f5c-a292-a1fcf8d4ec0d</v>
       </c>
-      <c r="Q2" t="str">
+      <c r="S2" t="str">
         <v>scheduled</v>
       </c>
     </row>
@@ -5373,42 +5604,48 @@
         <v>Hannah</v>
       </c>
       <c r="E3" t="str">
+        <v/>
+      </c>
+      <c r="F3" t="str">
         <v>DL</v>
       </c>
-      <c r="F3" t="str">
+      <c r="G3" t="str">
+        <v/>
+      </c>
+      <c r="H3" t="str">
         <v>2026-06-03T08:45:00</v>
       </c>
-      <c r="G3" t="str">
+      <c r="I3" t="str">
         <v>2026-06-03T12:15:00</v>
       </c>
-      <c r="H3" t="str">
+      <c r="J3" t="str">
         <v>FALSE</v>
       </c>
-      <c r="I3" t="str">
+      <c r="K3" t="str">
         <v>TRUE</v>
       </c>
-      <c r="J3" t="str">
+      <c r="L3" t="str">
         <v>client-session</v>
       </c>
-      <c r="K3" t="str">
-        <v/>
-      </c>
-      <c r="L3" t="str">
-        <v/>
-      </c>
       <c r="M3" t="str">
         <v/>
       </c>
       <c r="N3" t="str">
+        <v/>
+      </c>
+      <c r="O3" t="str">
+        <v/>
+      </c>
+      <c r="P3" t="str">
         <v>TRUE</v>
       </c>
-      <c r="O3" t="str">
+      <c r="Q3" t="str">
         <v>custom</v>
       </c>
-      <c r="P3" t="str">
+      <c r="R3" t="str">
         <v>f62a31a0-1e5f-4f5c-a292-a1fcf8d4ec0d</v>
       </c>
-      <c r="Q3" t="str">
+      <c r="S3" t="str">
         <v>scheduled</v>
       </c>
     </row>
@@ -5426,42 +5663,48 @@
         <v>Hannah</v>
       </c>
       <c r="E4" t="str">
+        <v/>
+      </c>
+      <c r="F4" t="str">
         <v>DL</v>
       </c>
-      <c r="F4" t="str">
+      <c r="G4" t="str">
+        <v/>
+      </c>
+      <c r="H4" t="str">
         <v>2026-06-05T08:45:00</v>
       </c>
-      <c r="G4" t="str">
+      <c r="I4" t="str">
         <v>2026-06-05T12:15:00</v>
       </c>
-      <c r="H4" t="str">
+      <c r="J4" t="str">
         <v>FALSE</v>
       </c>
-      <c r="I4" t="str">
+      <c r="K4" t="str">
         <v>TRUE</v>
       </c>
-      <c r="J4" t="str">
+      <c r="L4" t="str">
         <v>client-session</v>
       </c>
-      <c r="K4" t="str">
-        <v/>
-      </c>
-      <c r="L4" t="str">
-        <v/>
-      </c>
       <c r="M4" t="str">
         <v/>
       </c>
       <c r="N4" t="str">
+        <v/>
+      </c>
+      <c r="O4" t="str">
+        <v/>
+      </c>
+      <c r="P4" t="str">
         <v>TRUE</v>
       </c>
-      <c r="O4" t="str">
+      <c r="Q4" t="str">
         <v>custom</v>
       </c>
-      <c r="P4" t="str">
+      <c r="R4" t="str">
         <v>f62a31a0-1e5f-4f5c-a292-a1fcf8d4ec0d</v>
       </c>
-      <c r="Q4" t="str">
+      <c r="S4" t="str">
         <v>scheduled</v>
       </c>
     </row>
@@ -5479,42 +5722,48 @@
         <v>Hannah</v>
       </c>
       <c r="E5" t="str">
+        <v/>
+      </c>
+      <c r="F5" t="str">
         <v>DL</v>
       </c>
-      <c r="F5" t="str">
+      <c r="G5" t="str">
+        <v/>
+      </c>
+      <c r="H5" t="str">
         <v>2026-06-08T08:45:00</v>
       </c>
-      <c r="G5" t="str">
+      <c r="I5" t="str">
         <v>2026-06-08T12:15:00</v>
       </c>
-      <c r="H5" t="str">
+      <c r="J5" t="str">
         <v>FALSE</v>
       </c>
-      <c r="I5" t="str">
+      <c r="K5" t="str">
         <v>TRUE</v>
       </c>
-      <c r="J5" t="str">
+      <c r="L5" t="str">
         <v>client-session</v>
       </c>
-      <c r="K5" t="str">
-        <v/>
-      </c>
-      <c r="L5" t="str">
-        <v/>
-      </c>
       <c r="M5" t="str">
         <v/>
       </c>
       <c r="N5" t="str">
+        <v/>
+      </c>
+      <c r="O5" t="str">
+        <v/>
+      </c>
+      <c r="P5" t="str">
         <v>TRUE</v>
       </c>
-      <c r="O5" t="str">
+      <c r="Q5" t="str">
         <v>custom</v>
       </c>
-      <c r="P5" t="str">
+      <c r="R5" t="str">
         <v>f62a31a0-1e5f-4f5c-a292-a1fcf8d4ec0d</v>
       </c>
-      <c r="Q5" t="str">
+      <c r="S5" t="str">
         <v>scheduled</v>
       </c>
     </row>
@@ -5532,42 +5781,48 @@
         <v>Hannah</v>
       </c>
       <c r="E6" t="str">
+        <v/>
+      </c>
+      <c r="F6" t="str">
         <v>DL</v>
       </c>
-      <c r="F6" t="str">
+      <c r="G6" t="str">
+        <v/>
+      </c>
+      <c r="H6" t="str">
         <v>2026-06-10T08:45:00</v>
       </c>
-      <c r="G6" t="str">
+      <c r="I6" t="str">
         <v>2026-06-10T12:15:00</v>
       </c>
-      <c r="H6" t="str">
+      <c r="J6" t="str">
         <v>FALSE</v>
       </c>
-      <c r="I6" t="str">
+      <c r="K6" t="str">
         <v>TRUE</v>
       </c>
-      <c r="J6" t="str">
+      <c r="L6" t="str">
         <v>client-session</v>
       </c>
-      <c r="K6" t="str">
-        <v/>
-      </c>
-      <c r="L6" t="str">
-        <v/>
-      </c>
       <c r="M6" t="str">
         <v/>
       </c>
       <c r="N6" t="str">
+        <v/>
+      </c>
+      <c r="O6" t="str">
+        <v/>
+      </c>
+      <c r="P6" t="str">
         <v>TRUE</v>
       </c>
-      <c r="O6" t="str">
+      <c r="Q6" t="str">
         <v>custom</v>
       </c>
-      <c r="P6" t="str">
+      <c r="R6" t="str">
         <v>f62a31a0-1e5f-4f5c-a292-a1fcf8d4ec0d</v>
       </c>
-      <c r="Q6" t="str">
+      <c r="S6" t="str">
         <v>scheduled</v>
       </c>
     </row>
@@ -5585,42 +5840,48 @@
         <v>Hannah</v>
       </c>
       <c r="E7" t="str">
+        <v/>
+      </c>
+      <c r="F7" t="str">
         <v>DL</v>
       </c>
-      <c r="F7" t="str">
+      <c r="G7" t="str">
+        <v/>
+      </c>
+      <c r="H7" t="str">
         <v>2026-06-12T08:45:00</v>
       </c>
-      <c r="G7" t="str">
+      <c r="I7" t="str">
         <v>2026-06-12T12:15:00</v>
       </c>
-      <c r="H7" t="str">
+      <c r="J7" t="str">
         <v>FALSE</v>
       </c>
-      <c r="I7" t="str">
+      <c r="K7" t="str">
         <v>TRUE</v>
       </c>
-      <c r="J7" t="str">
+      <c r="L7" t="str">
         <v>client-session</v>
       </c>
-      <c r="K7" t="str">
-        <v/>
-      </c>
-      <c r="L7" t="str">
-        <v/>
-      </c>
       <c r="M7" t="str">
         <v/>
       </c>
       <c r="N7" t="str">
+        <v/>
+      </c>
+      <c r="O7" t="str">
+        <v/>
+      </c>
+      <c r="P7" t="str">
         <v>TRUE</v>
       </c>
-      <c r="O7" t="str">
+      <c r="Q7" t="str">
         <v>custom</v>
       </c>
-      <c r="P7" t="str">
+      <c r="R7" t="str">
         <v>f62a31a0-1e5f-4f5c-a292-a1fcf8d4ec0d</v>
       </c>
-      <c r="Q7" t="str">
+      <c r="S7" t="str">
         <v>scheduled</v>
       </c>
     </row>
@@ -5638,42 +5899,48 @@
         <v>Hannah</v>
       </c>
       <c r="E8" t="str">
+        <v/>
+      </c>
+      <c r="F8" t="str">
         <v>DL</v>
       </c>
-      <c r="F8" t="str">
+      <c r="G8" t="str">
+        <v/>
+      </c>
+      <c r="H8" t="str">
         <v>2026-06-15T08:45:00</v>
       </c>
-      <c r="G8" t="str">
+      <c r="I8" t="str">
         <v>2026-06-15T12:15:00</v>
       </c>
-      <c r="H8" t="str">
+      <c r="J8" t="str">
         <v>FALSE</v>
       </c>
-      <c r="I8" t="str">
+      <c r="K8" t="str">
         <v>TRUE</v>
       </c>
-      <c r="J8" t="str">
+      <c r="L8" t="str">
         <v>client-session</v>
       </c>
-      <c r="K8" t="str">
-        <v/>
-      </c>
-      <c r="L8" t="str">
-        <v/>
-      </c>
       <c r="M8" t="str">
         <v/>
       </c>
       <c r="N8" t="str">
+        <v/>
+      </c>
+      <c r="O8" t="str">
+        <v/>
+      </c>
+      <c r="P8" t="str">
         <v>TRUE</v>
       </c>
-      <c r="O8" t="str">
+      <c r="Q8" t="str">
         <v>custom</v>
       </c>
-      <c r="P8" t="str">
+      <c r="R8" t="str">
         <v>f62a31a0-1e5f-4f5c-a292-a1fcf8d4ec0d</v>
       </c>
-      <c r="Q8" t="str">
+      <c r="S8" t="str">
         <v>scheduled</v>
       </c>
     </row>
@@ -5691,42 +5958,48 @@
         <v>Hannah</v>
       </c>
       <c r="E9" t="str">
+        <v/>
+      </c>
+      <c r="F9" t="str">
         <v>DL</v>
       </c>
-      <c r="F9" t="str">
+      <c r="G9" t="str">
+        <v/>
+      </c>
+      <c r="H9" t="str">
         <v>2026-06-17T08:45:00</v>
       </c>
-      <c r="G9" t="str">
+      <c r="I9" t="str">
         <v>2026-06-17T12:15:00</v>
       </c>
-      <c r="H9" t="str">
+      <c r="J9" t="str">
         <v>FALSE</v>
       </c>
-      <c r="I9" t="str">
+      <c r="K9" t="str">
         <v>TRUE</v>
       </c>
-      <c r="J9" t="str">
+      <c r="L9" t="str">
         <v>client-session</v>
       </c>
-      <c r="K9" t="str">
-        <v/>
-      </c>
-      <c r="L9" t="str">
-        <v/>
-      </c>
       <c r="M9" t="str">
         <v/>
       </c>
       <c r="N9" t="str">
+        <v/>
+      </c>
+      <c r="O9" t="str">
+        <v/>
+      </c>
+      <c r="P9" t="str">
         <v>TRUE</v>
       </c>
-      <c r="O9" t="str">
+      <c r="Q9" t="str">
         <v>custom</v>
       </c>
-      <c r="P9" t="str">
+      <c r="R9" t="str">
         <v>f62a31a0-1e5f-4f5c-a292-a1fcf8d4ec0d</v>
       </c>
-      <c r="Q9" t="str">
+      <c r="S9" t="str">
         <v>scheduled</v>
       </c>
     </row>
@@ -5744,42 +6017,48 @@
         <v>Hannah</v>
       </c>
       <c r="E10" t="str">
+        <v/>
+      </c>
+      <c r="F10" t="str">
         <v>DL</v>
       </c>
-      <c r="F10" t="str">
+      <c r="G10" t="str">
+        <v/>
+      </c>
+      <c r="H10" t="str">
         <v>2026-06-19T08:45:00</v>
       </c>
-      <c r="G10" t="str">
+      <c r="I10" t="str">
         <v>2026-06-19T12:15:00</v>
       </c>
-      <c r="H10" t="str">
+      <c r="J10" t="str">
         <v>FALSE</v>
       </c>
-      <c r="I10" t="str">
+      <c r="K10" t="str">
         <v>TRUE</v>
       </c>
-      <c r="J10" t="str">
+      <c r="L10" t="str">
         <v>client-session</v>
       </c>
-      <c r="K10" t="str">
-        <v/>
-      </c>
-      <c r="L10" t="str">
-        <v/>
-      </c>
       <c r="M10" t="str">
         <v/>
       </c>
       <c r="N10" t="str">
+        <v/>
+      </c>
+      <c r="O10" t="str">
+        <v/>
+      </c>
+      <c r="P10" t="str">
         <v>TRUE</v>
       </c>
-      <c r="O10" t="str">
+      <c r="Q10" t="str">
         <v>custom</v>
       </c>
-      <c r="P10" t="str">
+      <c r="R10" t="str">
         <v>f62a31a0-1e5f-4f5c-a292-a1fcf8d4ec0d</v>
       </c>
-      <c r="Q10" t="str">
+      <c r="S10" t="str">
         <v>scheduled</v>
       </c>
     </row>
@@ -5797,42 +6076,48 @@
         <v>Hannah</v>
       </c>
       <c r="E11" t="str">
+        <v/>
+      </c>
+      <c r="F11" t="str">
         <v>DL</v>
       </c>
-      <c r="F11" t="str">
+      <c r="G11" t="str">
+        <v/>
+      </c>
+      <c r="H11" t="str">
         <v>2026-06-22T08:45:00</v>
       </c>
-      <c r="G11" t="str">
+      <c r="I11" t="str">
         <v>2026-06-22T12:15:00</v>
       </c>
-      <c r="H11" t="str">
+      <c r="J11" t="str">
         <v>FALSE</v>
       </c>
-      <c r="I11" t="str">
+      <c r="K11" t="str">
         <v>TRUE</v>
       </c>
-      <c r="J11" t="str">
+      <c r="L11" t="str">
         <v>client-session</v>
       </c>
-      <c r="K11" t="str">
-        <v/>
-      </c>
-      <c r="L11" t="str">
-        <v/>
-      </c>
       <c r="M11" t="str">
         <v/>
       </c>
       <c r="N11" t="str">
+        <v/>
+      </c>
+      <c r="O11" t="str">
+        <v/>
+      </c>
+      <c r="P11" t="str">
         <v>TRUE</v>
       </c>
-      <c r="O11" t="str">
+      <c r="Q11" t="str">
         <v>custom</v>
       </c>
-      <c r="P11" t="str">
+      <c r="R11" t="str">
         <v>f62a31a0-1e5f-4f5c-a292-a1fcf8d4ec0d</v>
       </c>
-      <c r="Q11" t="str">
+      <c r="S11" t="str">
         <v>scheduled</v>
       </c>
     </row>
@@ -5850,42 +6135,48 @@
         <v>Hannah</v>
       </c>
       <c r="E12" t="str">
+        <v/>
+      </c>
+      <c r="F12" t="str">
         <v>DL</v>
       </c>
-      <c r="F12" t="str">
+      <c r="G12" t="str">
+        <v/>
+      </c>
+      <c r="H12" t="str">
         <v>2026-06-24T08:45:00</v>
       </c>
-      <c r="G12" t="str">
+      <c r="I12" t="str">
         <v>2026-06-24T12:15:00</v>
       </c>
-      <c r="H12" t="str">
+      <c r="J12" t="str">
         <v>FALSE</v>
       </c>
-      <c r="I12" t="str">
+      <c r="K12" t="str">
         <v>TRUE</v>
       </c>
-      <c r="J12" t="str">
+      <c r="L12" t="str">
         <v>client-session</v>
       </c>
-      <c r="K12" t="str">
-        <v/>
-      </c>
-      <c r="L12" t="str">
-        <v/>
-      </c>
       <c r="M12" t="str">
         <v/>
       </c>
       <c r="N12" t="str">
+        <v/>
+      </c>
+      <c r="O12" t="str">
+        <v/>
+      </c>
+      <c r="P12" t="str">
         <v>TRUE</v>
       </c>
-      <c r="O12" t="str">
+      <c r="Q12" t="str">
         <v>custom</v>
       </c>
-      <c r="P12" t="str">
+      <c r="R12" t="str">
         <v>f62a31a0-1e5f-4f5c-a292-a1fcf8d4ec0d</v>
       </c>
-      <c r="Q12" t="str">
+      <c r="S12" t="str">
         <v>scheduled</v>
       </c>
     </row>
@@ -5903,42 +6194,48 @@
         <v>Hannah</v>
       </c>
       <c r="E13" t="str">
+        <v/>
+      </c>
+      <c r="F13" t="str">
         <v>DL</v>
       </c>
-      <c r="F13" t="str">
+      <c r="G13" t="str">
+        <v/>
+      </c>
+      <c r="H13" t="str">
         <v>2026-06-26T08:45:00</v>
       </c>
-      <c r="G13" t="str">
+      <c r="I13" t="str">
         <v>2026-06-26T12:15:00</v>
       </c>
-      <c r="H13" t="str">
+      <c r="J13" t="str">
         <v>FALSE</v>
       </c>
-      <c r="I13" t="str">
+      <c r="K13" t="str">
         <v>TRUE</v>
       </c>
-      <c r="J13" t="str">
+      <c r="L13" t="str">
         <v>client-session</v>
       </c>
-      <c r="K13" t="str">
-        <v/>
-      </c>
-      <c r="L13" t="str">
-        <v/>
-      </c>
       <c r="M13" t="str">
         <v/>
       </c>
       <c r="N13" t="str">
+        <v/>
+      </c>
+      <c r="O13" t="str">
+        <v/>
+      </c>
+      <c r="P13" t="str">
         <v>TRUE</v>
       </c>
-      <c r="O13" t="str">
+      <c r="Q13" t="str">
         <v>custom</v>
       </c>
-      <c r="P13" t="str">
+      <c r="R13" t="str">
         <v>f62a31a0-1e5f-4f5c-a292-a1fcf8d4ec0d</v>
       </c>
-      <c r="Q13" t="str">
+      <c r="S13" t="str">
         <v>scheduled</v>
       </c>
     </row>
@@ -5956,42 +6253,48 @@
         <v>Hannah</v>
       </c>
       <c r="E14" t="str">
+        <v/>
+      </c>
+      <c r="F14" t="str">
         <v>DL</v>
       </c>
-      <c r="F14" t="str">
+      <c r="G14" t="str">
+        <v/>
+      </c>
+      <c r="H14" t="str">
         <v>2026-06-29T08:45:00</v>
       </c>
-      <c r="G14" t="str">
+      <c r="I14" t="str">
         <v>2026-06-29T12:15:00</v>
       </c>
-      <c r="H14" t="str">
+      <c r="J14" t="str">
         <v>FALSE</v>
       </c>
-      <c r="I14" t="str">
+      <c r="K14" t="str">
         <v>TRUE</v>
       </c>
-      <c r="J14" t="str">
+      <c r="L14" t="str">
         <v>client-session</v>
       </c>
-      <c r="K14" t="str">
-        <v/>
-      </c>
-      <c r="L14" t="str">
-        <v/>
-      </c>
       <c r="M14" t="str">
         <v/>
       </c>
       <c r="N14" t="str">
+        <v/>
+      </c>
+      <c r="O14" t="str">
+        <v/>
+      </c>
+      <c r="P14" t="str">
         <v>TRUE</v>
       </c>
-      <c r="O14" t="str">
+      <c r="Q14" t="str">
         <v>custom</v>
       </c>
-      <c r="P14" t="str">
+      <c r="R14" t="str">
         <v>f62a31a0-1e5f-4f5c-a292-a1fcf8d4ec0d</v>
       </c>
-      <c r="Q14" t="str">
+      <c r="S14" t="str">
         <v>scheduled</v>
       </c>
     </row>
@@ -6009,42 +6312,48 @@
         <v>Hannah</v>
       </c>
       <c r="E15" t="str">
+        <v/>
+      </c>
+      <c r="F15" t="str">
         <v>DL</v>
       </c>
-      <c r="F15" t="str">
+      <c r="G15" t="str">
+        <v/>
+      </c>
+      <c r="H15" t="str">
         <v>2026-07-01T08:45:00</v>
       </c>
-      <c r="G15" t="str">
+      <c r="I15" t="str">
         <v>2026-07-01T12:15:00</v>
       </c>
-      <c r="H15" t="str">
+      <c r="J15" t="str">
         <v>FALSE</v>
       </c>
-      <c r="I15" t="str">
+      <c r="K15" t="str">
         <v>TRUE</v>
       </c>
-      <c r="J15" t="str">
+      <c r="L15" t="str">
         <v>client-session</v>
       </c>
-      <c r="K15" t="str">
-        <v/>
-      </c>
-      <c r="L15" t="str">
-        <v/>
-      </c>
       <c r="M15" t="str">
         <v/>
       </c>
       <c r="N15" t="str">
+        <v/>
+      </c>
+      <c r="O15" t="str">
+        <v/>
+      </c>
+      <c r="P15" t="str">
         <v>TRUE</v>
       </c>
-      <c r="O15" t="str">
+      <c r="Q15" t="str">
         <v>custom</v>
       </c>
-      <c r="P15" t="str">
+      <c r="R15" t="str">
         <v>f62a31a0-1e5f-4f5c-a292-a1fcf8d4ec0d</v>
       </c>
-      <c r="Q15" t="str">
+      <c r="S15" t="str">
         <v>scheduled</v>
       </c>
     </row>
@@ -6062,42 +6371,48 @@
         <v>Hannah</v>
       </c>
       <c r="E16" t="str">
+        <v/>
+      </c>
+      <c r="F16" t="str">
         <v>DL</v>
       </c>
-      <c r="F16" t="str">
+      <c r="G16" t="str">
+        <v/>
+      </c>
+      <c r="H16" t="str">
         <v>2026-07-03T08:45:00</v>
       </c>
-      <c r="G16" t="str">
+      <c r="I16" t="str">
         <v>2026-07-03T12:15:00</v>
       </c>
-      <c r="H16" t="str">
+      <c r="J16" t="str">
         <v>FALSE</v>
       </c>
-      <c r="I16" t="str">
+      <c r="K16" t="str">
         <v>TRUE</v>
       </c>
-      <c r="J16" t="str">
+      <c r="L16" t="str">
         <v>client-session</v>
       </c>
-      <c r="K16" t="str">
-        <v/>
-      </c>
-      <c r="L16" t="str">
-        <v/>
-      </c>
       <c r="M16" t="str">
         <v/>
       </c>
       <c r="N16" t="str">
+        <v/>
+      </c>
+      <c r="O16" t="str">
+        <v/>
+      </c>
+      <c r="P16" t="str">
         <v>TRUE</v>
       </c>
-      <c r="O16" t="str">
+      <c r="Q16" t="str">
         <v>custom</v>
       </c>
-      <c r="P16" t="str">
+      <c r="R16" t="str">
         <v>f62a31a0-1e5f-4f5c-a292-a1fcf8d4ec0d</v>
       </c>
-      <c r="Q16" t="str">
+      <c r="S16" t="str">
         <v>scheduled</v>
       </c>
     </row>
@@ -6115,42 +6430,48 @@
         <v>Hannah</v>
       </c>
       <c r="E17" t="str">
+        <v/>
+      </c>
+      <c r="F17" t="str">
         <v>DL</v>
       </c>
-      <c r="F17" t="str">
+      <c r="G17" t="str">
+        <v/>
+      </c>
+      <c r="H17" t="str">
         <v>2026-07-06T08:45:00</v>
       </c>
-      <c r="G17" t="str">
+      <c r="I17" t="str">
         <v>2026-07-06T12:15:00</v>
       </c>
-      <c r="H17" t="str">
+      <c r="J17" t="str">
         <v>FALSE</v>
       </c>
-      <c r="I17" t="str">
+      <c r="K17" t="str">
         <v>TRUE</v>
       </c>
-      <c r="J17" t="str">
+      <c r="L17" t="str">
         <v>client-session</v>
       </c>
-      <c r="K17" t="str">
-        <v/>
-      </c>
-      <c r="L17" t="str">
-        <v/>
-      </c>
       <c r="M17" t="str">
         <v/>
       </c>
       <c r="N17" t="str">
+        <v/>
+      </c>
+      <c r="O17" t="str">
+        <v/>
+      </c>
+      <c r="P17" t="str">
         <v>TRUE</v>
       </c>
-      <c r="O17" t="str">
+      <c r="Q17" t="str">
         <v>custom</v>
       </c>
-      <c r="P17" t="str">
+      <c r="R17" t="str">
         <v>f62a31a0-1e5f-4f5c-a292-a1fcf8d4ec0d</v>
       </c>
-      <c r="Q17" t="str">
+      <c r="S17" t="str">
         <v>scheduled</v>
       </c>
     </row>
@@ -6168,42 +6489,48 @@
         <v>Hannah</v>
       </c>
       <c r="E18" t="str">
+        <v/>
+      </c>
+      <c r="F18" t="str">
         <v>DL</v>
       </c>
-      <c r="F18" t="str">
+      <c r="G18" t="str">
+        <v/>
+      </c>
+      <c r="H18" t="str">
         <v>2026-07-08T08:45:00</v>
       </c>
-      <c r="G18" t="str">
+      <c r="I18" t="str">
         <v>2026-07-08T12:15:00</v>
       </c>
-      <c r="H18" t="str">
+      <c r="J18" t="str">
         <v>FALSE</v>
       </c>
-      <c r="I18" t="str">
+      <c r="K18" t="str">
         <v>TRUE</v>
       </c>
-      <c r="J18" t="str">
+      <c r="L18" t="str">
         <v>client-session</v>
       </c>
-      <c r="K18" t="str">
-        <v/>
-      </c>
-      <c r="L18" t="str">
-        <v/>
-      </c>
       <c r="M18" t="str">
         <v/>
       </c>
       <c r="N18" t="str">
+        <v/>
+      </c>
+      <c r="O18" t="str">
+        <v/>
+      </c>
+      <c r="P18" t="str">
         <v>TRUE</v>
       </c>
-      <c r="O18" t="str">
+      <c r="Q18" t="str">
         <v>custom</v>
       </c>
-      <c r="P18" t="str">
+      <c r="R18" t="str">
         <v>f62a31a0-1e5f-4f5c-a292-a1fcf8d4ec0d</v>
       </c>
-      <c r="Q18" t="str">
+      <c r="S18" t="str">
         <v>scheduled</v>
       </c>
     </row>
@@ -6221,42 +6548,48 @@
         <v>Hannah</v>
       </c>
       <c r="E19" t="str">
+        <v/>
+      </c>
+      <c r="F19" t="str">
         <v>DL</v>
       </c>
-      <c r="F19" t="str">
+      <c r="G19" t="str">
+        <v/>
+      </c>
+      <c r="H19" t="str">
         <v>2026-07-10T08:45:00</v>
       </c>
-      <c r="G19" t="str">
+      <c r="I19" t="str">
         <v>2026-07-10T12:15:00</v>
       </c>
-      <c r="H19" t="str">
+      <c r="J19" t="str">
         <v>FALSE</v>
       </c>
-      <c r="I19" t="str">
+      <c r="K19" t="str">
         <v>TRUE</v>
       </c>
-      <c r="J19" t="str">
+      <c r="L19" t="str">
         <v>client-session</v>
       </c>
-      <c r="K19" t="str">
-        <v/>
-      </c>
-      <c r="L19" t="str">
-        <v/>
-      </c>
       <c r="M19" t="str">
         <v/>
       </c>
       <c r="N19" t="str">
+        <v/>
+      </c>
+      <c r="O19" t="str">
+        <v/>
+      </c>
+      <c r="P19" t="str">
         <v>TRUE</v>
       </c>
-      <c r="O19" t="str">
+      <c r="Q19" t="str">
         <v>custom</v>
       </c>
-      <c r="P19" t="str">
+      <c r="R19" t="str">
         <v>f62a31a0-1e5f-4f5c-a292-a1fcf8d4ec0d</v>
       </c>
-      <c r="Q19" t="str">
+      <c r="S19" t="str">
         <v>scheduled</v>
       </c>
     </row>
@@ -6274,42 +6607,48 @@
         <v>Hannah</v>
       </c>
       <c r="E20" t="str">
+        <v/>
+      </c>
+      <c r="F20" t="str">
         <v>DL</v>
       </c>
-      <c r="F20" t="str">
+      <c r="G20" t="str">
+        <v/>
+      </c>
+      <c r="H20" t="str">
         <v>2026-07-13T08:45:00</v>
       </c>
-      <c r="G20" t="str">
+      <c r="I20" t="str">
         <v>2026-07-13T12:15:00</v>
       </c>
-      <c r="H20" t="str">
+      <c r="J20" t="str">
         <v>FALSE</v>
       </c>
-      <c r="I20" t="str">
+      <c r="K20" t="str">
         <v>TRUE</v>
       </c>
-      <c r="J20" t="str">
+      <c r="L20" t="str">
         <v>client-session</v>
       </c>
-      <c r="K20" t="str">
-        <v/>
-      </c>
-      <c r="L20" t="str">
-        <v/>
-      </c>
       <c r="M20" t="str">
         <v/>
       </c>
       <c r="N20" t="str">
+        <v/>
+      </c>
+      <c r="O20" t="str">
+        <v/>
+      </c>
+      <c r="P20" t="str">
         <v>TRUE</v>
       </c>
-      <c r="O20" t="str">
+      <c r="Q20" t="str">
         <v>custom</v>
       </c>
-      <c r="P20" t="str">
+      <c r="R20" t="str">
         <v>f62a31a0-1e5f-4f5c-a292-a1fcf8d4ec0d</v>
       </c>
-      <c r="Q20" t="str">
+      <c r="S20" t="str">
         <v>scheduled</v>
       </c>
     </row>
@@ -6327,42 +6666,48 @@
         <v>Hannah</v>
       </c>
       <c r="E21" t="str">
+        <v/>
+      </c>
+      <c r="F21" t="str">
         <v>DL</v>
       </c>
-      <c r="F21" t="str">
+      <c r="G21" t="str">
+        <v/>
+      </c>
+      <c r="H21" t="str">
         <v>2026-07-15T08:45:00</v>
       </c>
-      <c r="G21" t="str">
+      <c r="I21" t="str">
         <v>2026-07-15T12:15:00</v>
       </c>
-      <c r="H21" t="str">
+      <c r="J21" t="str">
         <v>FALSE</v>
       </c>
-      <c r="I21" t="str">
+      <c r="K21" t="str">
         <v>TRUE</v>
       </c>
-      <c r="J21" t="str">
+      <c r="L21" t="str">
         <v>client-session</v>
       </c>
-      <c r="K21" t="str">
-        <v/>
-      </c>
-      <c r="L21" t="str">
-        <v/>
-      </c>
       <c r="M21" t="str">
         <v/>
       </c>
       <c r="N21" t="str">
+        <v/>
+      </c>
+      <c r="O21" t="str">
+        <v/>
+      </c>
+      <c r="P21" t="str">
         <v>TRUE</v>
       </c>
-      <c r="O21" t="str">
+      <c r="Q21" t="str">
         <v>custom</v>
       </c>
-      <c r="P21" t="str">
+      <c r="R21" t="str">
         <v>f62a31a0-1e5f-4f5c-a292-a1fcf8d4ec0d</v>
       </c>
-      <c r="Q21" t="str">
+      <c r="S21" t="str">
         <v>scheduled</v>
       </c>
     </row>
@@ -6380,42 +6725,48 @@
         <v>Hannah</v>
       </c>
       <c r="E22" t="str">
+        <v/>
+      </c>
+      <c r="F22" t="str">
         <v>DL</v>
       </c>
-      <c r="F22" t="str">
+      <c r="G22" t="str">
+        <v/>
+      </c>
+      <c r="H22" t="str">
         <v>2026-07-17T08:45:00</v>
       </c>
-      <c r="G22" t="str">
+      <c r="I22" t="str">
         <v>2026-07-17T12:15:00</v>
       </c>
-      <c r="H22" t="str">
+      <c r="J22" t="str">
         <v>FALSE</v>
       </c>
-      <c r="I22" t="str">
+      <c r="K22" t="str">
         <v>TRUE</v>
       </c>
-      <c r="J22" t="str">
+      <c r="L22" t="str">
         <v>client-session</v>
       </c>
-      <c r="K22" t="str">
-        <v/>
-      </c>
-      <c r="L22" t="str">
-        <v/>
-      </c>
       <c r="M22" t="str">
         <v/>
       </c>
       <c r="N22" t="str">
+        <v/>
+      </c>
+      <c r="O22" t="str">
+        <v/>
+      </c>
+      <c r="P22" t="str">
         <v>TRUE</v>
       </c>
-      <c r="O22" t="str">
+      <c r="Q22" t="str">
         <v>custom</v>
       </c>
-      <c r="P22" t="str">
+      <c r="R22" t="str">
         <v>f62a31a0-1e5f-4f5c-a292-a1fcf8d4ec0d</v>
       </c>
-      <c r="Q22" t="str">
+      <c r="S22" t="str">
         <v>scheduled</v>
       </c>
     </row>
@@ -6433,42 +6784,48 @@
         <v>Hannah</v>
       </c>
       <c r="E23" t="str">
+        <v/>
+      </c>
+      <c r="F23" t="str">
         <v>DL</v>
       </c>
-      <c r="F23" t="str">
+      <c r="G23" t="str">
+        <v/>
+      </c>
+      <c r="H23" t="str">
         <v>2026-07-20T08:45:00</v>
       </c>
-      <c r="G23" t="str">
+      <c r="I23" t="str">
         <v>2026-07-20T12:15:00</v>
       </c>
-      <c r="H23" t="str">
+      <c r="J23" t="str">
         <v>FALSE</v>
       </c>
-      <c r="I23" t="str">
+      <c r="K23" t="str">
         <v>TRUE</v>
       </c>
-      <c r="J23" t="str">
+      <c r="L23" t="str">
         <v>client-session</v>
       </c>
-      <c r="K23" t="str">
-        <v/>
-      </c>
-      <c r="L23" t="str">
-        <v/>
-      </c>
       <c r="M23" t="str">
         <v/>
       </c>
       <c r="N23" t="str">
+        <v/>
+      </c>
+      <c r="O23" t="str">
+        <v/>
+      </c>
+      <c r="P23" t="str">
         <v>TRUE</v>
       </c>
-      <c r="O23" t="str">
+      <c r="Q23" t="str">
         <v>custom</v>
       </c>
-      <c r="P23" t="str">
+      <c r="R23" t="str">
         <v>f62a31a0-1e5f-4f5c-a292-a1fcf8d4ec0d</v>
       </c>
-      <c r="Q23" t="str">
+      <c r="S23" t="str">
         <v>scheduled</v>
       </c>
     </row>
@@ -6486,42 +6843,48 @@
         <v>Hannah</v>
       </c>
       <c r="E24" t="str">
+        <v/>
+      </c>
+      <c r="F24" t="str">
         <v>DL</v>
       </c>
-      <c r="F24" t="str">
+      <c r="G24" t="str">
+        <v/>
+      </c>
+      <c r="H24" t="str">
         <v>2026-07-22T08:45:00</v>
       </c>
-      <c r="G24" t="str">
+      <c r="I24" t="str">
         <v>2026-07-22T12:15:00</v>
       </c>
-      <c r="H24" t="str">
+      <c r="J24" t="str">
         <v>FALSE</v>
       </c>
-      <c r="I24" t="str">
+      <c r="K24" t="str">
         <v>TRUE</v>
       </c>
-      <c r="J24" t="str">
+      <c r="L24" t="str">
         <v>client-session</v>
       </c>
-      <c r="K24" t="str">
-        <v/>
-      </c>
-      <c r="L24" t="str">
-        <v/>
-      </c>
       <c r="M24" t="str">
         <v/>
       </c>
       <c r="N24" t="str">
+        <v/>
+      </c>
+      <c r="O24" t="str">
+        <v/>
+      </c>
+      <c r="P24" t="str">
         <v>TRUE</v>
       </c>
-      <c r="O24" t="str">
+      <c r="Q24" t="str">
         <v>custom</v>
       </c>
-      <c r="P24" t="str">
+      <c r="R24" t="str">
         <v>f62a31a0-1e5f-4f5c-a292-a1fcf8d4ec0d</v>
       </c>
-      <c r="Q24" t="str">
+      <c r="S24" t="str">
         <v>scheduled</v>
       </c>
     </row>
@@ -6539,42 +6902,48 @@
         <v>Hannah</v>
       </c>
       <c r="E25" t="str">
+        <v/>
+      </c>
+      <c r="F25" t="str">
         <v>DL</v>
       </c>
-      <c r="F25" t="str">
+      <c r="G25" t="str">
+        <v/>
+      </c>
+      <c r="H25" t="str">
         <v>2026-07-24T08:45:00</v>
       </c>
-      <c r="G25" t="str">
+      <c r="I25" t="str">
         <v>2026-07-24T12:15:00</v>
       </c>
-      <c r="H25" t="str">
+      <c r="J25" t="str">
         <v>FALSE</v>
       </c>
-      <c r="I25" t="str">
+      <c r="K25" t="str">
         <v>TRUE</v>
       </c>
-      <c r="J25" t="str">
+      <c r="L25" t="str">
         <v>client-session</v>
       </c>
-      <c r="K25" t="str">
-        <v/>
-      </c>
-      <c r="L25" t="str">
-        <v/>
-      </c>
       <c r="M25" t="str">
         <v/>
       </c>
       <c r="N25" t="str">
+        <v/>
+      </c>
+      <c r="O25" t="str">
+        <v/>
+      </c>
+      <c r="P25" t="str">
         <v>TRUE</v>
       </c>
-      <c r="O25" t="str">
+      <c r="Q25" t="str">
         <v>custom</v>
       </c>
-      <c r="P25" t="str">
+      <c r="R25" t="str">
         <v>f62a31a0-1e5f-4f5c-a292-a1fcf8d4ec0d</v>
       </c>
-      <c r="Q25" t="str">
+      <c r="S25" t="str">
         <v>scheduled</v>
       </c>
     </row>
@@ -6592,42 +6961,48 @@
         <v>Hannah</v>
       </c>
       <c r="E26" t="str">
+        <v/>
+      </c>
+      <c r="F26" t="str">
         <v>DL</v>
       </c>
-      <c r="F26" t="str">
+      <c r="G26" t="str">
+        <v/>
+      </c>
+      <c r="H26" t="str">
         <v>2026-07-27T08:45:00</v>
       </c>
-      <c r="G26" t="str">
+      <c r="I26" t="str">
         <v>2026-07-27T12:15:00</v>
       </c>
-      <c r="H26" t="str">
+      <c r="J26" t="str">
         <v>FALSE</v>
       </c>
-      <c r="I26" t="str">
+      <c r="K26" t="str">
         <v>TRUE</v>
       </c>
-      <c r="J26" t="str">
+      <c r="L26" t="str">
         <v>client-session</v>
       </c>
-      <c r="K26" t="str">
-        <v/>
-      </c>
-      <c r="L26" t="str">
-        <v/>
-      </c>
       <c r="M26" t="str">
         <v/>
       </c>
       <c r="N26" t="str">
+        <v/>
+      </c>
+      <c r="O26" t="str">
+        <v/>
+      </c>
+      <c r="P26" t="str">
         <v>TRUE</v>
       </c>
-      <c r="O26" t="str">
+      <c r="Q26" t="str">
         <v>custom</v>
       </c>
-      <c r="P26" t="str">
+      <c r="R26" t="str">
         <v>f62a31a0-1e5f-4f5c-a292-a1fcf8d4ec0d</v>
       </c>
-      <c r="Q26" t="str">
+      <c r="S26" t="str">
         <v>scheduled</v>
       </c>
     </row>
@@ -6645,42 +7020,48 @@
         <v>Hannah</v>
       </c>
       <c r="E27" t="str">
+        <v/>
+      </c>
+      <c r="F27" t="str">
         <v>DL</v>
       </c>
-      <c r="F27" t="str">
+      <c r="G27" t="str">
+        <v/>
+      </c>
+      <c r="H27" t="str">
         <v>2026-07-29T08:45:00</v>
       </c>
-      <c r="G27" t="str">
+      <c r="I27" t="str">
         <v>2026-07-29T12:15:00</v>
       </c>
-      <c r="H27" t="str">
+      <c r="J27" t="str">
         <v>FALSE</v>
       </c>
-      <c r="I27" t="str">
+      <c r="K27" t="str">
         <v>TRUE</v>
       </c>
-      <c r="J27" t="str">
+      <c r="L27" t="str">
         <v>client-session</v>
       </c>
-      <c r="K27" t="str">
-        <v/>
-      </c>
-      <c r="L27" t="str">
-        <v/>
-      </c>
       <c r="M27" t="str">
         <v/>
       </c>
       <c r="N27" t="str">
+        <v/>
+      </c>
+      <c r="O27" t="str">
+        <v/>
+      </c>
+      <c r="P27" t="str">
         <v>TRUE</v>
       </c>
-      <c r="O27" t="str">
+      <c r="Q27" t="str">
         <v>custom</v>
       </c>
-      <c r="P27" t="str">
+      <c r="R27" t="str">
         <v>f62a31a0-1e5f-4f5c-a292-a1fcf8d4ec0d</v>
       </c>
-      <c r="Q27" t="str">
+      <c r="S27" t="str">
         <v>scheduled</v>
       </c>
     </row>
@@ -6698,42 +7079,48 @@
         <v>Hannah</v>
       </c>
       <c r="E28" t="str">
+        <v/>
+      </c>
+      <c r="F28" t="str">
         <v>DL</v>
       </c>
-      <c r="F28" t="str">
+      <c r="G28" t="str">
+        <v/>
+      </c>
+      <c r="H28" t="str">
         <v>2026-07-31T08:45:00</v>
       </c>
-      <c r="G28" t="str">
+      <c r="I28" t="str">
         <v>2026-07-31T12:15:00</v>
       </c>
-      <c r="H28" t="str">
+      <c r="J28" t="str">
         <v>FALSE</v>
       </c>
-      <c r="I28" t="str">
+      <c r="K28" t="str">
         <v>TRUE</v>
       </c>
-      <c r="J28" t="str">
+      <c r="L28" t="str">
         <v>client-session</v>
       </c>
-      <c r="K28" t="str">
-        <v/>
-      </c>
-      <c r="L28" t="str">
-        <v/>
-      </c>
       <c r="M28" t="str">
         <v/>
       </c>
       <c r="N28" t="str">
+        <v/>
+      </c>
+      <c r="O28" t="str">
+        <v/>
+      </c>
+      <c r="P28" t="str">
         <v>TRUE</v>
       </c>
-      <c r="O28" t="str">
+      <c r="Q28" t="str">
         <v>custom</v>
       </c>
-      <c r="P28" t="str">
+      <c r="R28" t="str">
         <v>f62a31a0-1e5f-4f5c-a292-a1fcf8d4ec0d</v>
       </c>
-      <c r="Q28" t="str">
+      <c r="S28" t="str">
         <v>scheduled</v>
       </c>
     </row>
@@ -6751,42 +7138,48 @@
         <v>Hannah</v>
       </c>
       <c r="E29" t="str">
+        <v/>
+      </c>
+      <c r="F29" t="str">
         <v>DL</v>
       </c>
-      <c r="F29" t="str">
+      <c r="G29" t="str">
+        <v/>
+      </c>
+      <c r="H29" t="str">
         <v>2026-08-03T08:45:00</v>
       </c>
-      <c r="G29" t="str">
+      <c r="I29" t="str">
         <v>2026-08-03T12:15:00</v>
       </c>
-      <c r="H29" t="str">
+      <c r="J29" t="str">
         <v>FALSE</v>
       </c>
-      <c r="I29" t="str">
+      <c r="K29" t="str">
         <v>TRUE</v>
       </c>
-      <c r="J29" t="str">
+      <c r="L29" t="str">
         <v>client-session</v>
       </c>
-      <c r="K29" t="str">
-        <v/>
-      </c>
-      <c r="L29" t="str">
-        <v/>
-      </c>
       <c r="M29" t="str">
         <v/>
       </c>
       <c r="N29" t="str">
+        <v/>
+      </c>
+      <c r="O29" t="str">
+        <v/>
+      </c>
+      <c r="P29" t="str">
         <v>TRUE</v>
       </c>
-      <c r="O29" t="str">
+      <c r="Q29" t="str">
         <v>custom</v>
       </c>
-      <c r="P29" t="str">
+      <c r="R29" t="str">
         <v>f62a31a0-1e5f-4f5c-a292-a1fcf8d4ec0d</v>
       </c>
-      <c r="Q29" t="str">
+      <c r="S29" t="str">
         <v>scheduled</v>
       </c>
     </row>
@@ -6804,42 +7197,48 @@
         <v>Hannah</v>
       </c>
       <c r="E30" t="str">
+        <v/>
+      </c>
+      <c r="F30" t="str">
         <v>DL</v>
       </c>
-      <c r="F30" t="str">
+      <c r="G30" t="str">
+        <v/>
+      </c>
+      <c r="H30" t="str">
         <v>2026-08-05T08:45:00</v>
       </c>
-      <c r="G30" t="str">
+      <c r="I30" t="str">
         <v>2026-08-05T12:15:00</v>
       </c>
-      <c r="H30" t="str">
+      <c r="J30" t="str">
         <v>FALSE</v>
       </c>
-      <c r="I30" t="str">
+      <c r="K30" t="str">
         <v>TRUE</v>
       </c>
-      <c r="J30" t="str">
+      <c r="L30" t="str">
         <v>client-session</v>
       </c>
-      <c r="K30" t="str">
-        <v/>
-      </c>
-      <c r="L30" t="str">
-        <v/>
-      </c>
       <c r="M30" t="str">
         <v/>
       </c>
       <c r="N30" t="str">
+        <v/>
+      </c>
+      <c r="O30" t="str">
+        <v/>
+      </c>
+      <c r="P30" t="str">
         <v>TRUE</v>
       </c>
-      <c r="O30" t="str">
+      <c r="Q30" t="str">
         <v>custom</v>
       </c>
-      <c r="P30" t="str">
+      <c r="R30" t="str">
         <v>f62a31a0-1e5f-4f5c-a292-a1fcf8d4ec0d</v>
       </c>
-      <c r="Q30" t="str">
+      <c r="S30" t="str">
         <v>scheduled</v>
       </c>
     </row>
@@ -6857,42 +7256,48 @@
         <v>Hannah</v>
       </c>
       <c r="E31" t="str">
+        <v/>
+      </c>
+      <c r="F31" t="str">
         <v>DL</v>
       </c>
-      <c r="F31" t="str">
+      <c r="G31" t="str">
+        <v/>
+      </c>
+      <c r="H31" t="str">
         <v>2026-08-07T08:45:00</v>
       </c>
-      <c r="G31" t="str">
+      <c r="I31" t="str">
         <v>2026-08-07T12:15:00</v>
       </c>
-      <c r="H31" t="str">
+      <c r="J31" t="str">
         <v>FALSE</v>
       </c>
-      <c r="I31" t="str">
+      <c r="K31" t="str">
         <v>TRUE</v>
       </c>
-      <c r="J31" t="str">
+      <c r="L31" t="str">
         <v>client-session</v>
       </c>
-      <c r="K31" t="str">
-        <v/>
-      </c>
-      <c r="L31" t="str">
-        <v/>
-      </c>
       <c r="M31" t="str">
         <v/>
       </c>
       <c r="N31" t="str">
+        <v/>
+      </c>
+      <c r="O31" t="str">
+        <v/>
+      </c>
+      <c r="P31" t="str">
         <v>TRUE</v>
       </c>
-      <c r="O31" t="str">
+      <c r="Q31" t="str">
         <v>custom</v>
       </c>
-      <c r="P31" t="str">
+      <c r="R31" t="str">
         <v>f62a31a0-1e5f-4f5c-a292-a1fcf8d4ec0d</v>
       </c>
-      <c r="Q31" t="str">
+      <c r="S31" t="str">
         <v>scheduled</v>
       </c>
     </row>
@@ -6910,42 +7315,48 @@
         <v>Hannah</v>
       </c>
       <c r="E32" t="str">
+        <v/>
+      </c>
+      <c r="F32" t="str">
         <v>DL</v>
       </c>
-      <c r="F32" t="str">
+      <c r="G32" t="str">
+        <v/>
+      </c>
+      <c r="H32" t="str">
         <v>2026-08-10T08:45:00</v>
       </c>
-      <c r="G32" t="str">
+      <c r="I32" t="str">
         <v>2026-08-10T12:15:00</v>
       </c>
-      <c r="H32" t="str">
+      <c r="J32" t="str">
         <v>FALSE</v>
       </c>
-      <c r="I32" t="str">
+      <c r="K32" t="str">
         <v>TRUE</v>
       </c>
-      <c r="J32" t="str">
+      <c r="L32" t="str">
         <v>client-session</v>
       </c>
-      <c r="K32" t="str">
-        <v/>
-      </c>
-      <c r="L32" t="str">
-        <v/>
-      </c>
       <c r="M32" t="str">
         <v/>
       </c>
       <c r="N32" t="str">
+        <v/>
+      </c>
+      <c r="O32" t="str">
+        <v/>
+      </c>
+      <c r="P32" t="str">
         <v>TRUE</v>
       </c>
-      <c r="O32" t="str">
+      <c r="Q32" t="str">
         <v>custom</v>
       </c>
-      <c r="P32" t="str">
+      <c r="R32" t="str">
         <v>f62a31a0-1e5f-4f5c-a292-a1fcf8d4ec0d</v>
       </c>
-      <c r="Q32" t="str">
+      <c r="S32" t="str">
         <v>scheduled</v>
       </c>
     </row>
@@ -6963,48 +7374,54 @@
         <v>Hannah</v>
       </c>
       <c r="E33" t="str">
+        <v/>
+      </c>
+      <c r="F33" t="str">
         <v>DL</v>
       </c>
-      <c r="F33" t="str">
+      <c r="G33" t="str">
+        <v/>
+      </c>
+      <c r="H33" t="str">
         <v>2026-08-12T08:45:00</v>
       </c>
-      <c r="G33" t="str">
+      <c r="I33" t="str">
         <v>2026-08-12T12:15:00</v>
       </c>
-      <c r="H33" t="str">
+      <c r="J33" t="str">
         <v>FALSE</v>
       </c>
-      <c r="I33" t="str">
+      <c r="K33" t="str">
         <v>TRUE</v>
       </c>
-      <c r="J33" t="str">
+      <c r="L33" t="str">
         <v>client-session</v>
       </c>
-      <c r="K33" t="str">
-        <v/>
-      </c>
-      <c r="L33" t="str">
-        <v/>
-      </c>
       <c r="M33" t="str">
         <v/>
       </c>
       <c r="N33" t="str">
+        <v/>
+      </c>
+      <c r="O33" t="str">
+        <v/>
+      </c>
+      <c r="P33" t="str">
         <v>TRUE</v>
       </c>
-      <c r="O33" t="str">
+      <c r="Q33" t="str">
         <v>custom</v>
       </c>
-      <c r="P33" t="str">
+      <c r="R33" t="str">
         <v>f62a31a0-1e5f-4f5c-a292-a1fcf8d4ec0d</v>
       </c>
-      <c r="Q33" t="str">
+      <c r="S33" t="str">
         <v>scheduled</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:Q33"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:S33"/>
   </ignoredErrors>
 </worksheet>
 </file>